--- a/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
+++ b/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
@@ -219,10 +219,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -613,13 +613,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="119" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="82" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 09:33:37 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
+          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 16:05:36 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
         </is>
       </c>
     </row>
@@ -785,11 +785,11 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>استعلام‌های موفق لحظه‌ای درگاه</t>
+          <t>استعلام‌های زنده و بروز امروز درگاه</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -798,18 +798,18 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>استعلام مستقیم موفق از وب‌سرویس پاسارگاد امروز</t>
+          <t>استعلام مستقیم موفق از وب‌سرویس بانک پاسارگاد در تاریخ امروز با کد رهگیری زنده</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>چک‌های با حفظ سابقه معتبر</t>
+          <t>چک‌های با حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
@@ -818,18 +818,18 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>حفظ ارقام معتبر پیشین بر اساس پایگاه داده</t>
+          <t>حفظ ارقام معتبر آخرین استعلام موفق (برای جلوگیری از صفر شدن داده‌ها)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>چک‌های تسویه یا سررسید گذشته</t>
+          <t>چک‌های خارج از کارتابل / عدم دسترسی</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -838,211 +838,231 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>سررسید گذشته و تسویه‌شده خارج از کارتابل</t>
+          <t>عدم حضور چک در کارتابل ۹ دارنده در استعلام گروهی امروز</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
+          <t>چک‌های سررسید گذشته و منقضی</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>فقره</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>سررسید گذشته و تسویه‌شده خارج از چرخه بانکی جاری</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>اسناد معاف از استعلام صیادی</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>فقره</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>سفته‌ها و اسناد ضمانتی فاقد شناسه ۱۶ رقمی صیاد</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>توزیع وضعیت رنگ اعتباری بانک مرکزی (CBI)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>رنگ اعتباری</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>تعداد مشتریان</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>درصد از کل</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>ارزیابی ریسک</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>سفید (خوش‌حساب بدون برگشتی)</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>کمترین ریسک اعتباری، فاقد هرگونه سوءاثر در سیستم بانکی</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>قرمز (دارای چک برگشتی فعال)</t>
+          <t>سفید (خوش‌حساب بدون برگشتی)</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C19" s="17" t="n">
-        <v>0.2692307692307692</v>
+        <v>36</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>0.6923076923076923</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>ریسک بالا؛ دارای چک برگشتی رفع سوءاثر نشده در شبکه بانکی</t>
+          <t>کمترین ریسک اعتباری، فاقد هرگونه سوءاثر در سیستم بانکی</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>قرمز (دارای چک برگشتی فعال)</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>0.2692307692307692</v>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>ریسک بالا؛ دارای چک برگشتی رفع سوءاثر نشده در شبکه بانکی</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>قهوه‌ای (سابقه چک‌های متعدد)</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B21" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C21" s="16" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>هشدار؛ سابقه چک‌های برگشتی مکرر یا حجم بالای نکول</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>ماتریس دوبعدی تحلیل ریسک اعتباری (Fintech Risk Matrix)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>رده ریسک مشتریان</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>تعداد مشتری</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>مجموع مبالغ تعهدات (ریال)</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>راهبرد پیشنهادی وصول و تعامل</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>ستاره‌ها (پرتراکنش و کم‌ریسک)</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>305440000000</v>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>توسعه همکاری و اعطای حداکثر تسهیلات و اعتبار تجاری</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>فرصت‌ها (کم‌تراکنش و کم‌ریسک)</t>
+          <t>ستاره‌ها (پرتراکنش و کم‌ریسک)</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>29920000000</v>
+        <v>305440000000</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>افزایش حجم تراکنش و تشویق به همکاری بیشتر</t>
+          <t>توسعه همکاری و اعطای حداکثر تسهیلات و اعتبار تجاری</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>تحت نظر (پرریسک با مبالغ خرد)</t>
+          <t>فرصت‌ها (کم‌تراکنش و کم‌ریسک)</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>13265000000</v>
+        <v>29920000000</v>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>کنترل مستمر و پایش وصولی‌ها قبل از سررسید</t>
+          <t>افزایش حجم تراکنش و تشویق به همکاری بیشتر</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>تحت نظر (پرریسک با مبالغ خرد)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>13265000000</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>کنترل مستمر و پایش وصولی‌ها قبل از سررسید</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
           <t>بحرانی (پرریسک با تعهدات سنگین)</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C28" s="13" t="n">
         <v>134700000000</v>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>اولویت فوری وصول؛ توقف پذیرش چک جدید و پیگیری حقوقی</t>
         </is>
@@ -1050,10 +1070,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1080,12 +1100,12 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="31" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="65" customWidth="1" min="17" max="17"/>
+    <col width="109" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1298,7 +1318,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M3" s="12" t="n">
@@ -1317,7 +1337,7 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:48 (کد پیگیری: 49685355323952)</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1395,7 @@
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M4" s="13" t="n">
@@ -1394,7 +1414,7 @@
       </c>
       <c r="Q4" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:48 (کد پیگیری: 49685355351830)</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1472,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M5" s="12" t="n">
@@ -1471,7 +1491,7 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:23 (کد پیگیری: 49685355298096)</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1549,7 @@
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M6" s="13" t="n">
@@ -1548,7 +1568,7 @@
       </c>
       <c r="Q6" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:52 (کد پیگیری: 49685355310602)</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1626,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M7" s="12" t="n">
@@ -1625,7 +1645,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:32 (کد پیگیری: 49685355323278)</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1703,7 @@
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M8" s="13" t="n">
@@ -1702,7 +1722,7 @@
       </c>
       <c r="Q8" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:42 (کد پیگیری: 49685355308538)</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1776,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M9" s="12" t="n">
@@ -1771,7 +1791,7 @@
       <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1849,7 @@
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M10" s="13" t="n">
@@ -1848,7 +1868,7 @@
       </c>
       <c r="Q10" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:33 (کد پیگیری: 49685355296282)</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1991,7 @@
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M12" s="13" t="n">
@@ -1990,7 +2010,7 @@
       </c>
       <c r="Q12" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:44 (کد پیگیری: 49685355304697)</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2068,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M13" s="12" t="n">
@@ -2067,7 +2087,7 @@
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:18 (کد پیگیری: 49685355310930)</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2145,7 @@
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M14" s="13" t="n">
@@ -2144,7 +2164,7 @@
       </c>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:46 (کد پیگیری: 49685355335081)</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2222,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M15" s="12" t="n">
@@ -2221,7 +2241,7 @@
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:22 (کد پیگیری: 49685355346621)</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2299,7 @@
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M16" s="13" t="n">
@@ -2298,7 +2318,7 @@
       </c>
       <c r="Q16" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:22 (کد پیگیری: 49685355318256)</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2376,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M17" s="12" t="n">
@@ -2375,7 +2395,7 @@
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:03 (کد پیگیری: 49685355280874)</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2453,7 @@
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M18" s="13" t="n">
@@ -2452,7 +2472,7 @@
       </c>
       <c r="Q18" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:40 (کد پیگیری: 49685355308517)</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2530,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M19" s="12" t="n">
@@ -2529,7 +2549,7 @@
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:14 (کد پیگیری: 49685355312796)</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2607,7 @@
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M20" s="13" t="n">
@@ -2606,7 +2626,7 @@
       </c>
       <c r="Q20" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:19 (کد پیگیری: 49685355346604)</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2684,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M21" s="12" t="n">
@@ -2683,7 +2703,7 @@
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:37 (کد پیگیری: 49685355357612)</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2761,7 @@
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M22" s="13" t="n">
@@ -2760,7 +2780,7 @@
       </c>
       <c r="Q22" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:43 (کد پیگیری: 49685355342484)</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2838,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M23" s="12" t="n">
@@ -2837,7 +2857,7 @@
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:47 (کد پیگیری: 49685355345990)</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2915,7 @@
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M24" s="13" t="n">
@@ -2914,7 +2934,7 @@
       </c>
       <c r="Q24" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:59 (کد پیگیری: 49685355276391)</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2992,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M25" s="12" t="n">
@@ -2991,7 +3011,7 @@
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:47 (کد پیگیری: 49685355304731)</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3069,7 @@
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M26" s="13" t="n">
@@ -3068,7 +3088,7 @@
       </c>
       <c r="Q26" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:21 (کد پیگیری: 49685355324524)</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3146,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M27" s="12" t="n">
@@ -3145,7 +3165,7 @@
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:50 (کد پیگیری: 49685355280295)</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3223,7 @@
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M28" s="13" t="n">
@@ -3222,7 +3242,7 @@
       </c>
       <c r="Q28" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:17 (کد پیگیری: 49685355297086)</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3300,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M29" s="12" t="n">
@@ -3299,7 +3319,7 @@
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:59 (کد پیگیری: 49685355335727)</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3373,7 @@
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M30" s="13" t="n">
@@ -3368,7 +3388,7 @@
       <c r="P30" s="10" t="inlineStr"/>
       <c r="Q30" s="11" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3446,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M31" s="12" t="n">
@@ -3445,7 +3465,7 @@
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:02 (کد پیگیری: 49685355310724)</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3523,7 @@
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M32" s="13" t="n">
@@ -3522,7 +3542,7 @@
       </c>
       <c r="Q32" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:04 (کد پیگیری: 49685355336236)</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3600,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M33" s="12" t="n">
@@ -3599,7 +3619,7 @@
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:29 (کد پیگیری: 49685355348704)</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3673,7 @@
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M34" s="13" t="n">
@@ -3668,7 +3688,7 @@
       <c r="P34" s="10" t="inlineStr"/>
       <c r="Q34" s="11" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3746,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M35" s="12" t="n">
@@ -3745,7 +3765,7 @@
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:16 (کد پیگیری: 49685355280999)</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3823,7 @@
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M36" s="13" t="n">
@@ -3822,7 +3842,7 @@
       </c>
       <c r="Q36" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:54 (کد پیگیری: 49685355305264)</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3900,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M37" s="12" t="n">
@@ -3899,7 +3919,7 @@
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:25 (کد پیگیری: 49685355351542)</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3977,7 @@
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M38" s="13" t="n">
@@ -3976,7 +3996,7 @@
       </c>
       <c r="Q38" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:40 (کد پیگیری: 49685355351224)</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4050,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M39" s="12" t="n">
@@ -4049,7 +4069,7 @@
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:36 (کد پیگیری: 49685355318403)</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4127,7 @@
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M40" s="13" t="n">
@@ -4126,7 +4146,7 @@
       </c>
       <c r="Q40" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:25 (کد پیگیری: 49685355320730)</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4204,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M41" s="12" t="n">
@@ -4199,7 +4219,7 @@
       <c r="P41" s="6" t="inlineStr"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4292,7 @@
       <c r="P42" s="10" t="inlineStr"/>
       <c r="Q42" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/05/28 منقضی شده و از کارتابل خارج است</t>
+          <t>سررسید چک در تاریخ 1405/05/28 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4350,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M43" s="12" t="n">
@@ -4349,7 +4369,7 @@
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:43:51) (کد پیگیری قبلی: 49682942030012)</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4427,7 @@
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M44" s="13" t="n">
@@ -4426,7 +4446,7 @@
       </c>
       <c r="Q44" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:32 (کد پیگیری: 49685355303590)</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4504,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M45" s="12" t="n">
@@ -4503,7 +4523,7 @@
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:11 (کد پیگیری: 49685355310284)</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4581,7 @@
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M46" s="13" t="n">
@@ -4580,7 +4600,7 @@
       </c>
       <c r="Q46" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:39 (کد پیگیری: 49685355325246)</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4658,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M47" s="12" t="n">
@@ -4657,7 +4677,7 @@
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:14 (کد پیگیری: 49685355340289)</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4735,7 @@
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M48" s="13" t="n">
@@ -4734,7 +4754,7 @@
       </c>
       <c r="Q48" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:42:05) (کد پیگیری قبلی: 49682941988821)</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4812,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M49" s="12" t="n">
@@ -4807,7 +4827,7 @@
       <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4900,7 @@
       <c r="P50" s="10" t="inlineStr"/>
       <c r="Q50" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل خارج است</t>
+          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4958,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M51" s="12" t="n">
@@ -4957,7 +4977,7 @@
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:58) (کد پیگیری قبلی: 49682942078736)</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5035,7 @@
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M52" s="13" t="n">
@@ -5034,7 +5054,7 @@
       </c>
       <c r="Q52" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:15 (کد پیگیری: 49685355321656)</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5112,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M53" s="12" t="n">
@@ -5111,7 +5131,7 @@
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:45 (کد پیگیری: 49685355335056)</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5189,7 @@
       </c>
       <c r="L54" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M54" s="13" t="n">
@@ -5188,7 +5208,7 @@
       </c>
       <c r="Q54" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:24:02 (کد پیگیری: 49685355362164)</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5266,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M55" s="12" t="n">
@@ -5265,7 +5285,7 @@
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:56 (کد پیگیری: 49685355290024)</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5343,7 @@
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M56" s="13" t="n">
@@ -5342,7 +5362,7 @@
       </c>
       <c r="Q56" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-08-28 20:51:57) (کد پیگیری قبلی: 49664982347170)</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5420,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M57" s="12" t="n">
@@ -5419,7 +5439,7 @@
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:16 (کد پیگیری: 49685355321681)</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5497,7 @@
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M58" s="13" t="n">
@@ -5496,7 +5516,7 @@
       </c>
       <c r="Q58" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:44 (کد پیگیری: 49685355345947)</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5589,7 @@
       <c r="P59" s="6" t="inlineStr"/>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/02 منقضی شده و از کارتابل خارج است</t>
+          <t>سررسید چک در تاریخ 1405/06/02 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5647,7 @@
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M60" s="13" t="n">
@@ -5646,7 +5666,7 @@
       </c>
       <c r="Q60" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:39 (کد پیگیری: 49685355295883)</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5724,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M61" s="12" t="n">
@@ -5723,7 +5743,7 @@
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:13 (کد پیگیری: 49685355317164)</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5801,7 @@
       </c>
       <c r="L62" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M62" s="13" t="n">
@@ -5800,7 +5820,7 @@
       </c>
       <c r="Q62" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:42 (کد پیگیری: 49685355330603)</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5878,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M63" s="12" t="n">
@@ -5877,7 +5897,7 @@
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:18 (کد پیگیری: 49685355337378)</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5955,7 @@
       </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M64" s="13" t="n">
@@ -5954,7 +5974,7 @@
       </c>
       <c r="Q64" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:36 (کد پیگیری: 49685355342412)</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6032,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M65" s="12" t="n">
@@ -6031,7 +6051,7 @@
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:46 (کد پیگیری: 49685355351800)</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6109,7 @@
       </c>
       <c r="L66" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M66" s="13" t="n">
@@ -6108,7 +6128,7 @@
       </c>
       <c r="Q66" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:49 (کد پیگیری: 49685355351842)</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6186,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M67" s="12" t="n">
@@ -6185,7 +6205,7 @@
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:50 (کد پیگیری: 49685355359143)</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6263,7 @@
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M68" s="13" t="n">
@@ -6262,7 +6282,7 @@
       </c>
       <c r="Q68" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:51 (کد پیگیری: 49685355356744)</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6340,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M69" s="12" t="n">
@@ -6335,7 +6355,7 @@
       <c r="P69" s="6" t="inlineStr"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6413,7 @@
       </c>
       <c r="L70" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M70" s="13" t="n">
@@ -6408,7 +6428,7 @@
       <c r="P70" s="10" t="inlineStr"/>
       <c r="Q70" s="11" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6501,7 @@
       <c r="P71" s="6" t="inlineStr"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/06 منقضی شده و از کارتابل خارج است</t>
+          <t>سررسید چک در تاریخ 1405/06/06 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6559,7 @@
       </c>
       <c r="L72" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M72" s="13" t="n">
@@ -6558,7 +6578,7 @@
       </c>
       <c r="Q72" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:45 (کد پیگیری: 49685355304716)</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6636,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M73" s="12" t="n">
@@ -6635,7 +6655,7 @@
       </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:19 (کد پیگیری: 49685355310375)</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6713,7 @@
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M74" s="13" t="n">
@@ -6712,7 +6732,7 @@
       </c>
       <c r="Q74" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:23 (کد پیگیری: 49685355339937)</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6786,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M75" s="12" t="n">
@@ -6781,7 +6801,7 @@
       <c r="P75" s="6" t="inlineStr"/>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6920,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M77" s="12" t="n">
@@ -6919,7 +6939,7 @@
       </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:41 (کد پیگیری: 49685355328166)</t>
         </is>
       </c>
     </row>
@@ -6988,7 +7008,7 @@
       <c r="P78" s="10" t="inlineStr"/>
       <c r="Q78" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل خارج است</t>
+          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7066,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M79" s="12" t="n">
@@ -7065,7 +7085,7 @@
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:41) (کد پیگیری قبلی: 49682942080036)</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7143,7 @@
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M80" s="13" t="n">
@@ -7142,7 +7162,7 @@
       </c>
       <c r="Q80" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:55 (کد پیگیری: 49685355305280)</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7220,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M81" s="12" t="n">
@@ -7219,7 +7239,7 @@
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:27 (کد پیگیری: 49685355323218)</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7297,7 @@
       </c>
       <c r="L82" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M82" s="13" t="n">
@@ -7296,7 +7316,7 @@
       </c>
       <c r="Q82" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:00 (کد پیگیری: 49685355327928)</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7374,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M83" s="12" t="n">
@@ -7373,7 +7393,7 @@
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:27 (کد پیگیری: 49685355351557)</t>
         </is>
       </c>
     </row>
@@ -7431,7 +7451,7 @@
       </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M84" s="13" t="n">
@@ -7450,7 +7470,7 @@
       </c>
       <c r="Q84" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:00 (کد پیگیری: 49685355305344)</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7528,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M85" s="12" t="n">
@@ -7523,7 +7543,7 @@
       <c r="P85" s="6" t="inlineStr"/>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7601,7 @@
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M86" s="13" t="n">
@@ -7600,7 +7620,7 @@
       </c>
       <c r="Q86" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:59 (کد پیگیری: 49685355307268)</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7678,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M87" s="12" t="n">
@@ -7677,7 +7697,7 @@
       </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:18 (کد پیگیری: 49685355297097)</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7755,7 @@
       </c>
       <c r="L88" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M88" s="13" t="n">
@@ -7754,7 +7774,7 @@
       </c>
       <c r="Q88" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:30 (کد پیگیری: 49685355323269)</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7832,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M89" s="12" t="n">
@@ -7831,7 +7851,7 @@
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:54 (کد پیگیری: 49685355273867)</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7909,7 @@
       </c>
       <c r="L90" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M90" s="13" t="n">
@@ -7908,7 +7928,7 @@
       </c>
       <c r="Q90" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:58 (کد پیگیری: 49685355276364)</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7986,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M91" s="12" t="n">
@@ -7985,7 +8005,7 @@
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:10 (کد پیگیری: 49685355321584)</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8063,7 @@
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M92" s="13" t="n">
@@ -8058,7 +8078,7 @@
       <c r="P92" s="10" t="inlineStr"/>
       <c r="Q92" s="11" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8136,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M93" s="12" t="n">
@@ -8135,7 +8155,7 @@
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:38 (کد پیگیری: 49685355330069)</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8213,7 @@
       </c>
       <c r="L94" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M94" s="13" t="n">
@@ -8208,7 +8228,7 @@
       <c r="P94" s="10" t="inlineStr"/>
       <c r="Q94" s="11" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8286,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M95" s="12" t="n">
@@ -8285,7 +8305,7 @@
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:12 (کد پیگیری: 49685355338321)</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8363,7 @@
       </c>
       <c r="L96" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M96" s="13" t="n">
@@ -8362,7 +8382,7 @@
       </c>
       <c r="Q96" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:33 (کد پیگیری: 49685355355077)</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8451,7 @@
       <c r="P97" s="6" t="inlineStr"/>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل خارج است</t>
+          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8509,7 @@
       </c>
       <c r="L98" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M98" s="13" t="n">
@@ -8508,7 +8528,7 @@
       </c>
       <c r="Q98" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:24 (کد پیگیری: 49685355289857)</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8586,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M99" s="12" t="n">
@@ -8585,7 +8605,7 @@
       </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:45:48) (کد پیگیری قبلی: 49682942065011)</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8663,7 @@
       </c>
       <c r="L100" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M100" s="13" t="n">
@@ -8662,7 +8682,7 @@
       </c>
       <c r="Q100" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:04 (کد پیگیری: 49685355310220)</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8740,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M101" s="12" t="n">
@@ -8739,7 +8759,7 @@
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:33 (کد پیگیری: 49685355326605)</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8817,7 @@
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M102" s="13" t="n">
@@ -8816,7 +8836,7 @@
       </c>
       <c r="Q102" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:55 (کد پیگیری: 49685355356775)</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8894,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M103" s="12" t="n">
@@ -8889,7 +8909,7 @@
       <c r="P103" s="6" t="inlineStr"/>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8967,7 @@
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M104" s="13" t="n">
@@ -8966,7 +8986,7 @@
       </c>
       <c r="Q104" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:47:08) (کد پیگیری قبلی: 49682942084694)</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9044,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M105" s="12" t="n">
@@ -9043,7 +9063,7 @@
       </c>
       <c r="Q105" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:24 (کد پیگیری: 49685355318270)</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9136,7 @@
       <c r="P106" s="10" t="inlineStr"/>
       <c r="Q106" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/11 منقضی شده و از کارتابل خارج است</t>
+          <t>سررسید چک در تاریخ 1405/06/11 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9194,7 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M107" s="12" t="n">
@@ -9193,7 +9213,7 @@
       </c>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:44 (کد پیگیری: 49685355330620)</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9271,7 @@
       </c>
       <c r="L108" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M108" s="13" t="n">
@@ -9270,7 +9290,7 @@
       </c>
       <c r="Q108" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:51 (کد پیگیری: 49685355327817)</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9348,7 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M109" s="12" t="n">
@@ -9347,7 +9367,7 @@
       </c>
       <c r="Q109" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:56 (کد پیگیری: 49685355336594)</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9425,7 @@
       </c>
       <c r="L110" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M110" s="13" t="n">
@@ -9424,7 +9444,7 @@
       </c>
       <c r="Q110" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:58 (کد پیگیری: 49685355335702)</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9502,7 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M111" s="12" t="n">
@@ -9501,7 +9521,7 @@
       </c>
       <c r="Q111" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:02 (کد پیگیری: 49685355327942)</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9579,7 @@
       </c>
       <c r="L112" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M112" s="13" t="n">
@@ -9578,7 +9598,7 @@
       </c>
       <c r="Q112" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:09 (کد پیگیری: 49685355345013)</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9656,7 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M113" s="12" t="n">
@@ -9651,7 +9671,7 @@
       <c r="P113" s="6" t="inlineStr"/>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9744,7 @@
       <c r="P114" s="10" t="inlineStr"/>
       <c r="Q114" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل خارج است</t>
+          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9802,7 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M115" s="12" t="n">
@@ -9801,7 +9821,7 @@
       </c>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:36 (کد پیگیری: 49685355299734)</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9879,7 @@
       </c>
       <c r="L116" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M116" s="13" t="n">
@@ -9878,7 +9898,7 @@
       </c>
       <c r="Q116" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-08-28 20:53:55) (کد پیگیری قبلی: 49664982349765)</t>
         </is>
       </c>
     </row>
@@ -9936,7 +9956,7 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M117" s="12" t="n">
@@ -9951,7 +9971,7 @@
       <c r="P117" s="6" t="inlineStr"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10029,7 @@
       </c>
       <c r="L118" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M118" s="13" t="n">
@@ -10028,7 +10048,7 @@
       </c>
       <c r="Q118" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:17 (کد پیگیری: 49685355338378)</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10106,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M119" s="12" t="n">
@@ -10105,7 +10125,7 @@
       </c>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:35 (کد پیگیری: 49685355346272)</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10183,7 @@
       </c>
       <c r="L120" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M120" s="13" t="n">
@@ -10182,7 +10202,7 @@
       </c>
       <c r="Q120" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:54 (کد پیگیری: 49685355356761)</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10260,7 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M121" s="12" t="n">
@@ -10259,7 +10279,7 @@
       </c>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:57 (کد پیگیری: 49685355362576)</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10337,7 @@
       </c>
       <c r="L122" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M122" s="13" t="n">
@@ -10336,7 +10356,7 @@
       </c>
       <c r="Q122" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:24:00 (کد پیگیری: 49685355359253)</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10414,7 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M123" s="12" t="n">
@@ -10413,7 +10433,7 @@
       </c>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:03 (کد پیگیری: 49685355304941)</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10491,7 @@
       </c>
       <c r="L124" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M124" s="13" t="n">
@@ -10490,7 +10510,7 @@
       </c>
       <c r="Q124" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:29 (کد پیگیری: 49685355323252)</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10568,7 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M125" s="12" t="n">
@@ -10567,7 +10587,7 @@
       </c>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:05 (کد پیگیری: 49685355336252)</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10645,7 @@
       </c>
       <c r="L126" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M126" s="13" t="n">
@@ -10644,7 +10664,7 @@
       </c>
       <c r="Q126" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:13 (کد پیگیری: 49685355332442)</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10722,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M127" s="12" t="n">
@@ -10721,7 +10741,7 @@
       </c>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:30 (کد پیگیری: 49685355351603)</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10799,7 @@
       </c>
       <c r="L128" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M128" s="13" t="n">
@@ -10798,7 +10818,7 @@
       </c>
       <c r="Q128" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:41 (کد پیگیری: 49685355348870)</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10876,7 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M129" s="12" t="n">
@@ -10875,7 +10895,7 @@
       </c>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:45 (کد پیگیری: 49685355345963)</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10953,7 @@
       </c>
       <c r="L130" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M130" s="13" t="n">
@@ -10952,7 +10972,7 @@
       </c>
       <c r="Q130" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:06 (کد پیگیری: 49685355308315)</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11030,7 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M131" s="12" t="n">
@@ -11029,7 +11049,7 @@
       </c>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:56 (کد پیگیری: 49685355307242)</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11107,7 @@
       </c>
       <c r="L132" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M132" s="13" t="n">
@@ -11106,7 +11126,7 @@
       </c>
       <c r="Q132" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:20 (کد پیگیری: 49685355297107)</t>
         </is>
       </c>
     </row>
@@ -11164,7 +11184,7 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M133" s="12" t="n">
@@ -11183,7 +11203,7 @@
       </c>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:29 (کد پیگیری: 49685355303545)</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11261,7 @@
       </c>
       <c r="L134" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M134" s="13" t="n">
@@ -11260,7 +11280,7 @@
       </c>
       <c r="Q134" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:47:12) (کد پیگیری قبلی: 49682942089573)</t>
         </is>
       </c>
     </row>
@@ -11318,7 +11338,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M135" s="12" t="n">
@@ -11333,7 +11353,7 @@
       <c r="P135" s="6" t="inlineStr"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11411,7 @@
       </c>
       <c r="L136" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M136" s="13" t="n">
@@ -11406,7 +11426,7 @@
       <c r="P136" s="10" t="inlineStr"/>
       <c r="Q136" s="11" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11484,7 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M137" s="12" t="n">
@@ -11483,7 +11503,7 @@
       </c>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:07 (کد پیگیری: 49685355318094)</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11561,7 @@
       </c>
       <c r="L138" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M138" s="13" t="n">
@@ -11560,7 +11580,7 @@
       </c>
       <c r="Q138" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:06 (کد پیگیری: 49685355344022)</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11638,7 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M139" s="12" t="n">
@@ -11633,7 +11653,7 @@
       <c r="P139" s="6" t="inlineStr"/>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11711,7 @@
       </c>
       <c r="L140" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M140" s="13" t="n">
@@ -11706,7 +11726,7 @@
       <c r="P140" s="10" t="inlineStr"/>
       <c r="Q140" s="11" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11784,7 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M141" s="12" t="n">
@@ -11783,7 +11803,7 @@
       </c>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:57 (کد پیگیری: 49685355304887)</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11861,7 @@
       </c>
       <c r="L142" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M142" s="13" t="n">
@@ -11856,7 +11876,7 @@
       <c r="P142" s="10" t="inlineStr"/>
       <c r="Q142" s="11" t="inlineStr">
         <is>
-          <t>اطلاعات معتبر آخرین استعلام موفق حفظ شد</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11934,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M143" s="12" t="n">
@@ -11933,7 +11953,7 @@
       </c>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:28 (کد پیگیری: 49685355318322)</t>
         </is>
       </c>
     </row>
@@ -11991,7 +12011,7 @@
       </c>
       <c r="L144" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M144" s="13" t="n">
@@ -12010,7 +12030,7 @@
       </c>
       <c r="Q144" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:28 (کد پیگیری: 49685355346211)</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12088,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M145" s="12" t="n">
@@ -12087,7 +12107,7 @@
       </c>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:13 (کد پیگیری: 49685355294555)</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12165,7 @@
       </c>
       <c r="L146" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M146" s="13" t="n">
@@ -12164,7 +12184,7 @@
       </c>
       <c r="Q146" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:31 (کد پیگیری: 49685355291850)</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12242,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M147" s="12" t="n">
@@ -12241,7 +12261,7 @@
       </c>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:09 (کد پیگیری: 49685355289191)</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12319,7 @@
       </c>
       <c r="L148" s="11" t="inlineStr">
         <is>
-          <t>موفق (درگاه زنده)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M148" s="13" t="n">
@@ -12318,7 +12338,7 @@
       </c>
       <c r="Q148" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده از درگاه پاسارگاد با موفقیت ثبت شد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:49 (کد پیگیری: 49685355309095)</t>
         </is>
       </c>
     </row>

--- a/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
+++ b/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 16:05:36 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
+          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 18:54:36 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>16109551207163</v>
+        <v>16448381207163</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>1,610,955 تومان (تعهدات صادرکنندگان در شبکه بانکی)</t>
+          <t>1,644,838 تومان (تعهدات صادرکنندگان در شبکه بانکی)</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>4064396530614</v>
+        <v>4076196530614</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>406,440 تومان (سابقه تسویه موفق)</t>
+          <t>407,620 تومان (سابقه تسویه موفق)</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>589878000000</v>
+        <v>602178000000</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>58,988 تومان (چک‌های برگشتی ثبت‌شده بانک مرکزی)</t>
+          <t>60,218 تومان (چک‌های برگشتی ثبت‌شده بانک مرکزی)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2884615384615384</v>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>305440000000</v>
+        <v>290440000000</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>134700000000</v>
+        <v>149700000000</v>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
@@ -3632,10 +3632,14 @@
           <t>زهرا بهرامي پويا</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr"/>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>0927624011</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -3668,27 +3672,31 @@
       </c>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>فاطمه زمانزاده</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M34" s="13" t="n">
-        <v>0</v>
+        <v>338830000000</v>
       </c>
       <c r="N34" s="13" t="n">
-        <v>0</v>
+        <v>11800000000</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="10" t="inlineStr"/>
+        <v>12300000000</v>
+      </c>
+      <c r="P34" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 18:54:14</t>
+        </is>
+      </c>
       <c r="Q34" s="11" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 18:54:14 (کد پیگیری: 49686363251893)</t>
         </is>
       </c>
     </row>
@@ -13265,23 +13273,27 @@
           <t>زهرا بهرامي پويا</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr"/>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>0927624011</t>
+        </is>
+      </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>سفید</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>87</v>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>عالی</t>
+        <v>0</v>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>پرخطر</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
         </is>
       </c>
       <c r="H18" s="10" t="n">
@@ -13291,14 +13303,14 @@
         <v>15000000000</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0</v>
+        <v>338830000000</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>0</v>
+        <v>12300000000</v>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
+          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
         </is>
       </c>
     </row>

--- a/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
+++ b/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 18:54:36 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
+          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 19:02:20 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
         </is>
       </c>
     </row>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.6730769230769231</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.03846153846153846</v>
+        <v>0</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>290440000000</v>
+        <v>235690000000</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>149700000000</v>
+        <v>204450000000</v>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
@@ -2336,9 +2336,9 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>قهوه ای</t>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -2413,9 +2413,9 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>قهوه ای</t>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -2490,9 +2490,9 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>قهوه ای</t>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -2567,9 +2567,9 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>قهوه ای</t>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -2644,9 +2644,9 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>قهوه ای</t>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -2721,9 +2721,9 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>قهوه ای</t>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -2798,9 +2798,9 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>قهوه ای</t>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -5234,9 +5234,9 @@
           <t>0922030936</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -5311,9 +5311,9 @@
           <t>0922030936</t>
         </is>
       </c>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -5388,9 +5388,9 @@
           <t>0922030936</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -5465,9 +5465,9 @@
           <t>0922030936</t>
         </is>
       </c>
-      <c r="D58" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -8477,9 +8477,9 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D98" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
@@ -8554,9 +8554,9 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D99" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D99" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -8631,9 +8631,9 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D100" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
@@ -8708,9 +8708,9 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D101" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -8785,9 +8785,9 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D102" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D102" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
@@ -8862,9 +8862,9 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D103" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D103" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -9089,9 +9089,9 @@
           <t>6430003159</t>
         </is>
       </c>
-      <c r="D106" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D106" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
@@ -9162,9 +9162,9 @@
           <t>6430003159</t>
         </is>
       </c>
-      <c r="D107" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D107" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -9239,9 +9239,9 @@
           <t>6430003159</t>
         </is>
       </c>
-      <c r="D108" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D108" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
@@ -9316,9 +9316,9 @@
           <t>6430003159</t>
         </is>
       </c>
-      <c r="D109" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D109" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -9393,9 +9393,9 @@
           <t>6430003159</t>
         </is>
       </c>
-      <c r="D110" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D110" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
@@ -9470,9 +9470,9 @@
           <t>6430003159</t>
         </is>
       </c>
-      <c r="D111" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D111" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -9547,9 +9547,9 @@
           <t>6430003159</t>
         </is>
       </c>
-      <c r="D112" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D112" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
@@ -9624,9 +9624,9 @@
           <t>6430003159</t>
         </is>
       </c>
-      <c r="D113" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+      <c r="D113" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -12210,9 +12210,9 @@
           <t>1920394974</t>
         </is>
       </c>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>قهوه ای</t>
+      <c r="D147" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
@@ -12287,9 +12287,9 @@
           <t>1920394974</t>
         </is>
       </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>قهوه ای</t>
+      <c r="D148" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E148" s="10" t="inlineStr">
@@ -12934,11 +12934,11 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>قهوه ای</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>48.8</v>
+        <v>42.8</v>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
@@ -13676,20 +13676,20 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>سفید</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>خوب</t>
+        <v>16</v>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>پرخطر</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
         </is>
       </c>
       <c r="H26" s="10" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>سلامت مالی مطلوب و کم‌ریسک. تداوم همکاری با رعایت دوره‌های معمول تسویه حساب توصیه می‌شود.</t>
+          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
         </is>
       </c>
     </row>
@@ -14310,20 +14310,20 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>سفید</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>خوب</t>
+        <v>25</v>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>پرخطر</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>سلامت مالی مطلوب و کم‌ریسک. تداوم همکاری با رعایت دوره‌های معمول تسویه حساب توصیه می‌شود.</t>
+          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
         </is>
       </c>
     </row>
@@ -14410,11 +14410,11 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>سفید</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>قهوه ای</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">

--- a/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
+++ b/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 19:02:20 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
+          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 19:14:20 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>16448381207163</v>
+        <v>16795489807163</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>1,644,838 تومان (تعهدات صادرکنندگان در شبکه بانکی)</t>
+          <t>1,679,549 تومان (تعهدات صادرکنندگان در شبکه بانکی)</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>4076196530614</v>
+        <v>4117195410614</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>407,620 تومان (سابقه تسویه موفق)</t>
+          <t>411,720 تومان (سابقه تسویه موفق)</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>602178000000</v>
+        <v>604830000000</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>60,218 تومان (چک‌های برگشتی ثبت‌شده بانک مرکزی)</t>
+          <t>60,483 تومان (چک‌های برگشتی ثبت‌شده بانک مرکزی)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -4207,27 +4207,31 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0</v>
+        <v>56196200000</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>0</v>
+        <v>20803880000</v>
       </c>
       <c r="O41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P41" s="6" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 19:14:03</t>
+        </is>
+      </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363364447)</t>
         </is>
       </c>
     </row>
@@ -6343,27 +6347,31 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0</v>
+        <v>28000000000</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
+        <v>240000000</v>
       </c>
       <c r="O69" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P69" s="6" t="inlineStr"/>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 19:14:03</t>
+        </is>
+      </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363374741)</t>
         </is>
       </c>
     </row>
@@ -6416,27 +6424,31 @@
       </c>
       <c r="K70" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L70" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M70" s="13" t="n">
-        <v>0</v>
+        <v>28000000000</v>
       </c>
       <c r="N70" s="13" t="n">
-        <v>0</v>
+        <v>240000000</v>
       </c>
       <c r="O70" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P70" s="10" t="inlineStr"/>
+      <c r="P70" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 19:14:03</t>
+        </is>
+      </c>
       <c r="Q70" s="11" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363377638)</t>
         </is>
       </c>
     </row>
@@ -8897,27 +8909,31 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0</v>
+        <v>48136400000</v>
       </c>
       <c r="N103" s="12" t="n">
-        <v>0</v>
+        <v>35000000</v>
       </c>
       <c r="O103" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P103" s="6" t="inlineStr"/>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 19:14:03</t>
+        </is>
+      </c>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363379579)</t>
         </is>
       </c>
     </row>
@@ -11641,27 +11657,31 @@
       </c>
       <c r="K139" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>علیرضا ضیافتی</t>
         </is>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M139" s="12" t="n">
-        <v>0</v>
+        <v>93388000000</v>
       </c>
       <c r="N139" s="12" t="n">
-        <v>0</v>
+        <v>9840000000</v>
       </c>
       <c r="O139" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" s="6" t="inlineStr"/>
+        <v>1326000000</v>
+      </c>
+      <c r="P139" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 19:14:03</t>
+        </is>
+      </c>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363364456)</t>
         </is>
       </c>
     </row>
@@ -11714,27 +11734,31 @@
       </c>
       <c r="K140" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>علیرضا ضیافتی</t>
         </is>
       </c>
       <c r="L140" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M140" s="13" t="n">
-        <v>0</v>
+        <v>93388000000</v>
       </c>
       <c r="N140" s="13" t="n">
-        <v>0</v>
+        <v>9840000000</v>
       </c>
       <c r="O140" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" s="10" t="inlineStr"/>
+        <v>1326000000</v>
+      </c>
+      <c r="P140" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 19:14:03</t>
+        </is>
+      </c>
       <c r="Q140" s="11" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363379050)</t>
         </is>
       </c>
     </row>
@@ -13449,7 +13473,7 @@
         <v>3520000000</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>56196200000</v>
+        <v>112392400000</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>0</v>
@@ -13730,7 +13754,7 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>91.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
@@ -13749,7 +13773,7 @@
         <v>24000000000</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>252000000000</v>
+        <v>308000000000</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
@@ -14314,7 +14338,7 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>25</v>
+        <v>29.2</v>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
@@ -14333,7 +14357,7 @@
         <v>16450000000</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>285933600000</v>
+        <v>334070000000</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>1326000000</v>
@@ -14814,7 +14838,7 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>20.7</v>
+        <v>0.6</v>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
@@ -14833,10 +14857,10 @@
         <v>22000000000</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>186776000000</v>
+        <v>373552000000</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>2652000000</v>
+        <v>5304000000</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>

--- a/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
+++ b/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 19:14:20 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
+          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 19:17:41 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
         </is>
       </c>
     </row>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>235690000000</v>
+        <v>293940000000</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>29920000000</v>
+        <v>29260000000</v>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>13265000000</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>204450000000</v>
+        <v>146860000000</v>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>احمد زحمت كش باجگيران</t>
+          <t>ابوالفضل شافعي</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>0860270361</t>
+          <t>0941987231</t>
         </is>
       </c>
       <c r="D2" s="18" t="inlineStr">
@@ -1214,28 +1214,32 @@
           <t>قرمز</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>9700040200262950</t>
+        </is>
+      </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>66666</t>
+          <t>695631</t>
         </is>
       </c>
       <c r="G2" s="13" t="n">
-        <v>1400000000</v>
+        <v>7500000000</v>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>1405/06/10</t>
+          <t>1405/05/30</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>منقضی (5 روز گذشته)</t>
+          <t>منقضی (16 روز گذشته)</t>
         </is>
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي</t>
+          <t>* شهر ميدان راهنمايي مشهد</t>
         </is>
       </c>
       <c r="K2" s="11" t="inlineStr">
@@ -1245,22 +1249,26 @@
       </c>
       <c r="L2" s="11" t="inlineStr">
         <is>
-          <t>سند سفته / فاقد صیاد (معاف)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M2" s="13" t="n">
-        <v>0</v>
+        <v>46230000000</v>
       </c>
       <c r="N2" s="13" t="n">
-        <v>0</v>
+        <v>18135000000</v>
       </c>
       <c r="O2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="10" t="inlineStr"/>
+        <v>12800000000</v>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:20:56</t>
+        </is>
+      </c>
       <c r="Q2" s="11" t="inlineStr">
         <is>
-          <t>سند تضمینی یا سفته فاقد شناسه ۱۶ رقمی صیاد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:56 (کد پیگیری: 49685355290024)</t>
         </is>
       </c>
     </row>
@@ -1283,14 +1291,10 @@
           <t>قرمز</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>4309030115225520</t>
-        </is>
-      </c>
+      <c r="E3" s="6" t="inlineStr"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>179686</t>
+          <t>66666</t>
         </is>
       </c>
       <c r="G3" s="12" t="n">
@@ -1298,12 +1302,12 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>1405/09/10</t>
+          <t>1405/06/10</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>86 روز مانده</t>
+          <t>منقضی (5 روز گذشته)</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
@@ -1318,26 +1322,22 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سند سفته / فاقد صیاد (معاف)</t>
         </is>
       </c>
       <c r="M3" s="12" t="n">
-        <v>135058325000</v>
+        <v>0</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>5534728000</v>
+        <v>0</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>11550000000</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:48</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:48 (کد پیگیری: 49685355323952)</t>
+          <t>سند تضمینی یا سفته فاقد شناسه ۱۶ رقمی صیاد</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>5764030115225522</t>
+          <t>4309030115225520</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>179688</t>
+          <t>179686</t>
         </is>
       </c>
       <c r="G4" s="13" t="n">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>1406/01/10</t>
+          <t>1405/09/10</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>205 روز مانده</t>
+          <t>86 روز مانده</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* بانک ملي کوي المهدي</t>
         </is>
       </c>
       <c r="K4" s="11" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="P4" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:48</t>
+          <t>2026-09-06 09:22:48</t>
         </is>
       </c>
       <c r="Q4" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:48 (کد پیگیری: 49685355351830)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:48 (کد پیگیری: 49685355323952)</t>
         </is>
       </c>
     </row>
@@ -1424,45 +1424,45 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>اسدیان سو هان حمید</t>
+          <t>احمد زحمت كش باجگيران</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>5220146602</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>0860270361</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>7376050020050460</t>
+          <t>5764030115225522</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>840429</t>
+          <t>179688</t>
         </is>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1700000000</v>
+        <v>1400000000</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>1405/06/25</t>
+          <t>1406/01/10</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>10 روز مانده</t>
+          <t>205 روز مانده</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>* صادرات کوي امام هادي</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1476,22 +1476,22 @@
         </is>
       </c>
       <c r="M5" s="12" t="n">
-        <v>50434720000</v>
+        <v>135058325000</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>5332712000</v>
+        <v>5534728000</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>0</v>
+        <v>11550000000</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:23</t>
+          <t>2026-09-06 09:23:48</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:23 (کد پیگیری: 49685355298096)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:48 (کد پیگیری: 49685355351830)</t>
         </is>
       </c>
     </row>
@@ -1516,30 +1516,30 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>3438040101328881</t>
+          <t>7376050020050460</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>922904</t>
+          <t>840429</t>
         </is>
       </c>
       <c r="G6" s="13" t="n">
-        <v>3400000000</v>
+        <v>1700000000</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>1405/07/14</t>
+          <t>1405/06/25</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>30 روز مانده</t>
+          <t>10 روز مانده</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>* صادرات کوي امام هادي 3357</t>
+          <t>* صادرات کوي امام هادي</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:52</t>
+          <t>2026-09-06 09:21:23</t>
         </is>
       </c>
       <c r="Q6" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:52 (کد پیگیری: 49685355310602)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:23 (کد پیگیری: 49685355298096)</t>
         </is>
       </c>
     </row>
@@ -1593,30 +1593,30 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>5400050020050462</t>
+          <t>3438040101328881</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>840431</t>
+          <t>922904</t>
         </is>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1700000000</v>
+        <v>3400000000</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>1405/08/25</t>
+          <t>1405/07/14</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>71 روز مانده</t>
+          <t>30 روز مانده</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>* صادرات کوي امام هادي</t>
+          <t>* صادرات کوي امام هادي 3357</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:32</t>
+          <t>2026-09-06 09:21:52</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:32 (کد پیگیری: 49685355323278)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:52 (کد پیگیری: 49685355310602)</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>افشاری قز غاوه سجاد</t>
+          <t>اسدیان سو هان حمید</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>0720388619</t>
+          <t>5220146602</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
@@ -1670,35 +1670,35 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>8611040064111640</t>
+          <t>5400050020050462</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>177793</t>
+          <t>840431</t>
         </is>
       </c>
       <c r="G8" s="13" t="n">
-        <v>320000000</v>
+        <v>1700000000</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>1405/07/05</t>
+          <t>1405/08/25</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>21 روز مانده</t>
+          <t>71 روز مانده</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>* صادرات 15 خرداد</t>
+          <t>* صادرات کوي امام هادي</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
@@ -1707,22 +1707,22 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>28996595380</v>
+        <v>50434720000</v>
       </c>
       <c r="N8" s="13" t="n">
-        <v>360000000</v>
+        <v>5332712000</v>
       </c>
       <c r="O8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:42</t>
+          <t>2026-09-06 09:22:32</t>
         </is>
       </c>
       <c r="Q8" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:42 (کد پیگیری: 49685355308538)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:32 (کد پیگیری: 49685355323278)</t>
         </is>
       </c>
     </row>
@@ -1732,10 +1732,14 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>اقاي ضيافتي</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr"/>
+          <t>افشاری قز غاوه سجاد</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0720388619</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -1743,55 +1747,59 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>5783030115225521</t>
+          <t>8611040064111640</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>179687</t>
+          <t>177793</t>
         </is>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1400000000</v>
+        <v>320000000</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>1405/11/10</t>
+          <t>1405/07/05</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>146 روز مانده</t>
+          <t>21 روز مانده</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* صادرات 15 خرداد</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M9" s="12" t="n">
-        <v>0</v>
+        <v>28996595380</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>0</v>
+        <v>360000000</v>
       </c>
       <c r="O9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:21:42</t>
+        </is>
+      </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:42 (کد پیگیری: 49685355308538)</t>
         </is>
       </c>
     </row>
@@ -1801,14 +1809,10 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>امه ليلا كلاه درازي</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>6519917109</t>
-        </is>
-      </c>
+          <t>اقاي ضيافتي</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr"/>
       <c r="D10" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -1816,44 +1820,44 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>2045050027968292</t>
+          <t>5783030115225521</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>233941</t>
+          <t>179687</t>
         </is>
       </c>
       <c r="G10" s="13" t="n">
-        <v>600000000</v>
+        <v>1400000000</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>1405/07/01</t>
+          <t>1405/11/10</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>17 روز مانده</t>
+          <t>146 روز مانده</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>* کشاورزي عبدل اباد فيض اباد</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M10" s="13" t="n">
-        <v>6420000000</v>
+        <v>0</v>
       </c>
       <c r="N10" s="13" t="n">
         <v>0</v>
@@ -1861,14 +1865,10 @@
       <c r="O10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:21:33</t>
-        </is>
-      </c>
+      <c r="P10" s="10" t="inlineStr"/>
       <c r="Q10" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:33 (کد پیگیری: 49685355296282)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -1878,51 +1878,59 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>اميرحسين عليپور</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr"/>
+          <t>امه ليلا كلاه درازي</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>6519917109</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2045050027968292</t>
+        </is>
+      </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>1113333</t>
+          <t>233941</t>
         </is>
       </c>
       <c r="G11" s="12" t="n">
-        <v>2000000000</v>
+        <v>600000000</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>1403/09/01</t>
+          <t>1405/07/01</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>منقضی (654 روز گذشته)</t>
+          <t>17 روز مانده</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>* قر سفته</t>
+          <t>* کشاورزي عبدل اباد فيض اباد</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>سند سفته / فاقد صیاد (معاف)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0</v>
+        <v>6420000000</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
@@ -1930,10 +1938,14 @@
       <c r="O11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:21:33</t>
+        </is>
+      </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>سند تضمینی یا سفته فاقد شناسه ۱۶ رقمی صیاد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:33 (کد پیگیری: 49685355296282)</t>
         </is>
       </c>
     </row>
@@ -1943,45 +1955,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>امين داوري</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>0681855436</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>3572020042035576</t>
-        </is>
-      </c>
+          <t>اميرحسين عليپور</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr"/>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>349378</t>
+          <t>1113333</t>
         </is>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1400000000</v>
+        <v>2000000000</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>1405/07/06</t>
+          <t>1403/09/01</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>22 روز مانده</t>
+          <t>منقضی (654 روز گذشته)</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>* سپه امام خميني</t>
+          <t>* قر سفته</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
@@ -1991,26 +1995,22 @@
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سند سفته / فاقد صیاد (معاف)</t>
         </is>
       </c>
       <c r="M12" s="13" t="n">
-        <v>97789824945</v>
+        <v>0</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>45367735500</v>
+        <v>0</v>
       </c>
       <c r="O12" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:21:44</t>
-        </is>
-      </c>
+      <c r="P12" s="10" t="inlineStr"/>
       <c r="Q12" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:44 (کد پیگیری: 49685355304697)</t>
+          <t>سند تضمینی یا سفته فاقد شناسه ۱۶ رقمی صیاد</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2512020042035577</t>
+          <t>3572020042035576</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>349379</t>
+          <t>349378</t>
         </is>
       </c>
       <c r="G13" s="12" t="n">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>1405/08/06</t>
+          <t>1405/07/06</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>52 روز مانده</t>
+          <t>22 روز مانده</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:18</t>
+          <t>2026-09-06 09:21:44</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:18 (کد پیگیری: 49685355310930)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:44 (کد پیگیری: 49685355304697)</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>8759020042035578</t>
+          <t>2512020042035577</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>349380</t>
+          <t>349379</t>
         </is>
       </c>
       <c r="G14" s="13" t="n">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>1405/09/06</t>
+          <t>1405/08/06</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>82 روز مانده</t>
+          <t>52 روز مانده</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="P14" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:46</t>
+          <t>2026-09-06 09:22:18</t>
         </is>
       </c>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:46 (کد پیگیری: 49685355335081)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:18 (کد پیگیری: 49685355310930)</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>4521020042035579</t>
+          <t>8759020042035578</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>349381</t>
+          <t>349380</t>
         </is>
       </c>
       <c r="G15" s="12" t="n">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>1405/10/06</t>
+          <t>1405/09/06</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>112 روز مانده</t>
+          <t>82 روز مانده</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:22</t>
+          <t>2026-09-06 09:22:46</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:22 (کد پیگیری: 49685355346621)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:46 (کد پیگیری: 49685355335081)</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>باقریان پور جو اد</t>
+          <t>امين داوري</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>0921646003</t>
+          <t>0681855436</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -2266,30 +2266,30 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>8691020116968671</t>
+          <t>4521020042035579</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>623498</t>
+          <t>349381</t>
         </is>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>1405/08/10</t>
+          <t>1405/10/06</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>56 روز مانده</t>
+          <t>112 روز مانده</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>* صادرات مهرآباد 1904281</t>
+          <t>* سپه امام خميني</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="M16" s="13" t="n">
-        <v>94591495000</v>
+        <v>97789824945</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>2827870000</v>
+        <v>45367735500</v>
       </c>
       <c r="O16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:22</t>
+          <t>2026-09-06 09:23:22</t>
         </is>
       </c>
       <c r="Q16" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:22 (کد پیگیری: 49685355318256)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:22 (کد پیگیری: 49685355346621)</t>
         </is>
       </c>
     </row>
@@ -2328,27 +2328,27 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>جواد غفوريان قالي باف</t>
+          <t>باقریان پور جو اد</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>0941314121</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0921646003</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2679040061560087</t>
+          <t>8691020116968671</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>239933</t>
+          <t>623498</t>
         </is>
       </c>
       <c r="G17" s="12" t="n">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>1405/06/03</t>
+          <t>1405/08/10</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>منقضی (12 روز گذشته)</t>
+          <t>56 روز مانده</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>* کشاورزي شريعتي</t>
+          <t>* صادرات مهرآباد 1904281</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -2380,22 +2380,22 @@
         </is>
       </c>
       <c r="M17" s="12" t="n">
-        <v>28682000000</v>
+        <v>94591495000</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>14295000000</v>
+        <v>2827870000</v>
       </c>
       <c r="O17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:03</t>
+          <t>2026-09-06 09:22:22</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:03 (کد پیگیری: 49685355280874)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:22 (کد پیگیری: 49685355318256)</t>
         </is>
       </c>
     </row>
@@ -2413,19 +2413,19 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>7195040061560088</t>
+          <t>2679040061560087</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>239934</t>
+          <t>239933</t>
         </is>
       </c>
       <c r="G18" s="13" t="n">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>1405/07/03</t>
+          <t>1405/06/03</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>19 روز مانده</t>
+          <t>منقضی (12 روز گذشته)</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="P18" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:40</t>
+          <t>2026-09-06 09:21:03</t>
         </is>
       </c>
       <c r="Q18" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:40 (کد پیگیری: 49685355308517)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:03 (کد پیگیری: 49685355280874)</t>
         </is>
       </c>
     </row>
@@ -2490,19 +2490,19 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>6663040061560089</t>
+          <t>7195040061560088</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>239935</t>
+          <t>239934</t>
         </is>
       </c>
       <c r="G19" s="12" t="n">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>1405/08/03</t>
+          <t>1405/07/03</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>49 روز مانده</t>
+          <t>19 روز مانده</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:14</t>
+          <t>2026-09-06 09:21:40</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:14 (کد پیگیری: 49685355312796)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:40 (کد پیگیری: 49685355308517)</t>
         </is>
       </c>
     </row>
@@ -2567,19 +2567,19 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>1422040061560091</t>
+          <t>6663040061560089</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>239937</t>
+          <t>239935</t>
         </is>
       </c>
       <c r="G20" s="13" t="n">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>1405/10/03</t>
+          <t>1405/08/03</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>109 روز مانده</t>
+          <t>49 روز مانده</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="P20" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:19</t>
+          <t>2026-09-06 09:22:14</t>
         </is>
       </c>
       <c r="Q20" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:19 (کد پیگیری: 49685355346604)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:14 (کد پیگیری: 49685355312796)</t>
         </is>
       </c>
     </row>
@@ -2644,19 +2644,19 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>4018040061560092</t>
+          <t>1422040061560091</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>239938</t>
+          <t>239937</t>
         </is>
       </c>
       <c r="G21" s="12" t="n">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>1405/11/03</t>
+          <t>1405/10/03</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>139 روز مانده</t>
+          <t>109 روز مانده</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:37</t>
+          <t>2026-09-06 09:23:19</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:37 (کد پیگیری: 49685355357612)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:19 (کد پیگیری: 49685355346604)</t>
         </is>
       </c>
     </row>
@@ -2721,19 +2721,19 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>3872040061560093</t>
+          <t>4018040061560092</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>239939</t>
+          <t>239938</t>
         </is>
       </c>
       <c r="G22" s="13" t="n">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>1405/12/03</t>
+          <t>1405/11/03</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>169 روز مانده</t>
+          <t>139 روز مانده</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="P22" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:43</t>
+          <t>2026-09-06 09:23:37</t>
         </is>
       </c>
       <c r="Q22" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:43 (کد پیگیری: 49685355342484)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:37 (کد پیگیری: 49685355357612)</t>
         </is>
       </c>
     </row>
@@ -2798,19 +2798,19 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>9179040061560094</t>
+          <t>3872040061560093</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>239940</t>
+          <t>239939</t>
         </is>
       </c>
       <c r="G23" s="12" t="n">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>1406/01/03</t>
+          <t>1405/12/03</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>198 روز مانده</t>
+          <t>169 روز مانده</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:47</t>
+          <t>2026-09-06 09:23:43</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:47 (کد پیگیری: 49685355345990)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:43 (کد پیگیری: 49685355342484)</t>
         </is>
       </c>
     </row>
@@ -2867,12 +2867,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>جواد همتي</t>
+          <t>جواد غفوريان قالي باف</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>0860010198</t>
+          <t>0941314121</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -2882,30 +2882,30 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>7515050006253687</t>
+          <t>9179040061560094</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>734272</t>
+          <t>239940</t>
         </is>
       </c>
       <c r="G24" s="13" t="n">
-        <v>9400000000</v>
+        <v>1000000000</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>1405/06/01</t>
+          <t>1406/01/03</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>منقضی (14 روز گذشته)</t>
+          <t>198 روز مانده</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>* رفاه هاشميه مشهد</t>
+          <t>* کشاورزي شريعتي</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
@@ -2919,22 +2919,22 @@
         </is>
       </c>
       <c r="M24" s="13" t="n">
-        <v>17878097081</v>
+        <v>28682000000</v>
       </c>
       <c r="N24" s="13" t="n">
-        <v>6960472000</v>
+        <v>14295000000</v>
       </c>
       <c r="O24" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:20:59</t>
+          <t>2026-09-06 09:23:47</t>
         </is>
       </c>
       <c r="Q24" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:59 (کد پیگیری: 49685355276391)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:47 (کد پیگیری: 49685355345990)</t>
         </is>
       </c>
     </row>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>حامد نهارداني</t>
+          <t>جواد همتي</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>0780642813</t>
+          <t>0860010198</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -2959,30 +2959,30 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>6896040120076060</t>
+          <t>7515050006253687</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>00769431</t>
+          <t>734272</t>
         </is>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1350000000</v>
+        <v>9400000000</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>1405/07/07</t>
+          <t>1405/06/01</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>23 روز مانده</t>
+          <t>منقضی (14 روز گذشته)</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>* ملت عطا ملک سبزوار</t>
+          <t>* رفاه هاشميه مشهد</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -2996,22 +2996,22 @@
         </is>
       </c>
       <c r="M25" s="12" t="n">
-        <v>172534650000</v>
+        <v>17878097081</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>75010839287</v>
+        <v>6960472000</v>
       </c>
       <c r="O25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:47</t>
+          <t>2026-09-06 09:20:59</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:47 (کد پیگیری: 49685355304731)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:59 (کد پیگیری: 49685355276391)</t>
         </is>
       </c>
     </row>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>9154040120076061</t>
+          <t>6896040120076060</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>00769517</t>
+          <t>00769431</t>
         </is>
       </c>
       <c r="G26" s="13" t="n">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>1405/08/07</t>
+          <t>1405/07/07</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>53 روز مانده</t>
+          <t>23 روز مانده</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="P26" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:21</t>
+          <t>2026-09-06 09:21:47</t>
         </is>
       </c>
       <c r="Q26" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:21 (کد پیگیری: 49685355324524)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:47 (کد پیگیری: 49685355304731)</t>
         </is>
       </c>
     </row>
@@ -3098,45 +3098,45 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>حسين حشمتي</t>
+          <t>حامد نهارداني</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>0933387075</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0780642813</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2380030072556088</t>
+          <t>9154040120076061</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>057751</t>
+          <t>00769517</t>
         </is>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1060000000</v>
+        <v>1350000000</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>1403/12/20</t>
+          <t>1405/08/07</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>منقضی (545 روز گذشته)</t>
+          <t>53 روز مانده</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>* ايران زمين مفتح مشهد</t>
+          <t>* ملت عطا ملک سبزوار</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -3150,22 +3150,22 @@
         </is>
       </c>
       <c r="M27" s="12" t="n">
-        <v>2500000000</v>
+        <v>172534650000</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
+        <v>75010839287</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>56960000000</v>
+        <v>0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:20:50</t>
+          <t>2026-09-06 09:22:21</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:50 (کد پیگیری: 49685355280295)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:21 (کد پیگیری: 49685355324524)</t>
         </is>
       </c>
     </row>
@@ -3175,50 +3175,50 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>حميد مددي</t>
+          <t>حسين حشمتي</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>0943162041</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>0933387075</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>9316030151725989</t>
+          <t>2380030072556088</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>412972</t>
+          <t>057751</t>
         </is>
       </c>
       <c r="G28" s="13" t="n">
-        <v>995000000</v>
+        <v>1060000000</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>1405/06/16</t>
+          <t>1403/12/20</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>سررسید نزدیک (1 روز مانده)</t>
+          <t>منقضی (545 روز گذشته)</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>* سپه بازار رضا</t>
+          <t>* ايران زمين مفتح مشهد</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
@@ -3227,22 +3227,22 @@
         </is>
       </c>
       <c r="M28" s="13" t="n">
-        <v>17294955324</v>
+        <v>2500000000</v>
       </c>
       <c r="N28" s="13" t="n">
-        <v>2371300000</v>
+        <v>0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0</v>
+        <v>56960000000</v>
       </c>
       <c r="P28" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:17</t>
+          <t>2026-09-06 09:20:50</t>
         </is>
       </c>
       <c r="Q28" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:17 (کد پیگیری: 49685355297086)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:50 (کد پیگیری: 49685355280295)</t>
         </is>
       </c>
     </row>
@@ -3267,12 +3267,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2116030151725985</t>
+          <t>9316030151725989</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>412968</t>
+          <t>412972</t>
         </is>
       </c>
       <c r="G29" s="12" t="n">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>1405/09/16</t>
+          <t>1405/06/16</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>92 روز مانده</t>
+          <t>سررسید نزدیک (1 روز مانده)</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:59</t>
+          <t>2026-09-06 09:21:17</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:59 (کد پیگیری: 49685355335727)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:17 (کد پیگیری: 49685355297086)</t>
         </is>
       </c>
     </row>
@@ -3329,41 +3329,45 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>داود رنگ رززاده خراساني</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr"/>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>حميد مددي</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>0943162041</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>3704040137481903</t>
+          <t>2116030151725985</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>415569</t>
+          <t>412968</t>
         </is>
       </c>
       <c r="G30" s="13" t="n">
-        <v>220000000</v>
+        <v>995000000</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>1405/06/27</t>
+          <t>1405/09/16</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>12 روز مانده</t>
+          <t>92 روز مانده</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>* پاسارگاد احمداباد</t>
+          <t>* سپه بازار رضا</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr">
@@ -3373,22 +3377,26 @@
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M30" s="13" t="n">
-        <v>0</v>
+        <v>17294955324</v>
       </c>
       <c r="N30" s="13" t="n">
-        <v>0</v>
+        <v>2371300000</v>
       </c>
       <c r="O30" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="10" t="inlineStr"/>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:22:59</t>
+        </is>
+      </c>
       <c r="Q30" s="11" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:59 (کد پیگیری: 49685355335727)</t>
         </is>
       </c>
     </row>
@@ -3398,45 +3406,41 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>ريحانه روضه خوان</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>0941183149</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>داود رنگ رززاده خراساني</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2987040018207050</t>
+          <t>3704040137481903</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>284935</t>
+          <t>415569</t>
         </is>
       </c>
       <c r="G31" s="12" t="n">
-        <v>2200000000</v>
+        <v>220000000</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>1405/07/25</t>
+          <t>1405/06/27</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>41 روز مانده</t>
+          <t>12 روز مانده</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي ب سازمان آب 8554</t>
+          <t>* پاسارگاد احمداباد</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -3446,26 +3450,22 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M31" s="12" t="n">
-        <v>32595000000</v>
+        <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1300000000</v>
+        <v>0</v>
       </c>
       <c r="O31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:02</t>
-        </is>
-      </c>
+      <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:02 (کد پیگیری: 49685355310724)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -3490,12 +3490,12 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>1954040018207052</t>
+          <t>2987040018207050</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>284937</t>
+          <t>284935</t>
         </is>
       </c>
       <c r="G32" s="13" t="n">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>1405/09/25</t>
+          <t>1405/07/25</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>101 روز مانده</t>
+          <t>41 روز مانده</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="P32" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:04</t>
+          <t>2026-09-06 09:22:02</t>
         </is>
       </c>
       <c r="Q32" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:04 (کد پیگیری: 49685355336236)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:02 (کد پیگیری: 49685355310724)</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>9108040018207053</t>
+          <t>1954040018207052</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>284938</t>
+          <t>284937</t>
         </is>
       </c>
       <c r="G33" s="12" t="n">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>1405/10/25</t>
+          <t>1405/09/25</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>131 روز مانده</t>
+          <t>101 روز مانده</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:29</t>
+          <t>2026-09-06 09:23:04</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:29 (کد پیگیری: 49685355348704)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:04 (کد پیگیری: 49685355336236)</t>
         </is>
       </c>
     </row>
@@ -3629,50 +3629,50 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>زهرا بهرامي پويا</t>
+          <t>ريحانه روضه خوان</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>0927624011</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0941183149</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>4317050049334681</t>
+          <t>9108040018207053</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>2999903</t>
+          <t>284938</t>
         </is>
       </c>
       <c r="G34" s="13" t="n">
-        <v>15000000000</v>
+        <v>2200000000</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>1405/07/25</t>
+          <t>1405/10/25</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>41 روز مانده</t>
+          <t>131 روز مانده</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>* کشاورزي امام رضا</t>
+          <t>* بانک ملي ب سازمان آب 8554</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>فاطمه زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
@@ -3681,22 +3681,22 @@
         </is>
       </c>
       <c r="M34" s="13" t="n">
-        <v>338830000000</v>
+        <v>32595000000</v>
       </c>
       <c r="N34" s="13" t="n">
-        <v>11800000000</v>
+        <v>1300000000</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>12300000000</v>
+        <v>0</v>
       </c>
       <c r="P34" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 18:54:14</t>
+          <t>2026-09-06 09:23:29</t>
         </is>
       </c>
       <c r="Q34" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 18:54:14 (کد پیگیری: 49686363251893)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:29 (کد پیگیری: 49685355348704)</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3706,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>زو ار وحید</t>
+          <t>زهرا بهرامي پويا</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>6430003159</t>
+          <t>0927624011</t>
         </is>
       </c>
       <c r="D35" s="18" t="inlineStr">
@@ -3721,35 +3721,35 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>7740040056179003</t>
+          <t>4317050049334681</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>824586</t>
+          <t>2999903</t>
         </is>
       </c>
       <c r="G35" s="12" t="n">
-        <v>2670000000</v>
+        <v>15000000000</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>1405/06/16</t>
+          <t>1405/07/25</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>سررسید نزدیک (1 روز مانده)</t>
+          <t>41 روز مانده</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>* صادرات سيدي</t>
+          <t>* کشاورزي امام رضا</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>فاطمه زمانزاده</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -3758,22 +3758,22 @@
         </is>
       </c>
       <c r="M35" s="12" t="n">
-        <v>294823500000</v>
+        <v>338830000000</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>152016000000</v>
+        <v>11800000000</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>46080000000</v>
+        <v>12300000000</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:16</t>
+          <t>2026-09-06 18:54:14</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:16 (کد پیگیری: 49685355280999)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 18:54:14 (کد پیگیری: 49686363251893)</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>2480040056179004</t>
+          <t>7740040056179003</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>824587</t>
+          <t>824586</t>
         </is>
       </c>
       <c r="G36" s="13" t="n">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>1405/07/16</t>
+          <t>1405/06/16</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>32 روز مانده</t>
+          <t>سررسید نزدیک (1 روز مانده)</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="K36" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="P36" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:54</t>
+          <t>2026-09-06 09:21:16</t>
         </is>
       </c>
       <c r="Q36" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:54 (کد پیگیری: 49685355305264)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:16 (کد پیگیری: 49685355280999)</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3875,12 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>4409040056178993</t>
+          <t>2480040056179004</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>824576</t>
+          <t>824587</t>
         </is>
       </c>
       <c r="G37" s="12" t="n">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>1405/10/16</t>
+          <t>1405/07/16</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>122 روز مانده</t>
+          <t>32 روز مانده</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:25</t>
+          <t>2026-09-06 09:21:54</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:25 (کد پیگیری: 49685355351542)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:54 (کد پیگیری: 49685355305264)</t>
         </is>
       </c>
     </row>
@@ -3952,12 +3952,12 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>1668040056178994</t>
+          <t>9330040056179006</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>824577</t>
+          <t>824589</t>
         </is>
       </c>
       <c r="G38" s="13" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>1405/11/16</t>
+          <t>1405/09/16</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>152 روز مانده</t>
+          <t>92 روز مانده</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="P38" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:40</t>
+          <t>2026-09-06 09:22:58</t>
         </is>
       </c>
       <c r="Q38" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:40 (کد پیگیری: 49685355351224)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:58 (کد پیگیری: 49685355335702)</t>
         </is>
       </c>
     </row>
@@ -4014,46 +4014,50 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>سمانه صيادقشه توت</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr"/>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>زو ار وحید</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>6430003159</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>9377040091817634</t>
+          <t>4409040056178993</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>685158</t>
+          <t>824576</t>
         </is>
       </c>
       <c r="G39" s="12" t="n">
-        <v>360000000</v>
+        <v>2670000000</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>1405/08/30</t>
+          <t>1405/10/16</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>76 روز مانده</t>
+          <t>122 روز مانده</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>* رفاه مفتح</t>
+          <t>* صادرات سيدي</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -4062,22 +4066,22 @@
         </is>
       </c>
       <c r="M39" s="12" t="n">
-        <v>18287300000</v>
+        <v>294823500000</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>50000000</v>
+        <v>152016000000</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>0</v>
+        <v>46080000000</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:36</t>
+          <t>2026-09-06 09:23:25</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:36 (کد پیگیری: 49685355318403)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:25 (کد پیگیری: 49685355351542)</t>
         </is>
       </c>
     </row>
@@ -4087,45 +4091,45 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>سميرا كارآزمامارشك</t>
+          <t>زو ار وحید</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>0931575941</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>6430003159</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>1509040118622468</t>
+          <t>1668040056178994</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>795571</t>
+          <t>824577</t>
         </is>
       </c>
       <c r="G40" s="13" t="n">
-        <v>570000000</v>
+        <v>2670000000</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>1405/08/15</t>
+          <t>1405/11/16</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>61 روز مانده</t>
+          <t>152 روز مانده</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>* رفاه بيمارستان امام رضا کد 1301111</t>
+          <t>* صادرات سيدي</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
@@ -4139,22 +4143,22 @@
         </is>
       </c>
       <c r="M40" s="13" t="n">
-        <v>56196200000</v>
+        <v>294823500000</v>
       </c>
       <c r="N40" s="13" t="n">
-        <v>20803880000</v>
+        <v>152016000000</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>0</v>
+        <v>46080000000</v>
       </c>
       <c r="P40" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:25</t>
+          <t>2026-09-06 09:23:40</t>
         </is>
       </c>
       <c r="Q40" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:25 (کد پیگیری: 49685355320730)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:40 (کد پیگیری: 49685355351224)</t>
         </is>
       </c>
     </row>
@@ -4164,14 +4168,10 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>سميرا كارآزمامارشك</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>0931575941</t>
-        </is>
-      </c>
+          <t>سمانه صيادقشه توت</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -4179,35 +4179,35 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>5938050026755149</t>
+          <t>9377040091817634</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>533556</t>
+          <t>685158</t>
         </is>
       </c>
       <c r="G41" s="12" t="n">
-        <v>2950000000</v>
+        <v>360000000</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>1405/10/05</t>
+          <t>1405/08/30</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>111 روز مانده</t>
+          <t>76 روز مانده</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>* رفاه بيمارستان امام رضا</t>
+          <t>* رفاه مفتح</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -4216,22 +4216,22 @@
         </is>
       </c>
       <c r="M41" s="12" t="n">
-        <v>56196200000</v>
+        <v>18287300000</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>20803880000</v>
+        <v>50000000</v>
       </c>
       <c r="O41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 19:14:03</t>
+          <t>2026-09-06 09:22:36</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363364447)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:36 (کد پیگیری: 49685355318403)</t>
         </is>
       </c>
     </row>
@@ -4241,45 +4241,45 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>سيدجمال موسوي علي آبادي</t>
+          <t>سميرا كارآزمامارشك</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>6510002647</t>
-        </is>
-      </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0931575941</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>9147040164254882</t>
+          <t>1509040118622468</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>400697</t>
+          <t>795571</t>
         </is>
       </c>
       <c r="G42" s="13" t="n">
-        <v>1500000000</v>
+        <v>570000000</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>1405/05/28</t>
+          <t>1405/08/15</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>منقضی (18 روز گذشته)</t>
+          <t>61 روز مانده</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>* قرض الحسنه رسالت بانکداري اجتماعي</t>
+          <t>* رفاه بيمارستان امام رضا کد 1301111</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr">
@@ -4289,22 +4289,26 @@
       </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M42" s="13" t="n">
-        <v>0</v>
+        <v>56196200000</v>
       </c>
       <c r="N42" s="13" t="n">
-        <v>0</v>
+        <v>20803880000</v>
       </c>
       <c r="O42" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P42" s="10" t="inlineStr"/>
+      <c r="P42" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:22:25</t>
+        </is>
+      </c>
       <c r="Q42" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/05/28 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:25 (کد پیگیری: 49685355320730)</t>
         </is>
       </c>
     </row>
@@ -4314,74 +4318,74 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>سيدجمال موسوي علي آبادي</t>
+          <t>سميرا كارآزمامارشك</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>6510002647</t>
-        </is>
-      </c>
-      <c r="D43" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0931575941</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>4946040164254881</t>
+          <t>5938050026755149</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>400696</t>
+          <t>533556</t>
         </is>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1500000000</v>
+        <v>2950000000</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>1405/06/12</t>
+          <t>1405/10/05</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>منقضی (3 روز گذشته)</t>
+          <t>111 روز مانده</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>* قرض الحسنه رسالت بانکداري اجتماعيي</t>
+          <t>* رفاه بيمارستان امام رضا</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M43" s="12" t="n">
-        <v>35090000000</v>
+        <v>56196200000</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>14938000000</v>
+        <v>20803880000</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>2800000000</v>
+        <v>0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 08:43:51</t>
+          <t>2026-09-06 19:14:03</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:43:51) (کد پیگیری قبلی: 49682942030012)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363364447)</t>
         </is>
       </c>
     </row>
@@ -4391,45 +4395,45 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>سيدمهدي راستگو</t>
+          <t>سيدجمال موسوي علي آبادي</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>5229804221</t>
-        </is>
-      </c>
-      <c r="D44" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>6510002647</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>1349040184813907</t>
+          <t>9147040164254882</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>33878626</t>
+          <t>400697</t>
         </is>
       </c>
       <c r="G44" s="13" t="n">
-        <v>2620000000</v>
+        <v>1500000000</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>1405/07/01</t>
+          <t>1405/05/28</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>17 روز مانده</t>
+          <t>منقضی (18 روز گذشته)</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>* ملت دانش اموز</t>
+          <t>* قرض الحسنه رسالت بانکداري اجتماعي</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
@@ -4439,11 +4443,11 @@
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M44" s="13" t="n">
-        <v>12980000000</v>
+        <v>0</v>
       </c>
       <c r="N44" s="13" t="n">
         <v>0</v>
@@ -4451,14 +4455,10 @@
       <c r="O44" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P44" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:21:32</t>
-        </is>
-      </c>
+      <c r="P44" s="10" t="inlineStr"/>
       <c r="Q44" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:32 (کد پیگیری: 49685355303590)</t>
+          <t>سررسید چک در تاریخ 1405/05/28 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -4468,74 +4468,74 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>سيدمهدي راستگو</t>
+          <t>سيدجمال موسوي علي آبادي</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>5229804221</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>6510002647</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2400040184813904</t>
+          <t>4946040164254881</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>33878317</t>
+          <t>400696</t>
         </is>
       </c>
       <c r="G45" s="12" t="n">
-        <v>2620000000</v>
+        <v>1500000000</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/06/12</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>47 روز مانده</t>
+          <t>منقضی (3 روز گذشته)</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>* ملت دانش اموز</t>
+          <t>* قرض الحسنه رسالت بانکداري اجتماعيي</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M45" s="12" t="n">
-        <v>12980000000</v>
+        <v>35090000000</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>0</v>
+        <v>14938000000</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>0</v>
+        <v>2800000000</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:11</t>
+          <t>2026-09-05 08:43:51</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:11 (کد پیگیری: 49685355310284)</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:43:51) (کد پیگیری قبلی: 49682942030012)</t>
         </is>
       </c>
     </row>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>2644040184813905</t>
+          <t>1349040184813907</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>33878454</t>
+          <t>33878626</t>
         </is>
       </c>
       <c r="G46" s="13" t="n">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>1405/09/01</t>
+          <t>1405/07/01</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>77 روز مانده</t>
+          <t>17 روز مانده</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="P46" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:39</t>
+          <t>2026-09-06 09:21:32</t>
         </is>
       </c>
       <c r="Q46" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:39 (کد پیگیری: 49685355325246)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:32 (کد پیگیری: 49685355303590)</t>
         </is>
       </c>
     </row>
@@ -4637,12 +4637,12 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>4356040184813906</t>
+          <t>2400040184813904</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>33878540</t>
+          <t>33878317</t>
         </is>
       </c>
       <c r="G47" s="12" t="n">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>1405/10/01</t>
+          <t>1405/08/01</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>107 روز مانده</t>
+          <t>47 روز مانده</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:14</t>
+          <t>2026-09-06 09:22:11</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:14 (کد پیگیری: 49685355340289)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:11 (کد پیگیری: 49685355310284)</t>
         </is>
       </c>
     </row>
@@ -4699,45 +4699,45 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>صاحب چک فريمان (۰۹۲۴۰۲۰۸۶۵)</t>
+          <t>سيدمهدي راستگو</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>0924020865</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>5229804221</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>1907030071639288</t>
+          <t>2644040184813905</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>804984</t>
+          <t>33878454</t>
         </is>
       </c>
       <c r="G48" s="13" t="n">
-        <v>1380000000</v>
+        <v>2620000000</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>1405/06/10</t>
+          <t>1405/09/01</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>منقضی (5 روز گذشته)</t>
+          <t>77 روز مانده</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>* سپه امام رضا فريمان</t>
+          <t>* ملت دانش اموز</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
@@ -4747,26 +4747,26 @@
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M48" s="13" t="n">
-        <v>91680000000</v>
+        <v>12980000000</v>
       </c>
       <c r="N48" s="13" t="n">
-        <v>43715000000</v>
+        <v>0</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>21630000000</v>
+        <v>0</v>
       </c>
       <c r="P48" s="10" t="inlineStr">
         <is>
-          <t>2026-09-05 08:42:05</t>
+          <t>2026-09-06 09:22:39</t>
         </is>
       </c>
       <c r="Q48" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:42:05) (کد پیگیری قبلی: 49682941988821)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:39 (کد پیگیری: 49685355325246)</t>
         </is>
       </c>
     </row>
@@ -4776,59 +4776,59 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>صاحب چک فريمان (۰۹۲۴۰۲۰۸۶۵)</t>
+          <t>سيدمهدي راستگو</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>0924020865</t>
-        </is>
-      </c>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>5229804221</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>9910030071163929</t>
+          <t>4356040184813906</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>804987</t>
+          <t>33878540</t>
         </is>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1380000000</v>
+        <v>2620000000</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>1405/09/10</t>
+          <t>1405/10/01</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>86 روز مانده</t>
+          <t>107 روز مانده</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>* سپه امام رضا فريمان</t>
+          <t>* ملت دانش اموز</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0</v>
+        <v>12980000000</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>0</v>
@@ -4836,10 +4836,14 @@
       <c r="O49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P49" s="6" t="inlineStr"/>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:23:14</t>
+        </is>
+      </c>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:14 (کد پیگیری: 49685355340289)</t>
         </is>
       </c>
     </row>
@@ -4849,45 +4853,45 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>طاهره حسني</t>
+          <t>صاحب چک فريمان (۰۹۲۴۰۲۰۸۶۵)</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>5228890297</t>
-        </is>
-      </c>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>0924020865</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>1748040121634559</t>
+          <t>1907030071639288</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>189764</t>
+          <t>804984</t>
         </is>
       </c>
       <c r="G50" s="13" t="n">
-        <v>3100000000</v>
+        <v>1380000000</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>1405/06/05</t>
+          <t>1405/06/10</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>منقضی (10 روز گذشته)</t>
+          <t>منقضی (5 روز گذشته)</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي</t>
+          <t>* سپه امام رضا فريمان</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
@@ -4897,22 +4901,26 @@
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M50" s="13" t="n">
-        <v>0</v>
+        <v>91680000000</v>
       </c>
       <c r="N50" s="13" t="n">
-        <v>0</v>
+        <v>43715000000</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="10" t="inlineStr"/>
+        <v>21630000000</v>
+      </c>
+      <c r="P50" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-05 08:42:05</t>
+        </is>
+      </c>
       <c r="Q50" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:42:05) (کد پیگیری قبلی: 49682941988821)</t>
         </is>
       </c>
     </row>
@@ -4922,45 +4930,45 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>طاهره حسني</t>
+          <t>صاحب چک فريمان (۰۹۲۴۰۲۰۸۶۵)</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>5228890297</t>
-        </is>
-      </c>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>0924020865</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2240040121634560</t>
+          <t>9910030071163929</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>189765</t>
+          <t>804987</t>
         </is>
       </c>
       <c r="G51" s="12" t="n">
-        <v>3100000000</v>
+        <v>1380000000</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>1405/07/05</t>
+          <t>1405/09/10</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>21 روز مانده</t>
+          <t>86 روز مانده</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي</t>
+          <t>* سپه امام رضا فريمان</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
@@ -4970,26 +4978,22 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M51" s="12" t="n">
-        <v>145613735000</v>
+        <v>0</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>59466770010</v>
+        <v>0</v>
       </c>
       <c r="O51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-05 08:46:58</t>
-        </is>
-      </c>
+      <c r="P51" s="6" t="inlineStr"/>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:58) (کد پیگیری قبلی: 49682942078736)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5018,12 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>4962040121634561</t>
+          <t>1748040121634559</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>189766</t>
+          <t>189764</t>
         </is>
       </c>
       <c r="G52" s="13" t="n">
@@ -5027,12 +5031,12 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>1405/08/05</t>
+          <t>1405/06/05</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>51 روز مانده</t>
+          <t>منقضی (10 روز گذشته)</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
@@ -5047,26 +5051,22 @@
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M52" s="13" t="n">
-        <v>145613735000</v>
+        <v>0</v>
       </c>
       <c r="N52" s="13" t="n">
-        <v>59466770010</v>
+        <v>0</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P52" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:15</t>
-        </is>
-      </c>
+      <c r="P52" s="10" t="inlineStr"/>
       <c r="Q52" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:15 (کد پیگیری: 49685355321656)</t>
+          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -5091,12 +5091,12 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2770040121634562</t>
+          <t>2240040121634560</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>189767</t>
+          <t>189765</t>
         </is>
       </c>
       <c r="G53" s="12" t="n">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>1405/09/05</t>
+          <t>1405/07/05</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>81 روز مانده</t>
+          <t>21 روز مانده</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M53" s="12" t="n">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:45</t>
+          <t>2026-09-05 08:46:58</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:45 (کد پیگیری: 49685355335056)</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:58) (کد پیگیری قبلی: 49682942078736)</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>1120040121634563</t>
+          <t>4962040121634561</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>189768</t>
+          <t>189766</t>
         </is>
       </c>
       <c r="G54" s="13" t="n">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>1406/08/05</t>
+          <t>1405/08/05</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>416 روز مانده</t>
+          <t>51 روز مانده</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="P54" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:24:02</t>
+          <t>2026-09-06 09:22:15</t>
         </is>
       </c>
       <c r="Q54" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:24:02 (کد پیگیری: 49685355362164)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:15 (کد پیگیری: 49685355321656)</t>
         </is>
       </c>
     </row>
@@ -5230,45 +5230,45 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>عباس مقنی</t>
+          <t>طاهره حسني</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>0922030936</t>
-        </is>
-      </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>5228890297</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>9700040200262950</t>
+          <t>2770040121634562</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>695631</t>
+          <t>189767</t>
         </is>
       </c>
       <c r="G55" s="12" t="n">
-        <v>7500000000</v>
+        <v>3100000000</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>1405/05/30</t>
+          <t>1405/09/05</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>منقضی (16 روز گذشته)</t>
+          <t>81 روز مانده</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>* شهر ميدان راهنمايي مشهد</t>
+          <t>* بانک ملي کوي المهدي</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
@@ -5282,22 +5282,22 @@
         </is>
       </c>
       <c r="M55" s="12" t="n">
-        <v>46230000000</v>
+        <v>145613735000</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>18135000000</v>
+        <v>59466770010</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>12800000000</v>
+        <v>0</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:20:56</t>
+          <t>2026-09-06 09:22:45</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:56 (کد پیگیری: 49685355290024)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:45 (کد پیگیری: 49685355335056)</t>
         </is>
       </c>
     </row>
@@ -5307,45 +5307,45 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>عباس مقنی</t>
+          <t>طاهره حسني</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>0922030936</t>
-        </is>
-      </c>
-      <c r="D56" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>5228890297</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>5560050044994051</t>
+          <t>1120040121634563</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>902051</t>
+          <t>189768</t>
         </is>
       </c>
       <c r="G56" s="13" t="n">
-        <v>6200000000</v>
+        <v>3100000000</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>1405/06/10</t>
+          <t>1406/08/05</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>منقضی (5 روز گذشته)</t>
+          <t>416 روز مانده</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>* سپه بلوار فرودگاه</t>
+          <t>* بانک ملي کوي المهدي</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
@@ -5355,26 +5355,26 @@
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M56" s="13" t="n">
-        <v>235323000000</v>
+        <v>145613735000</v>
       </c>
       <c r="N56" s="13" t="n">
-        <v>30402825000</v>
+        <v>59466770010</v>
       </c>
       <c r="O56" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:51:57</t>
+          <t>2026-09-06 09:24:02</t>
         </is>
       </c>
       <c r="Q56" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-08-28 20:51:57) (کد پیگیری قبلی: 49664982347170)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:24:02 (کد پیگیری: 49685355362164)</t>
         </is>
       </c>
     </row>
@@ -5392,37 +5392,37 @@
           <t>0922030936</t>
         </is>
       </c>
-      <c r="D57" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>9515050044994052</t>
+          <t>5560050044994051</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>902052</t>
+          <t>902051</t>
         </is>
       </c>
       <c r="G57" s="12" t="n">
-        <v>6800000000</v>
+        <v>6200000000</v>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>1405/08/05</t>
+          <t>1405/06/10</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>51 روز مانده</t>
+          <t>منقضی (5 روز گذشته)</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>* سپه بلوار فرودگاه مشهد</t>
+          <t>* سپه بلوار فرودگاه</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
@@ -5432,11 +5432,11 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M57" s="12" t="n">
-        <v>224823000000</v>
+        <v>235323000000</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>30402825000</v>
@@ -5446,12 +5446,12 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:16</t>
+          <t>2026-08-28 20:51:57</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:16 (کد پیگیری: 49685355321681)</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-08-28 20:51:57) (کد پیگیری قبلی: 49664982347170)</t>
         </is>
       </c>
     </row>
@@ -5469,37 +5469,37 @@
           <t>0922030936</t>
         </is>
       </c>
-      <c r="D58" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>8940050044994059</t>
+          <t>4204010168700706</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>902059</t>
+          <t>076149</t>
         </is>
       </c>
       <c r="G58" s="13" t="n">
-        <v>17800000000</v>
+        <v>11520000000</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>1405/12/15</t>
+          <t>1405/07/25</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>181 روز مانده</t>
+          <t>41 روز مانده</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>* سپه بلوار فرودگاه مشهد</t>
+          <t>* صادرات شهرک صنعتي طرق</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="P58" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:44</t>
+          <t>2026-09-06 09:22:06</t>
         </is>
       </c>
       <c r="Q58" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:44 (کد پیگیری: 49685355345947)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:06 (کد پیگیری: 49685355308315)</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>عطاری ید اله</t>
+          <t>عباس مقنی</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>2298907366</t>
+          <t>0922030936</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -5553,30 +5553,30 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2011030010355250</t>
+          <t>9515050044994052</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>810231</t>
+          <t>902052</t>
         </is>
       </c>
       <c r="G59" s="12" t="n">
-        <v>2000000000</v>
+        <v>6800000000</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>1405/06/02</t>
+          <t>1405/08/05</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>منقضی (13 روز گذشته)</t>
+          <t>51 روز مانده</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>* صادرات صفاشم</t>
+          <t>* سپه بلوار فرودگاه مشهد</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
@@ -5586,22 +5586,26 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0</v>
+        <v>224823000000</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
+        <v>30402825000</v>
       </c>
       <c r="O59" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P59" s="6" t="inlineStr"/>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:22:16</t>
+        </is>
+      </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/02 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:16 (کد پیگیری: 49685355321681)</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5615,12 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>عطاری ید اله</t>
+          <t>عباس مقنی</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>2298907366</t>
+          <t>0922030936</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr">
@@ -5626,30 +5630,30 @@
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>8509030010355251</t>
+          <t>8940050044994059</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>810232</t>
+          <t>902059</t>
         </is>
       </c>
       <c r="G60" s="13" t="n">
-        <v>2000000000</v>
+        <v>17800000000</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>1405/07/02</t>
+          <t>1405/12/15</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>18 روز مانده</t>
+          <t>181 روز مانده</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>* صادرات صفاشم</t>
+          <t>* سپه بلوار فرودگاه مشهد</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
@@ -5663,22 +5667,22 @@
         </is>
       </c>
       <c r="M60" s="13" t="n">
-        <v>28000000000</v>
+        <v>224823000000</v>
       </c>
       <c r="N60" s="13" t="n">
-        <v>240000000</v>
+        <v>30402825000</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:39</t>
+          <t>2026-09-06 09:23:44</t>
         </is>
       </c>
       <c r="Q60" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:39 (کد پیگیری: 49685355295883)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:44 (کد پیگیری: 49685355345947)</t>
         </is>
       </c>
     </row>
@@ -5703,12 +5707,12 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>5533030010355252</t>
+          <t>2011030010355250</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>810233</t>
+          <t>810231</t>
         </is>
       </c>
       <c r="G61" s="12" t="n">
@@ -5716,12 +5720,12 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>1405/08/02</t>
+          <t>1405/06/02</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>48 روز مانده</t>
+          <t>منقضی (13 روز گذشته)</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
@@ -5736,26 +5740,22 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M61" s="12" t="n">
-        <v>28000000000</v>
+        <v>0</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>240000000</v>
+        <v>0</v>
       </c>
       <c r="O61" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:13</t>
-        </is>
-      </c>
+      <c r="P61" s="6" t="inlineStr"/>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:13 (کد پیگیری: 49685355317164)</t>
+          <t>سررسید چک در تاریخ 1405/06/02 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -5780,12 +5780,12 @@
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>4680030010355253</t>
+          <t>8509030010355251</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>810234</t>
+          <t>810232</t>
         </is>
       </c>
       <c r="G62" s="13" t="n">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>1405/09/02</t>
+          <t>1405/07/02</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>78 روز مانده</t>
+          <t>18 روز مانده</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="P62" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:42</t>
+          <t>2026-09-06 09:21:39</t>
         </is>
       </c>
       <c r="Q62" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:42 (کد پیگیری: 49685355330603)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:39 (کد پیگیری: 49685355295883)</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>3201030010355254</t>
+          <t>5533030010355252</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>810235</t>
+          <t>810233</t>
         </is>
       </c>
       <c r="G63" s="12" t="n">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>1405/10/02</t>
+          <t>1405/08/02</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>108 روز مانده</t>
+          <t>48 روز مانده</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:18</t>
+          <t>2026-09-06 09:22:13</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:18 (کد پیگیری: 49685355337378)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:13 (کد پیگیری: 49685355317164)</t>
         </is>
       </c>
     </row>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>9379030010355255</t>
+          <t>4680030010355253</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>810236</t>
+          <t>810234</t>
         </is>
       </c>
       <c r="G64" s="13" t="n">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>1405/11/02</t>
+          <t>1405/09/02</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>138 روز مانده</t>
+          <t>78 روز مانده</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="P64" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:36</t>
+          <t>2026-09-06 09:22:42</t>
         </is>
       </c>
       <c r="Q64" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:36 (کد پیگیری: 49685355342412)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:42 (کد پیگیری: 49685355330603)</t>
         </is>
       </c>
     </row>
@@ -6011,12 +6011,12 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>6144030010355257</t>
+          <t>3201030010355254</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>810238</t>
+          <t>810235</t>
         </is>
       </c>
       <c r="G65" s="12" t="n">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>1406/01/02</t>
+          <t>1405/10/02</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>197 روز مانده</t>
+          <t>108 روز مانده</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:46</t>
+          <t>2026-09-06 09:23:18</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:46 (کد پیگیری: 49685355351800)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:18 (کد پیگیری: 49685355337378)</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>3090030010355258</t>
+          <t>9379030010355255</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>810239</t>
+          <t>810236</t>
         </is>
       </c>
       <c r="G66" s="13" t="n">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>1406/02/02</t>
+          <t>1405/11/02</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>228 روز مانده</t>
+          <t>138 روز مانده</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="P66" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:49</t>
+          <t>2026-09-06 09:23:36</t>
         </is>
       </c>
       <c r="Q66" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:49 (کد پیگیری: 49685355351842)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:36 (کد پیگیری: 49685355342412)</t>
         </is>
       </c>
     </row>
@@ -6165,12 +6165,12 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>7644030010355259</t>
+          <t>6144030010355257</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>810240</t>
+          <t>810238</t>
         </is>
       </c>
       <c r="G67" s="12" t="n">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>1406/03/02</t>
+          <t>1406/01/02</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>259 روز مانده</t>
+          <t>197 روز مانده</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:50</t>
+          <t>2026-09-06 09:23:46</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:50 (کد پیگیری: 49685355359143)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:46 (کد پیگیری: 49685355351800)</t>
         </is>
       </c>
     </row>
@@ -6242,12 +6242,12 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>7525030010355260</t>
+          <t>3090030010355258</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>810241</t>
+          <t>810239</t>
         </is>
       </c>
       <c r="G68" s="13" t="n">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>1406/04/02</t>
+          <t>1406/02/02</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>290 روز مانده</t>
+          <t>228 روز مانده</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="P68" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:51</t>
+          <t>2026-09-06 09:23:49</t>
         </is>
       </c>
       <c r="Q68" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:51 (کد پیگیری: 49685355356744)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:49 (کد پیگیری: 49685355351842)</t>
         </is>
       </c>
     </row>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>9793030010355261</t>
+          <t>7644030010355259</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>810242</t>
+          <t>810240</t>
         </is>
       </c>
       <c r="G69" s="12" t="n">
@@ -6332,12 +6332,12 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>1406/05/02</t>
+          <t>1406/03/02</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>321 روز مانده</t>
+          <t>259 روز مانده</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 19:14:03</t>
+          <t>2026-09-06 09:23:50</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363374741)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:50 (کد پیگیری: 49685355359143)</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>6392030010355262</t>
+          <t>7525030010355260</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>810243</t>
+          <t>810241</t>
         </is>
       </c>
       <c r="G70" s="13" t="n">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>1406/06/02</t>
+          <t>1406/04/02</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>352 روز مانده</t>
+          <t>290 روز مانده</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="K70" s="11" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L70" s="11" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="P70" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 19:14:03</t>
+          <t>2026-09-06 09:23:51</t>
         </is>
       </c>
       <c r="Q70" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363377638)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:51 (کد پیگیری: 49685355356744)</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>عقيل نرمكي</t>
+          <t>عطاری ید اله</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>0920541526</t>
+          <t>2298907366</t>
         </is>
       </c>
       <c r="D71" s="19" t="inlineStr">
@@ -6473,55 +6473,59 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>5561040153416463</t>
+          <t>9793030010355261</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>030616</t>
+          <t>810242</t>
         </is>
       </c>
       <c r="G71" s="12" t="n">
-        <v>1160000000</v>
+        <v>2000000000</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>1405/06/06</t>
+          <t>1406/05/02</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>منقضی (9 روز گذشته)</t>
+          <t>321 روز مانده</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>* سپه سيدي مشهد</t>
+          <t>* صادرات صفاشم</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0</v>
+        <v>28000000000</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
+        <v>240000000</v>
       </c>
       <c r="O71" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P71" s="6" t="inlineStr"/>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 19:14:03</t>
+        </is>
+      </c>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/06 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363374741)</t>
         </is>
       </c>
     </row>
@@ -6531,12 +6535,12 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>عقيل نرمكي</t>
+          <t>عطاری ید اله</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>0920541526</t>
+          <t>2298907366</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
@@ -6546,35 +6550,35 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>5320040153416464</t>
+          <t>6392030010355262</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>030617</t>
+          <t>810243</t>
         </is>
       </c>
       <c r="G72" s="13" t="n">
-        <v>1160000000</v>
+        <v>2000000000</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>1405/07/06</t>
+          <t>1406/06/02</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>22 روز مانده</t>
+          <t>352 روز مانده</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>* سپه سيدي مشهد</t>
+          <t>* صادرات صفاشم</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
@@ -6583,22 +6587,22 @@
         </is>
       </c>
       <c r="M72" s="13" t="n">
-        <v>61089499998</v>
+        <v>28000000000</v>
       </c>
       <c r="N72" s="13" t="n">
-        <v>1018900000</v>
+        <v>240000000</v>
       </c>
       <c r="O72" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:45</t>
+          <t>2026-09-06 19:14:03</t>
         </is>
       </c>
       <c r="Q72" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:45 (کد پیگیری: 49685355304716)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363377638)</t>
         </is>
       </c>
     </row>
@@ -6623,12 +6627,12 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>3478040153416465</t>
+          <t>5561040153416463</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>030618</t>
+          <t>030616</t>
         </is>
       </c>
       <c r="G73" s="12" t="n">
@@ -6636,12 +6640,12 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>1405/08/06</t>
+          <t>1405/06/06</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>52 روز مانده</t>
+          <t>منقضی (9 روز گذشته)</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
@@ -6656,26 +6660,22 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M73" s="12" t="n">
-        <v>61089499998</v>
+        <v>0</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1018900000</v>
+        <v>0</v>
       </c>
       <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P73" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:19</t>
-        </is>
-      </c>
+      <c r="P73" s="6" t="inlineStr"/>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:19 (کد پیگیری: 49685355310375)</t>
+          <t>سررسید چک در تاریخ 1405/06/06 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>2610040153416467</t>
+          <t>5320040153416464</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>030620</t>
+          <t>030617</t>
         </is>
       </c>
       <c r="G74" s="13" t="n">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>1405/10/06</t>
+          <t>1405/07/06</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>112 روز مانده</t>
+          <t>22 روز مانده</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="P74" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:23</t>
+          <t>2026-09-06 09:21:45</t>
         </is>
       </c>
       <c r="Q74" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:23 (کد پیگیری: 49685355339937)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:45 (کد پیگیری: 49685355304716)</t>
         </is>
       </c>
     </row>
@@ -6762,10 +6762,14 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>عليرضا ضرغام مقدم</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr"/>
+          <t>عقيل نرمكي</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>0920541526</t>
+        </is>
+      </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -6773,30 +6777,30 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>7283030156765780</t>
+          <t>3478040153416465</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>444417</t>
+          <t>030618</t>
         </is>
       </c>
       <c r="G75" s="12" t="n">
-        <v>350000000</v>
+        <v>1160000000</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>1405/06/25</t>
+          <t>1405/08/06</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>10 روز مانده</t>
+          <t>52 روز مانده</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>* سپه فرهنگيان مشهد</t>
+          <t>* سپه سيدي مشهد</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -6806,22 +6810,26 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0</v>
+        <v>61089499998</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>0</v>
+        <v>1018900000</v>
       </c>
       <c r="O75" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P75" s="6" t="inlineStr"/>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:22:19</t>
+        </is>
+      </c>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:19 (کد پیگیری: 49685355310375)</t>
         </is>
       </c>
     </row>
@@ -6831,37 +6839,45 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>عليرضا يعقوبي</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr"/>
+          <t>عقيل نرمكي</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>0920541526</t>
+        </is>
+      </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr"/>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>2610040153416467</t>
+        </is>
+      </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>030620</t>
         </is>
       </c>
       <c r="G76" s="13" t="n">
-        <v>870000000</v>
+        <v>1160000000</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>1405/06/01</t>
+          <t>1405/10/06</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>منقضی (14 روز گذشته)</t>
+          <t>112 روز مانده</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>* کشاورزي دکتر حسابي</t>
+          <t>* سپه سيدي مشهد</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
@@ -6871,22 +6887,26 @@
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>سند سفته / فاقد صیاد (معاف)</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M76" s="13" t="n">
-        <v>0</v>
+        <v>61089499998</v>
       </c>
       <c r="N76" s="13" t="n">
-        <v>0</v>
+        <v>1018900000</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P76" s="10" t="inlineStr"/>
+      <c r="P76" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:23:23</t>
+        </is>
+      </c>
       <c r="Q76" s="11" t="inlineStr">
         <is>
-          <t>سند تضمینی یا سفته فاقد شناسه ۱۶ رقمی صیاد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:23 (کد پیگیری: 49685355339937)</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6916,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>عليرضا يعقوبي</t>
+          <t>عليرضا ضرغام مقدم</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr"/>
@@ -6907,59 +6927,55 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2033040067329144</t>
+          <t>7283030156765780</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>243520</t>
+          <t>444417</t>
         </is>
       </c>
       <c r="G77" s="12" t="n">
-        <v>870000000</v>
+        <v>350000000</v>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>1405/09/02</t>
+          <t>1405/06/25</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>78 روز مانده</t>
+          <t>10 روز مانده</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>* کشاورزي دکتر حسابي</t>
+          <t>* سپه فرهنگيان مشهد</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M77" s="12" t="n">
-        <v>26680000000</v>
+        <v>0</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>37000000</v>
+        <v>0</v>
       </c>
       <c r="O77" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P77" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:41</t>
-        </is>
-      </c>
+      <c r="P77" s="6" t="inlineStr"/>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:41 (کد پیگیری: 49685355328166)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6985,7 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>فر هنگ نیا مهزیار</t>
+          <t>عليرضا يعقوبي</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr"/>
@@ -6978,32 +6994,28 @@
           <t>سفید</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>3778020108164326</t>
-        </is>
-      </c>
+      <c r="E78" s="10" t="inlineStr"/>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>756139</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="G78" s="13" t="n">
-        <v>895000000</v>
+        <v>870000000</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>1405/06/05</t>
+          <t>1405/06/01</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>منقضی (10 روز گذشته)</t>
+          <t>منقضی (14 روز گذشته)</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>* صادرات کوي اب و برق</t>
+          <t>* کشاورزي دکتر حسابي</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
@@ -7013,7 +7025,7 @@
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>سند سفته / فاقد صیاد (معاف)</t>
         </is>
       </c>
       <c r="M78" s="13" t="n">
@@ -7028,7 +7040,7 @@
       <c r="P78" s="10" t="inlineStr"/>
       <c r="Q78" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>سند تضمینی یا سفته فاقد شناسه ۱۶ رقمی صیاد</t>
         </is>
       </c>
     </row>
@@ -7038,14 +7050,10 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>فريد والي</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>0010485295</t>
-        </is>
-      </c>
+          <t>عليرضا يعقوبي</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr"/>
       <c r="D79" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -7053,59 +7061,59 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>8842040083741990</t>
+          <t>2033040067329144</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>682185</t>
+          <t>243520</t>
         </is>
       </c>
       <c r="G79" s="12" t="n">
-        <v>4000000000</v>
+        <v>870000000</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>1405/06/30</t>
+          <t>1405/09/02</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>15 روز مانده</t>
+          <t>78 روز مانده</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>* سپه رودکي</t>
+          <t>* کشاورزي دکتر حسابي</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M79" s="12" t="n">
-        <v>58720000000</v>
+        <v>26680000000</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>750000000</v>
+        <v>37000000</v>
       </c>
       <c r="O79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 08:46:41</t>
+          <t>2026-09-06 09:22:41</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:41) (کد پیگیری قبلی: 49682942080036)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:41 (کد پیگیری: 49685355328166)</t>
         </is>
       </c>
     </row>
@@ -7115,14 +7123,10 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>محمد ابراهيمي دشت بياض</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>0880141281</t>
-        </is>
-      </c>
+          <t>فر هنگ نیا مهزیار</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr"/>
       <c r="D80" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -7130,59 +7134,55 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>5179050070509551</t>
+          <t>3778020108164326</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>266951</t>
+          <t>756139</t>
         </is>
       </c>
       <c r="G80" s="13" t="n">
-        <v>487500000</v>
+        <v>895000000</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>1405/07/16</t>
+          <t>1405/06/05</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>32 روز مانده</t>
+          <t>منقضی (10 روز گذشته)</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>* کشاورزي خضري</t>
+          <t>* صادرات کوي اب و برق</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M80" s="13" t="n">
-        <v>101507099414</v>
+        <v>0</v>
       </c>
       <c r="N80" s="13" t="n">
-        <v>26820000000</v>
+        <v>0</v>
       </c>
       <c r="O80" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P80" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:21:55</t>
-        </is>
-      </c>
+      <c r="P80" s="10" t="inlineStr"/>
       <c r="Q80" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:55 (کد پیگیری: 49685355305280)</t>
+          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -7192,12 +7192,12 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>محمد ابراهيمي دشت بياض</t>
+          <t>فريد والي</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>0880141281</t>
+          <t>0010485295</t>
         </is>
       </c>
       <c r="D81" s="19" t="inlineStr">
@@ -7207,59 +7207,59 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>3750050070509552</t>
+          <t>8842040083741990</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>266952</t>
+          <t>682185</t>
         </is>
       </c>
       <c r="G81" s="12" t="n">
-        <v>487500000</v>
+        <v>4000000000</v>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>1405/08/16</t>
+          <t>1405/06/30</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>62 روز مانده</t>
+          <t>15 روز مانده</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>* کشاورزي خضري</t>
+          <t>* سپه رودکي</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M81" s="12" t="n">
-        <v>101507099414</v>
+        <v>58720000000</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>26820000000</v>
+        <v>750000000</v>
       </c>
       <c r="O81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:27</t>
+          <t>2026-09-05 08:46:41</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:27 (کد پیگیری: 49685355323218)</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:41) (کد پیگیری قبلی: 49682942080036)</t>
         </is>
       </c>
     </row>
@@ -7284,12 +7284,12 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>2462050070509553</t>
+          <t>5179050070509551</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>266953</t>
+          <t>266951</t>
         </is>
       </c>
       <c r="G82" s="13" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>1405/09/16</t>
+          <t>1405/07/16</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>92 روز مانده</t>
+          <t>32 روز مانده</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="P82" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:00</t>
+          <t>2026-09-06 09:21:55</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:00 (کد پیگیری: 49685355327928)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:55 (کد پیگیری: 49685355305280)</t>
         </is>
       </c>
     </row>
@@ -7361,12 +7361,12 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>3194050070509554</t>
+          <t>3750050070509552</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>266954</t>
+          <t>266952</t>
         </is>
       </c>
       <c r="G83" s="12" t="n">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>1405/10/16</t>
+          <t>1405/08/16</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>122 روز مانده</t>
+          <t>62 روز مانده</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="P83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:27</t>
+          <t>2026-09-06 09:22:27</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:27 (کد پیگیری: 49685355351557)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:27 (کد پیگیری: 49685355323218)</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7423,12 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>محمد حميدي شيرغان</t>
+          <t>محمد ابراهيمي دشت بياض</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>0924049650</t>
+          <t>0880141281</t>
         </is>
       </c>
       <c r="D84" s="19" t="inlineStr">
@@ -7438,35 +7438,35 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>7646040094693690</t>
+          <t>2462050070509553</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>093814</t>
+          <t>266953</t>
         </is>
       </c>
       <c r="G84" s="13" t="n">
-        <v>3720000000</v>
+        <v>487500000</v>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>1405/07/24</t>
+          <t>1405/09/16</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>40 روز مانده</t>
+          <t>92 روز مانده</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>* سپه بازار بزرگ اطلس</t>
+          <t>* کشاورزي خضري</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L84" s="11" t="inlineStr">
@@ -7475,22 +7475,22 @@
         </is>
       </c>
       <c r="M84" s="13" t="n">
-        <v>17880000000</v>
+        <v>101507099414</v>
       </c>
       <c r="N84" s="13" t="n">
-        <v>10283000000</v>
+        <v>26820000000</v>
       </c>
       <c r="O84" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:00</t>
+          <t>2026-09-06 09:23:00</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:00 (کد پیگیری: 49685355305344)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:00 (کد پیگیری: 49685355327928)</t>
         </is>
       </c>
     </row>
@@ -7500,12 +7500,12 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>محمد حميدي شيرغان</t>
+          <t>محمد ابراهيمي دشت بياض</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>0924049650</t>
+          <t>0880141281</t>
         </is>
       </c>
       <c r="D85" s="19" t="inlineStr">
@@ -7515,55 +7515,59 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>7704040137481904</t>
+          <t>3194050070509554</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>415570</t>
+          <t>266954</t>
         </is>
       </c>
       <c r="G85" s="12" t="n">
-        <v>220000000</v>
+        <v>487500000</v>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>1405/07/24</t>
+          <t>1405/10/16</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>40 روز مانده</t>
+          <t>122 روز مانده</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>* پاسارگاد احمداباد</t>
+          <t>* کشاورزي خضري</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0</v>
+        <v>101507099414</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
+        <v>26820000000</v>
       </c>
       <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P85" s="6" t="inlineStr"/>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:23:27</t>
+        </is>
+      </c>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:27 (کد پیگیری: 49685355351557)</t>
         </is>
       </c>
     </row>
@@ -7573,45 +7577,45 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>محمد رفیق طرقی</t>
+          <t>محمد حميدي شيرغان</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>0890543331</t>
-        </is>
-      </c>
-      <c r="D86" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0924049650</t>
+        </is>
+      </c>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>7510050000558312</t>
+          <t>7646040094693690</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>750111</t>
+          <t>093814</t>
         </is>
       </c>
       <c r="G86" s="13" t="n">
-        <v>15000000000</v>
+        <v>3720000000</v>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>1405/07/22</t>
+          <t>1405/07/24</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>38 روز مانده</t>
+          <t>40 روز مانده</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>* تجارت خيابان تهران</t>
+          <t>* سپه بازار بزرگ اطلس</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr">
@@ -7625,22 +7629,22 @@
         </is>
       </c>
       <c r="M86" s="13" t="n">
-        <v>265665000000</v>
+        <v>17880000000</v>
       </c>
       <c r="N86" s="13" t="n">
-        <v>81847500000</v>
+        <v>10283000000</v>
       </c>
       <c r="O86" s="13" t="n">
-        <v>40300000000</v>
+        <v>0</v>
       </c>
       <c r="P86" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:59</t>
+          <t>2026-09-06 09:22:00</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:59 (کد پیگیری: 49685355307268)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:00 (کد پیگیری: 49685355305344)</t>
         </is>
       </c>
     </row>
@@ -7650,45 +7654,45 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>محمد زاهدي آغوي</t>
+          <t>محمد حميدي شيرغان</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>0690489838</t>
-        </is>
-      </c>
-      <c r="D87" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0924049650</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2745040155889930</t>
+          <t>7704040137481904</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>218783</t>
+          <t>415570</t>
         </is>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1890000000</v>
+        <v>220000000</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>1405/06/17</t>
+          <t>1405/07/24</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>سررسید نزدیک (2 روز مانده)</t>
+          <t>40 روز مانده</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>* کشاورزي ترمينال</t>
+          <t>* پاسارگاد احمداباد</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
@@ -7698,26 +7702,22 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M87" s="12" t="n">
-        <v>59290930000</v>
+        <v>0</v>
       </c>
       <c r="N87" s="12" t="n">
-        <v>52840962000</v>
+        <v>0</v>
       </c>
       <c r="O87" s="12" t="n">
-        <v>9398000000</v>
-      </c>
-      <c r="P87" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:21:18</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P87" s="6" t="inlineStr"/>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:18 (کد پیگیری: 49685355297097)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -7727,12 +7727,12 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>محمد زاهدي آغوي</t>
+          <t>محمد رفیق طرقی</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>0690489838</t>
+          <t>0890543331</t>
         </is>
       </c>
       <c r="D88" s="18" t="inlineStr">
@@ -7742,35 +7742,35 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>6170040155889947</t>
+          <t>7510050000558312</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>218800</t>
+          <t>750111</t>
         </is>
       </c>
       <c r="G88" s="13" t="n">
-        <v>7000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>1405/08/25</t>
+          <t>1405/07/22</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>71 روز مانده</t>
+          <t>38 روز مانده</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>* کشاورزي ترمينال مشهد</t>
+          <t>* تجارت خيابان تهران</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>علیرضا ضیافتی</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr">
@@ -7779,22 +7779,22 @@
         </is>
       </c>
       <c r="M88" s="13" t="n">
-        <v>59290930000</v>
+        <v>265665000000</v>
       </c>
       <c r="N88" s="13" t="n">
-        <v>52840962000</v>
+        <v>81847500000</v>
       </c>
       <c r="O88" s="13" t="n">
-        <v>9398000000</v>
+        <v>40300000000</v>
       </c>
       <c r="P88" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:30</t>
+          <t>2026-09-06 09:21:59</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:30 (کد پیگیری: 49685355323269)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:59 (کد پیگیری: 49685355307268)</t>
         </is>
       </c>
     </row>
@@ -7804,12 +7804,12 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>محمد ضيافتي مالدار</t>
+          <t>محمد زاهدي آغوي</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>0922236992</t>
+          <t>0690489838</t>
         </is>
       </c>
       <c r="D89" s="18" t="inlineStr">
@@ -7819,30 +7819,30 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>5138040187866685</t>
+          <t>2745040155889930</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>180057</t>
+          <t>218783</t>
         </is>
       </c>
       <c r="G89" s="12" t="n">
-        <v>16000000000</v>
+        <v>1890000000</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>1405/05/01</t>
+          <t>1405/06/17</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>منقضی (45 روز گذشته)</t>
+          <t>سررسید نزدیک (2 روز مانده)</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي</t>
+          <t>* کشاورزي ترمينال</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
@@ -7856,22 +7856,22 @@
         </is>
       </c>
       <c r="M89" s="12" t="n">
-        <v>1144807000000</v>
+        <v>59290930000</v>
       </c>
       <c r="N89" s="12" t="n">
-        <v>305078252000</v>
+        <v>52840962000</v>
       </c>
       <c r="O89" s="12" t="n">
-        <v>19160000000</v>
+        <v>9398000000</v>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:20:54</t>
+          <t>2026-09-06 09:21:18</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:54 (کد پیگیری: 49685355273867)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:18 (کد پیگیری: 49685355297097)</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7881,12 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>محمد ضيافتي مالدار</t>
+          <t>محمد زاهدي آغوي</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>0922236992</t>
+          <t>0690489838</t>
         </is>
       </c>
       <c r="D90" s="18" t="inlineStr">
@@ -7896,35 +7896,35 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>5080030099110169</t>
+          <t>6170040155889947</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>970083</t>
+          <t>218800</t>
         </is>
       </c>
       <c r="G90" s="13" t="n">
-        <v>5660000000</v>
+        <v>7000000000</v>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>1405/06/01</t>
+          <t>1405/08/25</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>منقضی (14 روز گذشته)</t>
+          <t>71 روز مانده</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* کشاورزي ترمينال مشهد</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>علیرضا ضیافتی</t>
         </is>
       </c>
       <c r="L90" s="11" t="inlineStr">
@@ -7933,22 +7933,22 @@
         </is>
       </c>
       <c r="M90" s="13" t="n">
-        <v>1144807000000</v>
+        <v>59290930000</v>
       </c>
       <c r="N90" s="13" t="n">
-        <v>305078252000</v>
+        <v>52840962000</v>
       </c>
       <c r="O90" s="13" t="n">
-        <v>19160000000</v>
+        <v>9398000000</v>
       </c>
       <c r="P90" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:20:58</t>
+          <t>2026-09-06 09:22:30</t>
         </is>
       </c>
       <c r="Q90" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:58 (کد پیگیری: 49685355276364)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:30 (کد پیگیری: 49685355323269)</t>
         </is>
       </c>
     </row>
@@ -7973,30 +7973,30 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>6200030099110171</t>
+          <t>5138040187866685</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>970085</t>
+          <t>180057</t>
         </is>
       </c>
       <c r="G91" s="12" t="n">
-        <v>5660000000</v>
+        <v>16000000000</v>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/05/01</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>47 روز مانده</t>
+          <t>منقضی (45 روز گذشته)</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* بانک ملي کوي المهدي</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
@@ -8020,12 +8020,12 @@
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:10</t>
+          <t>2026-09-06 09:20:54</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:10 (کد پیگیری: 49685355321584)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:54 (کد پیگیری: 49685355273867)</t>
         </is>
       </c>
     </row>
@@ -8050,30 +8050,30 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>0885050004531113</t>
+          <t>5080030099110169</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>855067</t>
+          <t>970083</t>
         </is>
       </c>
       <c r="G92" s="13" t="n">
-        <v>5500000000</v>
+        <v>5660000000</v>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>1405/08/25</t>
+          <t>1405/06/01</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
         <is>
-          <t>71 روز مانده</t>
+          <t>منقضی (14 روز گذشته)</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>* ملت شيرازي</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr">
@@ -8083,22 +8083,26 @@
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M92" s="13" t="n">
-        <v>0</v>
+        <v>1144807000000</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>0</v>
+        <v>305078252000</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" s="10" t="inlineStr"/>
+        <v>19160000000</v>
+      </c>
+      <c r="P92" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:20:58</t>
+        </is>
+      </c>
       <c r="Q92" s="11" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:58 (کد پیگیری: 49685355276364)</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8127,12 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>2718030099110172</t>
+          <t>6200030099110171</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>970086</t>
+          <t>970085</t>
         </is>
       </c>
       <c r="G93" s="12" t="n">
@@ -8136,17 +8140,17 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>1405/09/01</t>
+          <t>1405/08/01</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>77 روز مانده</t>
+          <t>47 روز مانده</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr">
@@ -8170,12 +8174,12 @@
       </c>
       <c r="P93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:38</t>
+          <t>2026-09-06 09:22:10</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:38 (کد پیگیری: 49685355330069)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:10 (کد پیگیری: 49685355321584)</t>
         </is>
       </c>
     </row>
@@ -8200,30 +8204,30 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>0411800094693691</t>
+          <t>0885050004531113</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>093815</t>
+          <t>855067</t>
         </is>
       </c>
       <c r="G94" s="13" t="n">
-        <v>3720000000</v>
+        <v>5500000000</v>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>1405/09/24</t>
+          <t>1405/08/25</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
         <is>
-          <t>100 روز مانده</t>
+          <t>71 روز مانده</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>* سپه بازار بزرگ اطلس</t>
+          <t>* ملت شيرازي</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr">
@@ -8273,12 +8277,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>5222030099110173</t>
+          <t>2718030099110172</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>970087</t>
+          <t>970086</t>
         </is>
       </c>
       <c r="G95" s="12" t="n">
@@ -8286,17 +8290,17 @@
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>1405/10/01</t>
+          <t>1405/09/01</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>107 روز مانده</t>
+          <t>77 روز مانده</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* بانک ملي کوي المهدي</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
@@ -8320,12 +8324,12 @@
       </c>
       <c r="P95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:12</t>
+          <t>2026-09-06 09:22:38</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:12 (کد پیگیری: 49685355338321)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:38 (کد پیگیری: 49685355330069)</t>
         </is>
       </c>
     </row>
@@ -8350,30 +8354,30 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>9569030099110174</t>
+          <t>0411800094693691</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>970088</t>
+          <t>093815</t>
         </is>
       </c>
       <c r="G96" s="13" t="n">
-        <v>5660000000</v>
+        <v>3720000000</v>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>1405/11/01</t>
+          <t>1405/09/24</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
         <is>
-          <t>137 روز مانده</t>
+          <t>100 روز مانده</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* سپه بازار بزرگ اطلس</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr">
@@ -8383,26 +8387,22 @@
       </c>
       <c r="L96" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M96" s="13" t="n">
-        <v>1144807000000</v>
+        <v>0</v>
       </c>
       <c r="N96" s="13" t="n">
-        <v>305078252000</v>
+        <v>0</v>
       </c>
       <c r="O96" s="13" t="n">
-        <v>19160000000</v>
-      </c>
-      <c r="P96" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:23:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P96" s="10" t="inlineStr"/>
       <c r="Q96" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:33 (کد پیگیری: 49685355355077)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -8412,41 +8412,45 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>محمد طاهري</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr"/>
-      <c r="D97" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>محمد ضيافتي مالدار</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>0922236992</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>7413040073308914</t>
+          <t>5222030099110173</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>793454</t>
+          <t>970087</t>
         </is>
       </c>
       <c r="G97" s="12" t="n">
-        <v>6000000000</v>
+        <v>5660000000</v>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>1405/06/01</t>
+          <t>1405/10/01</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>منقضی (14 روز گذشته)</t>
+          <t>107 روز مانده</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي شهداي گمنام تربت حيدريه</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
@@ -8456,22 +8460,26 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0</v>
+        <v>1144807000000</v>
       </c>
       <c r="N97" s="12" t="n">
-        <v>0</v>
+        <v>305078252000</v>
       </c>
       <c r="O97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="6" t="inlineStr"/>
+        <v>19160000000</v>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:23:12</t>
+        </is>
+      </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:12 (کد پیگیری: 49685355338321)</t>
         </is>
       </c>
     </row>
@@ -8481,12 +8489,12 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>محمدباقر مشيري</t>
+          <t>محمد ضيافتي مالدار</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>0922010536</t>
+          <t>0922236992</t>
         </is>
       </c>
       <c r="D98" s="18" t="inlineStr">
@@ -8496,30 +8504,30 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>7220040201829551</t>
+          <t>9569030099110174</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>849737</t>
+          <t>970088</t>
         </is>
       </c>
       <c r="G98" s="13" t="n">
-        <v>2190000000</v>
+        <v>5660000000</v>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>1405/06/25</t>
+          <t>1405/11/01</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
         <is>
-          <t>10 روز مانده</t>
+          <t>137 روز مانده</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>* مسکن وکيل اباد</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr">
@@ -8533,22 +8541,22 @@
         </is>
       </c>
       <c r="M98" s="13" t="n">
-        <v>48136400000</v>
+        <v>1144807000000</v>
       </c>
       <c r="N98" s="13" t="n">
-        <v>35000000</v>
+        <v>305078252000</v>
       </c>
       <c r="O98" s="13" t="n">
-        <v>0</v>
+        <v>19160000000</v>
       </c>
       <c r="P98" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:24</t>
+          <t>2026-09-06 09:23:33</t>
         </is>
       </c>
       <c r="Q98" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:24 (کد پیگیری: 49685355289857)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:33 (کد پیگیری: 49685355355077)</t>
         </is>
       </c>
     </row>
@@ -8558,45 +8566,41 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>محمدباقر مشيري</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>0922010536</t>
-        </is>
-      </c>
-      <c r="D99" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>محمد طاهري</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr"/>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>2359050004531111</t>
+          <t>7413040073308914</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>855065</t>
+          <t>793454</t>
         </is>
       </c>
       <c r="G99" s="12" t="n">
-        <v>5500000000</v>
+        <v>6000000000</v>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>1405/06/25</t>
+          <t>1405/06/01</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>10 روز مانده</t>
+          <t>منقضی (14 روز گذشته)</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>* ملت شيرازي</t>
+          <t>* بانک ملي شهداي گمنام تربت حيدريه</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
@@ -8606,26 +8610,22 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M99" s="12" t="n">
-        <v>93388000000</v>
+        <v>0</v>
       </c>
       <c r="N99" s="12" t="n">
-        <v>9840000000</v>
+        <v>0</v>
       </c>
       <c r="O99" s="12" t="n">
-        <v>1326000000</v>
-      </c>
-      <c r="P99" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-05 08:45:48</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P99" s="6" t="inlineStr"/>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:45:48) (کد پیگیری قبلی: 49682942065011)</t>
+          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -8643,19 +8643,19 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D100" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D100" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>9910040201829536</t>
+          <t>7220040201829551</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>849738</t>
+          <t>849737</t>
         </is>
       </c>
       <c r="G100" s="13" t="n">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>1405/07/25</t>
+          <t>1405/06/25</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
         <is>
-          <t>41 روز مانده</t>
+          <t>10 روز مانده</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="P100" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:04</t>
+          <t>2026-09-06 09:21:24</t>
         </is>
       </c>
       <c r="Q100" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:04 (کد پیگیری: 49685355310220)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:24 (کد پیگیری: 49685355289857)</t>
         </is>
       </c>
     </row>
@@ -8720,37 +8720,37 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D101" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>2757040201829543</t>
+          <t>2359050004531111</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>849739</t>
+          <t>855065</t>
         </is>
       </c>
       <c r="G101" s="12" t="n">
-        <v>2190000000</v>
+        <v>5500000000</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>1405/08/25</t>
+          <t>1405/06/25</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>71 روز مانده</t>
+          <t>10 روز مانده</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>* مسکن وکيل اباد</t>
+          <t>* ملت شيرازي</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
@@ -8760,26 +8760,26 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M101" s="12" t="n">
-        <v>48136400000</v>
+        <v>93388000000</v>
       </c>
       <c r="N101" s="12" t="n">
-        <v>35000000</v>
+        <v>9840000000</v>
       </c>
       <c r="O101" s="12" t="n">
-        <v>0</v>
+        <v>1326000000</v>
       </c>
       <c r="P101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:33</t>
+          <t>2026-09-05 08:45:48</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:33 (کد پیگیری: 49685355326605)</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:45:48) (کد پیگیری قبلی: 49682942065011)</t>
         </is>
       </c>
     </row>
@@ -8797,19 +8797,19 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D102" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D102" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>1161040201829557</t>
+          <t>9910040201829536</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>849748</t>
+          <t>849738</t>
         </is>
       </c>
       <c r="G102" s="13" t="n">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>1406/05/25</t>
+          <t>1405/07/25</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
         <is>
-          <t>344 روز مانده</t>
+          <t>41 روز مانده</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="P102" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:55</t>
+          <t>2026-09-06 09:22:04</t>
         </is>
       </c>
       <c r="Q102" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:55 (کد پیگیری: 49685355356775)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:04 (کد پیگیری: 49685355310220)</t>
         </is>
       </c>
     </row>
@@ -8874,19 +8874,19 @@
           <t>0922010536</t>
         </is>
       </c>
-      <c r="D103" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>5621040201829539</t>
+          <t>2757040201829543</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>849749</t>
+          <t>849739</t>
         </is>
       </c>
       <c r="G103" s="12" t="n">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>1406/06/25</t>
+          <t>1405/08/25</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>375 روز مانده</t>
+          <t>71 روز مانده</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -8928,12 +8928,12 @@
       </c>
       <c r="P103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 19:14:03</t>
+          <t>2026-09-06 09:22:33</t>
         </is>
       </c>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363379579)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:33 (کد پیگیری: 49685355326605)</t>
         </is>
       </c>
     </row>
@@ -8943,74 +8943,74 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>محمدجواد وفادارعيدگاهي</t>
+          <t>محمدباقر مشيري</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>0924020865</t>
-        </is>
-      </c>
-      <c r="D104" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0922010536</t>
+        </is>
+      </c>
+      <c r="D104" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>5963030071639289</t>
+          <t>1161040201829557</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>804985</t>
+          <t>849748</t>
         </is>
       </c>
       <c r="G104" s="13" t="n">
-        <v>1380000000</v>
+        <v>2190000000</v>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>1405/07/10</t>
+          <t>1406/05/25</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
-          <t>26 روز مانده</t>
+          <t>344 روز مانده</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>* سپه امام رضا فريمان</t>
+          <t>* مسکن وکيل اباد</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M104" s="13" t="n">
-        <v>91680000000</v>
+        <v>48136400000</v>
       </c>
       <c r="N104" s="13" t="n">
-        <v>43715000000</v>
+        <v>35000000</v>
       </c>
       <c r="O104" s="13" t="n">
-        <v>21630000000</v>
+        <v>0</v>
       </c>
       <c r="P104" s="10" t="inlineStr">
         <is>
-          <t>2026-09-05 08:47:08</t>
+          <t>2026-09-06 09:23:55</t>
         </is>
       </c>
       <c r="Q104" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:47:08) (کد پیگیری قبلی: 49682942084694)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:55 (کد پیگیری: 49685355356775)</t>
         </is>
       </c>
     </row>
@@ -9020,50 +9020,50 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>محمدجواد وفادارعيدگاهي</t>
+          <t>محمدباقر مشيري</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>0924020865</t>
-        </is>
-      </c>
-      <c r="D105" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0922010536</t>
+        </is>
+      </c>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>5755030071639290</t>
+          <t>5621040201829539</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>804986</t>
+          <t>849749</t>
         </is>
       </c>
       <c r="G105" s="12" t="n">
-        <v>1380000000</v>
+        <v>2190000000</v>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>1405/08/10</t>
+          <t>1406/06/25</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>56 روز مانده</t>
+          <t>375 روز مانده</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>* سپه امام رضا فريمان</t>
+          <t>* مسکن وکيل اباد</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -9072,22 +9072,22 @@
         </is>
       </c>
       <c r="M105" s="12" t="n">
-        <v>91680000000</v>
+        <v>48136400000</v>
       </c>
       <c r="N105" s="12" t="n">
-        <v>43715000000</v>
+        <v>35000000</v>
       </c>
       <c r="O105" s="12" t="n">
-        <v>21630000000</v>
+        <v>0</v>
       </c>
       <c r="P105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:24</t>
+          <t>2026-09-06 19:14:03</t>
         </is>
       </c>
       <c r="Q105" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:24 (کد پیگیری: 49685355318270)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363379579)</t>
         </is>
       </c>
     </row>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>مرتضي مؤذن</t>
+          <t>محمدجواد وفادارعيدگاهي</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>6430003159</t>
+          <t>0924020865</t>
         </is>
       </c>
       <c r="D106" s="18" t="inlineStr">
@@ -9112,30 +9112,30 @@
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>0889304019406437</t>
+          <t>5963030071639289</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>327252</t>
+          <t>804985</t>
         </is>
       </c>
       <c r="G106" s="13" t="n">
-        <v>400000000</v>
+        <v>1380000000</v>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>1405/06/11</t>
+          <t>1405/07/10</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
         <is>
-          <t>منقضی (4 روز گذشته)</t>
+          <t>26 روز مانده</t>
         </is>
       </c>
       <c r="J106" s="11" t="inlineStr">
         <is>
-          <t>* صادرات معلم</t>
+          <t>* سپه امام رضا فريمان</t>
         </is>
       </c>
       <c r="K106" s="11" t="inlineStr">
@@ -9145,22 +9145,26 @@
       </c>
       <c r="L106" s="11" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M106" s="13" t="n">
-        <v>0</v>
+        <v>91680000000</v>
       </c>
       <c r="N106" s="13" t="n">
-        <v>0</v>
+        <v>43715000000</v>
       </c>
       <c r="O106" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" s="10" t="inlineStr"/>
+        <v>21630000000</v>
+      </c>
+      <c r="P106" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-05 08:47:08</t>
+        </is>
+      </c>
       <c r="Q106" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/11 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:47:08) (کد پیگیری قبلی: 49682942084694)</t>
         </is>
       </c>
     </row>
@@ -9170,12 +9174,12 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>مرتضي مؤذن</t>
+          <t>محمدجواد وفادارعيدگاهي</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>6430003159</t>
+          <t>0924020865</t>
         </is>
       </c>
       <c r="D107" s="18" t="inlineStr">
@@ -9185,35 +9189,35 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>1648040177207489</t>
+          <t>5755030071639290</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>791198</t>
+          <t>804986</t>
         </is>
       </c>
       <c r="G107" s="12" t="n">
-        <v>490000000</v>
+        <v>1380000000</v>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>1405/09/03</t>
+          <t>1405/08/10</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>79 روز مانده</t>
+          <t>56 روز مانده</t>
         </is>
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>* پاسارگاد قرني مشهد</t>
+          <t>* سپه امام رضا فريمان</t>
         </is>
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -9222,22 +9226,22 @@
         </is>
       </c>
       <c r="M107" s="12" t="n">
-        <v>47434500000</v>
+        <v>91680000000</v>
       </c>
       <c r="N107" s="12" t="n">
-        <v>890000000</v>
+        <v>43715000000</v>
       </c>
       <c r="O107" s="12" t="n">
-        <v>0</v>
+        <v>21630000000</v>
       </c>
       <c r="P107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:44</t>
+          <t>2026-09-06 09:22:24</t>
         </is>
       </c>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:44 (کد پیگیری: 49685355330620)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:24 (کد پیگیری: 49685355318270)</t>
         </is>
       </c>
     </row>
@@ -9252,69 +9256,65 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>6430003159</t>
-        </is>
-      </c>
-      <c r="D108" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0920630138</t>
+        </is>
+      </c>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>3079040177207490</t>
+          <t>0889304019406437</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>791199</t>
+          <t>327252</t>
         </is>
       </c>
       <c r="G108" s="13" t="n">
-        <v>490000000</v>
+        <v>400000000</v>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>1405/09/10</t>
+          <t>1405/06/11</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr">
         <is>
-          <t>86 روز مانده</t>
+          <t>منقضی (4 روز گذشته)</t>
         </is>
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>* پاسارگاد قرني مشهد</t>
+          <t>* صادرات معلم</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L108" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M108" s="13" t="n">
-        <v>47434500000</v>
+        <v>0</v>
       </c>
       <c r="N108" s="13" t="n">
-        <v>890000000</v>
+        <v>0</v>
       </c>
       <c r="O108" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P108" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:51</t>
-        </is>
-      </c>
+      <c r="P108" s="10" t="inlineStr"/>
       <c r="Q108" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:51 (کد پیگیری: 49685355327817)</t>
+          <t>سررسید چک در تاریخ 1405/06/11 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -9329,22 +9329,22 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>6430003159</t>
-        </is>
-      </c>
-      <c r="D109" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0920630138</t>
+        </is>
+      </c>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>4477040177207491</t>
+          <t>1648040177207489</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>791200</t>
+          <t>791198</t>
         </is>
       </c>
       <c r="G109" s="12" t="n">
@@ -9352,17 +9352,17 @@
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>1405/09/15</t>
+          <t>1405/09/03</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>91 روز مانده</t>
+          <t>79 روز مانده</t>
         </is>
       </c>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>* پاسارگاد قرني</t>
+          <t>* پاسارگاد قرني مشهد</t>
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="P109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:56</t>
+          <t>2026-09-06 09:22:44</t>
         </is>
       </c>
       <c r="Q109" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:56 (کد پیگیری: 49685355336594)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:44 (کد پیگیری: 49685355330620)</t>
         </is>
       </c>
     </row>
@@ -9406,45 +9406,45 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>6430003159</t>
-        </is>
-      </c>
-      <c r="D110" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0920630138</t>
+        </is>
+      </c>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>9330040056179006</t>
+          <t>3079040177207490</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>824589</t>
+          <t>791199</t>
         </is>
       </c>
       <c r="G110" s="13" t="n">
-        <v>2670000000</v>
+        <v>490000000</v>
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>1405/09/16</t>
+          <t>1405/09/10</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr">
         <is>
-          <t>92 روز مانده</t>
+          <t>86 روز مانده</t>
         </is>
       </c>
       <c r="J110" s="11" t="inlineStr">
         <is>
-          <t>* صادرات سيدي</t>
+          <t>* پاسارگاد قرني مشهد</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L110" s="11" t="inlineStr">
@@ -9453,22 +9453,22 @@
         </is>
       </c>
       <c r="M110" s="13" t="n">
-        <v>294823500000</v>
+        <v>47434500000</v>
       </c>
       <c r="N110" s="13" t="n">
-        <v>152016000000</v>
+        <v>890000000</v>
       </c>
       <c r="O110" s="13" t="n">
-        <v>46080000000</v>
+        <v>0</v>
       </c>
       <c r="P110" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:58</t>
+          <t>2026-09-06 09:22:51</t>
         </is>
       </c>
       <c r="Q110" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:58 (کد پیگیری: 49685355335702)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:51 (کد پیگیری: 49685355327817)</t>
         </is>
       </c>
     </row>
@@ -9483,22 +9483,22 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>6430003159</t>
-        </is>
-      </c>
-      <c r="D111" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0920630138</t>
+        </is>
+      </c>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>3404040177207492</t>
+          <t>4477040177207491</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>791201</t>
+          <t>791200</t>
         </is>
       </c>
       <c r="G111" s="12" t="n">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>1405/09/20</t>
+          <t>1405/09/15</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>96 روز مانده</t>
+          <t>91 روز مانده</t>
         </is>
       </c>
       <c r="J111" s="7" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="P111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:02</t>
+          <t>2026-09-06 09:22:56</t>
         </is>
       </c>
       <c r="Q111" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:02 (کد پیگیری: 49685355327942)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:56 (کد پیگیری: 49685355336594)</t>
         </is>
       </c>
     </row>
@@ -9560,22 +9560,22 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>6430003159</t>
-        </is>
-      </c>
-      <c r="D112" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0920630138</t>
+        </is>
+      </c>
+      <c r="D112" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>5120040177207493</t>
+          <t>3404040177207492</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>791202</t>
+          <t>791201</t>
         </is>
       </c>
       <c r="G112" s="13" t="n">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>1405/09/25</t>
+          <t>1405/09/20</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
         <is>
-          <t>101 روز مانده</t>
+          <t>96 روز مانده</t>
         </is>
       </c>
       <c r="J112" s="11" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="P112" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:09</t>
+          <t>2026-09-06 09:23:02</t>
         </is>
       </c>
       <c r="Q112" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:09 (کد پیگیری: 49685355345013)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:02 (کد پیگیری: 49685355327942)</t>
         </is>
       </c>
     </row>
@@ -9637,22 +9637,22 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>6430003159</t>
-        </is>
-      </c>
-      <c r="D113" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0920630138</t>
+        </is>
+      </c>
+      <c r="D113" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>6201040177207494</t>
+          <t>5120040177207493</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>791203</t>
+          <t>791202</t>
         </is>
       </c>
       <c r="G113" s="12" t="n">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>1405/09/30</t>
+          <t>1405/09/25</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>106 روز مانده</t>
+          <t>101 روز مانده</t>
         </is>
       </c>
       <c r="J113" s="7" t="inlineStr">
@@ -9675,27 +9675,31 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0</v>
+        <v>47434500000</v>
       </c>
       <c r="N113" s="12" t="n">
-        <v>0</v>
+        <v>890000000</v>
       </c>
       <c r="O113" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P113" s="6" t="inlineStr"/>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:23:09</t>
+        </is>
+      </c>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:09 (کد پیگیری: 49685355345013)</t>
         </is>
       </c>
     </row>
@@ -9705,12 +9709,12 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>مرتضي پيروزيان</t>
+          <t>مرتضي مؤذن</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>0942904257</t>
+          <t>0920630138</t>
         </is>
       </c>
       <c r="D114" s="19" t="inlineStr">
@@ -9720,30 +9724,30 @@
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>8140050019357728</t>
+          <t>6201040177207494</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>135598</t>
+          <t>791203</t>
         </is>
       </c>
       <c r="G114" s="13" t="n">
-        <v>1000000000</v>
+        <v>490000000</v>
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>1405/06/01</t>
+          <t>1405/09/30</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
         <is>
-          <t>منقضی (14 روز گذشته)</t>
+          <t>106 روز مانده</t>
         </is>
       </c>
       <c r="J114" s="11" t="inlineStr">
         <is>
-          <t>* قرض الحسنه رسالت بانکداري اجتماعي</t>
+          <t>* پاسارگاد قرني</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr">
@@ -9753,7 +9757,7 @@
       </c>
       <c r="L114" s="11" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M114" s="13" t="n">
@@ -9768,7 +9772,7 @@
       <c r="P114" s="10" t="inlineStr"/>
       <c r="Q114" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -9793,12 +9797,12 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>1470050019357729</t>
+          <t>8140050019357728</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>135599</t>
+          <t>135598</t>
         </is>
       </c>
       <c r="G115" s="12" t="n">
@@ -9806,12 +9810,12 @@
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>1405/07/01</t>
+          <t>1405/06/01</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>17 روز مانده</t>
+          <t>منقضی (14 روز گذشته)</t>
         </is>
       </c>
       <c r="J115" s="7" t="inlineStr">
@@ -9826,26 +9830,22 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M115" s="12" t="n">
-        <v>20290000000</v>
+        <v>0</v>
       </c>
       <c r="N115" s="12" t="n">
-        <v>2605000000</v>
+        <v>0</v>
       </c>
       <c r="O115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P115" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:21:36</t>
-        </is>
-      </c>
+      <c r="P115" s="6" t="inlineStr"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:36 (کد پیگیری: 49685355299734)</t>
+          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -9870,12 +9870,12 @@
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>5540050019357730</t>
+          <t>1470050019357729</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>135600</t>
+          <t>135599</t>
         </is>
       </c>
       <c r="G116" s="13" t="n">
@@ -9883,17 +9883,17 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/07/01</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
         <is>
-          <t>47 روز مانده</t>
+          <t>17 روز مانده</t>
         </is>
       </c>
       <c r="J116" s="11" t="inlineStr">
         <is>
-          <t>* قرض الحسنه رسالت بانکداري اجتماعيي</t>
+          <t>* قرض الحسنه رسالت بانکداري اجتماعي</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="L116" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M116" s="13" t="n">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="P116" s="10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:55</t>
+          <t>2026-09-06 09:21:36</t>
         </is>
       </c>
       <c r="Q116" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-08-28 20:53:55) (کد پیگیری قبلی: 49664982349765)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:36 (کد پیگیری: 49685355299734)</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>5524050019357731</t>
+          <t>5540050019357730</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>135601</t>
+          <t>135600</t>
         </is>
       </c>
       <c r="G117" s="12" t="n">
@@ -9960,17 +9960,17 @@
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>1405/09/01</t>
+          <t>1405/08/01</t>
         </is>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>77 روز مانده</t>
+          <t>47 روز مانده</t>
         </is>
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>* قرض الحسنه رسالت بانکداري اجتماعي</t>
+          <t>* قرض الحسنه رسالت بانکداري اجتماعيي</t>
         </is>
       </c>
       <c r="K117" s="7" t="inlineStr">
@@ -9980,22 +9980,26 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0</v>
+        <v>20290000000</v>
       </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
+        <v>2605000000</v>
       </c>
       <c r="O117" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P117" s="6" t="inlineStr"/>
+      <c r="P117" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:53:55</t>
+        </is>
+      </c>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-08-28 20:53:55) (کد پیگیری قبلی: 49664982349765)</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10024,12 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>3096050019357732</t>
+          <t>5524050019357731</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>135602</t>
+          <t>135601</t>
         </is>
       </c>
       <c r="G118" s="13" t="n">
@@ -10033,12 +10037,12 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>1405/10/01</t>
+          <t>1405/09/01</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
         <is>
-          <t>107 روز مانده</t>
+          <t>77 روز مانده</t>
         </is>
       </c>
       <c r="J118" s="11" t="inlineStr">
@@ -10053,26 +10057,22 @@
       </c>
       <c r="L118" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M118" s="13" t="n">
-        <v>20290000000</v>
+        <v>0</v>
       </c>
       <c r="N118" s="13" t="n">
-        <v>2605000000</v>
+        <v>0</v>
       </c>
       <c r="O118" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P118" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:23:17</t>
-        </is>
-      </c>
+      <c r="P118" s="10" t="inlineStr"/>
       <c r="Q118" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:17 (کد پیگیری: 49685355338378)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -10097,12 +10097,12 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>1114050019357733</t>
+          <t>3096050019357732</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>135603</t>
+          <t>135602</t>
         </is>
       </c>
       <c r="G119" s="12" t="n">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>1405/11/01</t>
+          <t>1405/10/01</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>137 روز مانده</t>
+          <t>107 روز مانده</t>
         </is>
       </c>
       <c r="J119" s="7" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="P119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:35</t>
+          <t>2026-09-06 09:23:17</t>
         </is>
       </c>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:35 (کد پیگیری: 49685355346272)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:17 (کد پیگیری: 49685355338378)</t>
         </is>
       </c>
     </row>
@@ -10159,12 +10159,12 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>مريم حسني</t>
+          <t>مرتضي پيروزيان</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>0934578771</t>
+          <t>0942904257</t>
         </is>
       </c>
       <c r="D120" s="19" t="inlineStr">
@@ -10174,30 +10174,30 @@
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>7553040121559293</t>
+          <t>1114050019357733</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>02563329</t>
+          <t>135603</t>
         </is>
       </c>
       <c r="G120" s="13" t="n">
-        <v>3100000000</v>
+        <v>1000000000</v>
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>1406/05/05</t>
+          <t>1405/11/01</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
         <is>
-          <t>324 روز مانده</t>
+          <t>137 روز مانده</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr">
         <is>
-          <t>* ملت گلشهر</t>
+          <t>* قرض الحسنه رسالت بانکداري اجتماعي</t>
         </is>
       </c>
       <c r="K120" s="11" t="inlineStr">
@@ -10211,22 +10211,22 @@
         </is>
       </c>
       <c r="M120" s="13" t="n">
-        <v>76774740000</v>
+        <v>20290000000</v>
       </c>
       <c r="N120" s="13" t="n">
-        <v>13688200000</v>
+        <v>2605000000</v>
       </c>
       <c r="O120" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:54</t>
+          <t>2026-09-06 09:23:35</t>
         </is>
       </c>
       <c r="Q120" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:54 (کد پیگیری: 49685355356761)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:35 (کد پیگیری: 49685355346272)</t>
         </is>
       </c>
     </row>
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>1850040121559294</t>
+          <t>7553040121559293</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>02563415</t>
+          <t>02563329</t>
         </is>
       </c>
       <c r="G121" s="12" t="n">
@@ -10264,12 +10264,12 @@
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>1406/06/05</t>
+          <t>1406/05/05</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>355 روز مانده</t>
+          <t>324 روز مانده</t>
         </is>
       </c>
       <c r="J121" s="7" t="inlineStr">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="P121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:57</t>
+          <t>2026-09-06 09:23:54</t>
         </is>
       </c>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:57 (کد پیگیری: 49685355362576)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:54 (کد پیگیری: 49685355356761)</t>
         </is>
       </c>
     </row>
@@ -10328,12 +10328,12 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>6331040121559295</t>
+          <t>1850040121559294</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>02563552</t>
+          <t>02563415</t>
         </is>
       </c>
       <c r="G122" s="13" t="n">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>1406/07/05</t>
+          <t>1406/06/05</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
         <is>
-          <t>386 روز مانده</t>
+          <t>355 روز مانده</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="P122" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:24:00</t>
+          <t>2026-09-06 09:23:57</t>
         </is>
       </c>
       <c r="Q122" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:24:00 (کد پیگیری: 49685355359253)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:57 (کد پیگیری: 49685355362576)</t>
         </is>
       </c>
     </row>
@@ -10390,12 +10390,12 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>مسعود زرين نام</t>
+          <t>مريم حسني</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>0945428022</t>
+          <t>0934578771</t>
         </is>
       </c>
       <c r="D123" s="19" t="inlineStr">
@@ -10405,30 +10405,30 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>1650010182049909</t>
+          <t>6331040121559295</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>186921</t>
+          <t>02563552</t>
         </is>
       </c>
       <c r="G123" s="12" t="n">
-        <v>2000000000</v>
+        <v>3100000000</v>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>1405/07/25</t>
+          <t>1406/07/05</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>41 روز مانده</t>
+          <t>386 روز مانده</t>
         </is>
       </c>
       <c r="J123" s="7" t="inlineStr">
         <is>
-          <t>* ملت جمهوري اسلامي مشهد</t>
+          <t>* ملت گلشهر</t>
         </is>
       </c>
       <c r="K123" s="7" t="inlineStr">
@@ -10442,22 +10442,22 @@
         </is>
       </c>
       <c r="M123" s="12" t="n">
-        <v>7899823000</v>
+        <v>76774740000</v>
       </c>
       <c r="N123" s="12" t="n">
-        <v>0</v>
+        <v>13688200000</v>
       </c>
       <c r="O123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:03</t>
+          <t>2026-09-06 09:24:00</t>
         </is>
       </c>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:03 (کد پیگیری: 49685355304941)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:24:00 (کد پیگیری: 49685355359253)</t>
         </is>
       </c>
     </row>
@@ -10467,12 +10467,12 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>معصومه دوامي</t>
+          <t>مسعود زرين نام</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>6439564609</t>
+          <t>0945428022</t>
         </is>
       </c>
       <c r="D124" s="19" t="inlineStr">
@@ -10482,30 +10482,30 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>7870040191134434</t>
+          <t>1650010182049909</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>300936</t>
+          <t>186921</t>
         </is>
       </c>
       <c r="G124" s="13" t="n">
-        <v>15200000000</v>
+        <v>2000000000</v>
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>1405/08/25</t>
+          <t>1405/07/25</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
         <is>
-          <t>71 روز مانده</t>
+          <t>41 روز مانده</t>
         </is>
       </c>
       <c r="J124" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي بيمارستان قايم</t>
+          <t>* ملت جمهوري اسلامي مشهد</t>
         </is>
       </c>
       <c r="K124" s="11" t="inlineStr">
@@ -10519,22 +10519,22 @@
         </is>
       </c>
       <c r="M124" s="13" t="n">
-        <v>162300000000</v>
+        <v>7899823000</v>
       </c>
       <c r="N124" s="13" t="n">
-        <v>265000000</v>
+        <v>0</v>
       </c>
       <c r="O124" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:29</t>
+          <t>2026-09-06 09:22:03</t>
         </is>
       </c>
       <c r="Q124" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:29 (کد پیگیری: 49685355323252)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:03 (کد پیگیری: 49685355304941)</t>
         </is>
       </c>
     </row>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>7108040191134435</t>
+          <t>7870040191134434</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>300937</t>
+          <t>300936</t>
         </is>
       </c>
       <c r="G125" s="12" t="n">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>1405/09/25</t>
+          <t>1405/08/25</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>101 روز مانده</t>
+          <t>71 روز مانده</t>
         </is>
       </c>
       <c r="J125" s="7" t="inlineStr">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="P125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:05</t>
+          <t>2026-09-06 09:22:29</t>
         </is>
       </c>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:05 (کد پیگیری: 49685355336252)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:29 (کد پیگیری: 49685355323252)</t>
         </is>
       </c>
     </row>
@@ -10636,30 +10636,30 @@
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>1512040191134431</t>
+          <t>7108040191134435</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>300933</t>
+          <t>300937</t>
         </is>
       </c>
       <c r="G126" s="13" t="n">
-        <v>6500000000</v>
+        <v>15200000000</v>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>1405/10/01</t>
+          <t>1405/09/25</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr">
         <is>
-          <t>107 روز مانده</t>
+          <t>101 روز مانده</t>
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي بيمارستان قايم مشهد 8545</t>
+          <t>* بانک ملي بيمارستان قايم</t>
         </is>
       </c>
       <c r="K126" s="11" t="inlineStr">
@@ -10683,12 +10683,12 @@
       </c>
       <c r="P126" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:13</t>
+          <t>2026-09-06 09:23:05</t>
         </is>
       </c>
       <c r="Q126" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:13 (کد پیگیری: 49685355332442)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:05 (کد پیگیری: 49685355336252)</t>
         </is>
       </c>
     </row>
@@ -10713,30 +10713,30 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>5457040191134436</t>
+          <t>1512040191134431</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>300938</t>
+          <t>300933</t>
         </is>
       </c>
       <c r="G127" s="12" t="n">
-        <v>15200000000</v>
+        <v>6500000000</v>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>1405/10/25</t>
+          <t>1405/10/01</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>131 روز مانده</t>
+          <t>107 روز مانده</t>
         </is>
       </c>
       <c r="J127" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي بيمارستان قايم</t>
+          <t>* بانک ملي بيمارستان قايم مشهد 8545</t>
         </is>
       </c>
       <c r="K127" s="7" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="P127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:30</t>
+          <t>2026-09-06 09:23:13</t>
         </is>
       </c>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:30 (کد پیگیری: 49685355351603)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:13 (کد پیگیری: 49685355332442)</t>
         </is>
       </c>
     </row>
@@ -10790,12 +10790,12 @@
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>5203040191134437</t>
+          <t>5457040191134436</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>300939</t>
+          <t>300938</t>
         </is>
       </c>
       <c r="G128" s="13" t="n">
@@ -10803,12 +10803,12 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>1405/11/25</t>
+          <t>1405/10/25</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr">
         <is>
-          <t>161 روز مانده</t>
+          <t>131 روز مانده</t>
         </is>
       </c>
       <c r="J128" s="11" t="inlineStr">
@@ -10837,12 +10837,12 @@
       </c>
       <c r="P128" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:41</t>
+          <t>2026-09-06 09:23:30</t>
         </is>
       </c>
       <c r="Q128" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:41 (کد پیگیری: 49685355348870)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:30 (کد پیگیری: 49685355351603)</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>1732040191134438</t>
+          <t>5203040191134437</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>300940</t>
+          <t>300939</t>
         </is>
       </c>
       <c r="G129" s="12" t="n">
@@ -10880,17 +10880,17 @@
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>1405/12/25</t>
+          <t>1405/11/25</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>191 روز مانده</t>
+          <t>161 روز مانده</t>
         </is>
       </c>
       <c r="J129" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي بيمارستان قايمم</t>
+          <t>* بانک ملي بيمارستان قايم</t>
         </is>
       </c>
       <c r="K129" s="7" t="inlineStr">
@@ -10914,12 +10914,12 @@
       </c>
       <c r="P129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:45</t>
+          <t>2026-09-06 09:23:41</t>
         </is>
       </c>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:45 (کد پیگیری: 49685355345963)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:41 (کد پیگیری: 49685355348870)</t>
         </is>
       </c>
     </row>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>مقنی عباس</t>
+          <t>معصومه دوامي</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>0922030936</t>
+          <t>6439564609</t>
         </is>
       </c>
       <c r="D130" s="19" t="inlineStr">
@@ -10944,30 +10944,30 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>4204010168700706</t>
+          <t>1732040191134438</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>076149</t>
+          <t>300940</t>
         </is>
       </c>
       <c r="G130" s="13" t="n">
-        <v>11520000000</v>
+        <v>15200000000</v>
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>1405/07/25</t>
+          <t>1405/12/25</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr">
         <is>
-          <t>41 روز مانده</t>
+          <t>191 روز مانده</t>
         </is>
       </c>
       <c r="J130" s="11" t="inlineStr">
         <is>
-          <t>* صادرات شهرک صنعتي طرق</t>
+          <t>* بانک ملي بيمارستان قايمم</t>
         </is>
       </c>
       <c r="K130" s="11" t="inlineStr">
@@ -10981,22 +10981,22 @@
         </is>
       </c>
       <c r="M130" s="13" t="n">
-        <v>224823000000</v>
+        <v>162300000000</v>
       </c>
       <c r="N130" s="13" t="n">
-        <v>30402825000</v>
+        <v>265000000</v>
       </c>
       <c r="O130" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:06</t>
+          <t>2026-09-06 09:23:45</t>
         </is>
       </c>
       <c r="Q130" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:06 (کد پیگیری: 49685355308315)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:45 (کد پیگیری: 49685355345963)</t>
         </is>
       </c>
     </row>
@@ -12520,7 +12520,7 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
@@ -12529,20 +12529,20 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>پرریسک با مبالغ خرد (تحت نظر)</t>
+          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
         </is>
       </c>
       <c r="H2" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="13" t="n">
-        <v>0</v>
+        <v>7500000000</v>
       </c>
       <c r="J2" s="13" t="n">
-        <v>0</v>
+        <v>46230000000</v>
       </c>
       <c r="K2" s="13" t="n">
-        <v>0</v>
+        <v>12800000000</v>
       </c>
       <c r="L2" s="11" t="inlineStr">
         <is>
@@ -12958,20 +12958,20 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>قرمز</t>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>پرخطر</t>
+        <v>96.8</v>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>عالی</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
+          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
+          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
         </is>
       </c>
     </row>
@@ -13371,16 +13371,16 @@
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>10680000000</v>
+        <v>13350000000</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>1179294000000</v>
+        <v>1474117500000</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>184320000000</v>
+        <v>230400000000</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -13700,37 +13700,37 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>قرمز</t>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>پرخطر</t>
+        <v>96.7</v>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>عالی</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
+          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
         </is>
       </c>
       <c r="H26" s="10" t="n">
         <v>4</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>38300000000</v>
+        <v>42320000000</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>731199000000</v>
+        <v>909792000000</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>12800000000</v>
+        <v>0</v>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
+          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
+          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
         </is>
       </c>
       <c r="H32" s="10" t="n">
@@ -14334,20 +14334,20 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>قرمز</t>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>پرخطر</t>
+        <v>83.2</v>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>خوب</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
+          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
+          <t>سلامت مالی مطلوب و کم‌ریسک. تداوم همکاری با رعایت دوره‌های معمول تسویه حساب توصیه می‌شود.</t>
         </is>
       </c>
     </row>
@@ -14429,42 +14429,42 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>6430003159</t>
+          <t>0920630138</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>قرمز</t>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>پرخطر</t>
+        <v>97.3</v>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>عالی</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
+          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>6010000000</v>
+        <v>3340000000</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>531996000000</v>
+        <v>237172500000</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>46080000000</v>
+        <v>0</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
+          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="E46" s="10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
@@ -14697,17 +14697,17 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>11520000000</v>
+        <v>0</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>224823000000</v>
+        <v>0</v>
       </c>
       <c r="K46" s="13" t="n">
         <v>0</v>

--- a/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
+++ b/گزارش_جامع_استعلام_چک_ها_۱۴۰۵۰۶۱۵.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 19:17:41 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
+          <t>سامانه صیاد پرو ۳.۱ | تاریخ تهیه گزارش: 1405/06/15 ساعت 19:55:42 | منبع داده: درگاه رسمی بانک مرکزی و بانک پاسارگاد</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>36</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>293940000000</v>
+        <v>289940000000</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>29260000000</v>
+        <v>33260000000</v>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>13265000000</v>
+        <v>11945000000</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>146860000000</v>
+        <v>148180000000</v>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -4853,45 +4853,45 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>صاحب چک فريمان (۰۹۲۴۰۲۰۸۶۵)</t>
+          <t>طاهره حسني</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>0924020865</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>5228890297</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>1907030071639288</t>
+          <t>1748040121634559</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>804984</t>
+          <t>189764</t>
         </is>
       </c>
       <c r="G50" s="13" t="n">
-        <v>1380000000</v>
+        <v>3100000000</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>1405/06/10</t>
+          <t>1405/06/05</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>منقضی (5 روز گذشته)</t>
+          <t>منقضی (10 روز گذشته)</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>* سپه امام رضا فريمان</t>
+          <t>* بانک ملي کوي المهدي</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
@@ -4901,26 +4901,22 @@
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M50" s="13" t="n">
-        <v>91680000000</v>
+        <v>0</v>
       </c>
       <c r="N50" s="13" t="n">
-        <v>43715000000</v>
+        <v>0</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>21630000000</v>
-      </c>
-      <c r="P50" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-05 08:42:05</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P50" s="10" t="inlineStr"/>
       <c r="Q50" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:42:05) (کد پیگیری قبلی: 49682941988821)</t>
+          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -4930,45 +4926,45 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>صاحب چک فريمان (۰۹۲۴۰۲۰۸۶۵)</t>
+          <t>طاهره حسني</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>0924020865</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>5228890297</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>9910030071163929</t>
+          <t>2240040121634560</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>804987</t>
+          <t>189765</t>
         </is>
       </c>
       <c r="G51" s="12" t="n">
-        <v>1380000000</v>
+        <v>3100000000</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>1405/09/10</t>
+          <t>1405/07/05</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>86 روز مانده</t>
+          <t>21 روز مانده</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>* سپه امام رضا فريمان</t>
+          <t>* بانک ملي کوي المهدي</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
@@ -4978,22 +4974,26 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0</v>
+        <v>145613735000</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>0</v>
+        <v>59466770010</v>
       </c>
       <c r="O51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P51" s="6" t="inlineStr"/>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-05 08:46:58</t>
+        </is>
+      </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:58) (کد پیگیری قبلی: 49682942078736)</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5018,12 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>1748040121634559</t>
+          <t>4962040121634561</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>189764</t>
+          <t>189766</t>
         </is>
       </c>
       <c r="G52" s="13" t="n">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>1405/06/05</t>
+          <t>1405/08/05</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>منقضی (10 روز گذشته)</t>
+          <t>51 روز مانده</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
@@ -5051,22 +5051,26 @@
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M52" s="13" t="n">
-        <v>0</v>
+        <v>145613735000</v>
       </c>
       <c r="N52" s="13" t="n">
-        <v>0</v>
+        <v>59466770010</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P52" s="10" t="inlineStr"/>
+      <c r="P52" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:22:15</t>
+        </is>
+      </c>
       <c r="Q52" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:15 (کد پیگیری: 49685355321656)</t>
         </is>
       </c>
     </row>
@@ -5091,12 +5095,12 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2240040121634560</t>
+          <t>2770040121634562</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>189765</t>
+          <t>189767</t>
         </is>
       </c>
       <c r="G53" s="12" t="n">
@@ -5104,12 +5108,12 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>1405/07/05</t>
+          <t>1405/09/05</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>21 روز مانده</t>
+          <t>81 روز مانده</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
@@ -5124,7 +5128,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M53" s="12" t="n">
@@ -5138,12 +5142,12 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 08:46:58</t>
+          <t>2026-09-06 09:22:45</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:58) (کد پیگیری قبلی: 49682942078736)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:45 (کد پیگیری: 49685355335056)</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5172,12 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>4962040121634561</t>
+          <t>1120040121634563</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>189766</t>
+          <t>189768</t>
         </is>
       </c>
       <c r="G54" s="13" t="n">
@@ -5181,12 +5185,12 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>1405/08/05</t>
+          <t>1406/08/05</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>51 روز مانده</t>
+          <t>416 روز مانده</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
@@ -5215,12 +5219,12 @@
       </c>
       <c r="P54" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:15</t>
+          <t>2026-09-06 09:24:02</t>
         </is>
       </c>
       <c r="Q54" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:15 (کد پیگیری: 49685355321656)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:24:02 (کد پیگیری: 49685355362164)</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5234,12 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>طاهره حسني</t>
+          <t>عباس مقنی</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>5228890297</t>
+          <t>0922030936</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -5245,30 +5249,30 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2770040121634562</t>
+          <t>5560050044994051</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>189767</t>
+          <t>902051</t>
         </is>
       </c>
       <c r="G55" s="12" t="n">
-        <v>3100000000</v>
+        <v>6200000000</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>1405/09/05</t>
+          <t>1405/06/10</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>81 روز مانده</t>
+          <t>منقضی (5 روز گذشته)</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي</t>
+          <t>* سپه بلوار فرودگاه</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
@@ -5278,26 +5282,26 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M55" s="12" t="n">
-        <v>145613735000</v>
+        <v>235323000000</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>59466770010</v>
+        <v>30402825000</v>
       </c>
       <c r="O55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:45</t>
+          <t>2026-08-28 20:51:57</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:45 (کد پیگیری: 49685355335056)</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-08-28 20:51:57) (کد پیگیری قبلی: 49664982347170)</t>
         </is>
       </c>
     </row>
@@ -5307,12 +5311,12 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>طاهره حسني</t>
+          <t>عباس مقنی</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>5228890297</t>
+          <t>0922030936</t>
         </is>
       </c>
       <c r="D56" s="19" t="inlineStr">
@@ -5322,30 +5326,30 @@
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>1120040121634563</t>
+          <t>4204010168700706</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>189768</t>
+          <t>076149</t>
         </is>
       </c>
       <c r="G56" s="13" t="n">
-        <v>3100000000</v>
+        <v>11520000000</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>1406/08/05</t>
+          <t>1405/07/25</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>416 روز مانده</t>
+          <t>41 روز مانده</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي</t>
+          <t>* صادرات شهرک صنعتي طرق</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
@@ -5359,22 +5363,22 @@
         </is>
       </c>
       <c r="M56" s="13" t="n">
-        <v>145613735000</v>
+        <v>224823000000</v>
       </c>
       <c r="N56" s="13" t="n">
-        <v>59466770010</v>
+        <v>30402825000</v>
       </c>
       <c r="O56" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:24:02</t>
+          <t>2026-09-06 09:22:06</t>
         </is>
       </c>
       <c r="Q56" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:24:02 (کد پیگیری: 49685355362164)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:06 (کد پیگیری: 49685355308315)</t>
         </is>
       </c>
     </row>
@@ -5399,30 +5403,30 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>5560050044994051</t>
+          <t>9515050044994052</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>902051</t>
+          <t>902052</t>
         </is>
       </c>
       <c r="G57" s="12" t="n">
-        <v>6200000000</v>
+        <v>6800000000</v>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>1405/06/10</t>
+          <t>1405/08/05</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>منقضی (5 روز گذشته)</t>
+          <t>51 روز مانده</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>* سپه بلوار فرودگاه</t>
+          <t>* سپه بلوار فرودگاه مشهد</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
@@ -5432,11 +5436,11 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M57" s="12" t="n">
-        <v>235323000000</v>
+        <v>224823000000</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>30402825000</v>
@@ -5446,12 +5450,12 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:51:57</t>
+          <t>2026-09-06 09:22:16</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-08-28 20:51:57) (کد پیگیری قبلی: 49664982347170)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:16 (کد پیگیری: 49685355321681)</t>
         </is>
       </c>
     </row>
@@ -5476,30 +5480,30 @@
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>4204010168700706</t>
+          <t>8940050044994059</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>076149</t>
+          <t>902059</t>
         </is>
       </c>
       <c r="G58" s="13" t="n">
-        <v>11520000000</v>
+        <v>17800000000</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>1405/07/25</t>
+          <t>1405/12/15</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>41 روز مانده</t>
+          <t>181 روز مانده</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>* صادرات شهرک صنعتي طرق</t>
+          <t>* سپه بلوار فرودگاه مشهد</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr">
@@ -5523,12 +5527,12 @@
       </c>
       <c r="P58" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:06</t>
+          <t>2026-09-06 09:23:44</t>
         </is>
       </c>
       <c r="Q58" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:06 (کد پیگیری: 49685355308315)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:44 (کد پیگیری: 49685355345947)</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5542,12 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>عباس مقنی</t>
+          <t>عطاری ید اله</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>0922030936</t>
+          <t>2298907366</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -5553,30 +5557,30 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>9515050044994052</t>
+          <t>2011030010355250</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>902052</t>
+          <t>810231</t>
         </is>
       </c>
       <c r="G59" s="12" t="n">
-        <v>6800000000</v>
+        <v>2000000000</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>1405/08/05</t>
+          <t>1405/06/02</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>51 روز مانده</t>
+          <t>منقضی (13 روز گذشته)</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>* سپه بلوار فرودگاه مشهد</t>
+          <t>* صادرات صفاشم</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
@@ -5586,26 +5590,22 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M59" s="12" t="n">
-        <v>224823000000</v>
+        <v>0</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>30402825000</v>
+        <v>0</v>
       </c>
       <c r="O59" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:16</t>
-        </is>
-      </c>
+      <c r="P59" s="6" t="inlineStr"/>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:16 (کد پیگیری: 49685355321681)</t>
+          <t>سررسید چک در تاریخ 1405/06/02 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -5615,12 +5615,12 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>عباس مقنی</t>
+          <t>عطاری ید اله</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>0922030936</t>
+          <t>2298907366</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr">
@@ -5630,30 +5630,30 @@
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>8940050044994059</t>
+          <t>8509030010355251</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>902059</t>
+          <t>810232</t>
         </is>
       </c>
       <c r="G60" s="13" t="n">
-        <v>17800000000</v>
+        <v>2000000000</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>1405/12/15</t>
+          <t>1405/07/02</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>181 روز مانده</t>
+          <t>18 روز مانده</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>* سپه بلوار فرودگاه مشهد</t>
+          <t>* صادرات صفاشم</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
@@ -5667,22 +5667,22 @@
         </is>
       </c>
       <c r="M60" s="13" t="n">
-        <v>224823000000</v>
+        <v>28000000000</v>
       </c>
       <c r="N60" s="13" t="n">
-        <v>30402825000</v>
+        <v>240000000</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:44</t>
+          <t>2026-09-06 09:21:39</t>
         </is>
       </c>
       <c r="Q60" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:44 (کد پیگیری: 49685355345947)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:39 (کد پیگیری: 49685355295883)</t>
         </is>
       </c>
     </row>
@@ -5707,12 +5707,12 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2011030010355250</t>
+          <t>5533030010355252</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>810231</t>
+          <t>810233</t>
         </is>
       </c>
       <c r="G61" s="12" t="n">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>1405/06/02</t>
+          <t>1405/08/02</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>منقضی (13 روز گذشته)</t>
+          <t>48 روز مانده</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
@@ -5740,22 +5740,26 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M61" s="12" t="n">
-        <v>0</v>
+        <v>28000000000</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
+        <v>240000000</v>
       </c>
       <c r="O61" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P61" s="6" t="inlineStr"/>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:22:13</t>
+        </is>
+      </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/02 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:13 (کد پیگیری: 49685355317164)</t>
         </is>
       </c>
     </row>
@@ -5780,12 +5784,12 @@
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>8509030010355251</t>
+          <t>4680030010355253</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>810232</t>
+          <t>810234</t>
         </is>
       </c>
       <c r="G62" s="13" t="n">
@@ -5793,12 +5797,12 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>1405/07/02</t>
+          <t>1405/09/02</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>18 روز مانده</t>
+          <t>78 روز مانده</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
@@ -5827,12 +5831,12 @@
       </c>
       <c r="P62" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:39</t>
+          <t>2026-09-06 09:22:42</t>
         </is>
       </c>
       <c r="Q62" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:39 (کد پیگیری: 49685355295883)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:42 (کد پیگیری: 49685355330603)</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5861,12 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>5533030010355252</t>
+          <t>3201030010355254</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>810233</t>
+          <t>810235</t>
         </is>
       </c>
       <c r="G63" s="12" t="n">
@@ -5870,12 +5874,12 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>1405/08/02</t>
+          <t>1405/10/02</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>48 روز مانده</t>
+          <t>108 روز مانده</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -5904,12 +5908,12 @@
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:13</t>
+          <t>2026-09-06 09:23:18</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:13 (کد پیگیری: 49685355317164)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:18 (کد پیگیری: 49685355337378)</t>
         </is>
       </c>
     </row>
@@ -5934,12 +5938,12 @@
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>4680030010355253</t>
+          <t>9379030010355255</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>810234</t>
+          <t>810236</t>
         </is>
       </c>
       <c r="G64" s="13" t="n">
@@ -5947,12 +5951,12 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>1405/09/02</t>
+          <t>1405/11/02</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>78 روز مانده</t>
+          <t>138 روز مانده</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr">
@@ -5981,12 +5985,12 @@
       </c>
       <c r="P64" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:42</t>
+          <t>2026-09-06 09:23:36</t>
         </is>
       </c>
       <c r="Q64" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:42 (کد پیگیری: 49685355330603)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:36 (کد پیگیری: 49685355342412)</t>
         </is>
       </c>
     </row>
@@ -6011,12 +6015,12 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>3201030010355254</t>
+          <t>6144030010355257</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>810235</t>
+          <t>810238</t>
         </is>
       </c>
       <c r="G65" s="12" t="n">
@@ -6024,12 +6028,12 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>1405/10/02</t>
+          <t>1406/01/02</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>108 روز مانده</t>
+          <t>197 روز مانده</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
@@ -6058,12 +6062,12 @@
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:18</t>
+          <t>2026-09-06 09:23:46</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:18 (کد پیگیری: 49685355337378)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:46 (کد پیگیری: 49685355351800)</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6092,12 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>9379030010355255</t>
+          <t>3090030010355258</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>810236</t>
+          <t>810239</t>
         </is>
       </c>
       <c r="G66" s="13" t="n">
@@ -6101,12 +6105,12 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>1405/11/02</t>
+          <t>1406/02/02</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>138 روز مانده</t>
+          <t>228 روز مانده</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -6135,12 +6139,12 @@
       </c>
       <c r="P66" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:36</t>
+          <t>2026-09-06 09:23:49</t>
         </is>
       </c>
       <c r="Q66" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:36 (کد پیگیری: 49685355342412)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:49 (کد پیگیری: 49685355351842)</t>
         </is>
       </c>
     </row>
@@ -6165,12 +6169,12 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>6144030010355257</t>
+          <t>7644030010355259</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>810238</t>
+          <t>810240</t>
         </is>
       </c>
       <c r="G67" s="12" t="n">
@@ -6178,12 +6182,12 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>1406/01/02</t>
+          <t>1406/03/02</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>197 روز مانده</t>
+          <t>259 روز مانده</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
@@ -6212,12 +6216,12 @@
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:46</t>
+          <t>2026-09-06 09:23:50</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:46 (کد پیگیری: 49685355351800)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:50 (کد پیگیری: 49685355359143)</t>
         </is>
       </c>
     </row>
@@ -6242,12 +6246,12 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>3090030010355258</t>
+          <t>7525030010355260</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>810239</t>
+          <t>810241</t>
         </is>
       </c>
       <c r="G68" s="13" t="n">
@@ -6255,12 +6259,12 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>1406/02/02</t>
+          <t>1406/04/02</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>228 روز مانده</t>
+          <t>290 روز مانده</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
@@ -6289,12 +6293,12 @@
       </c>
       <c r="P68" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:49</t>
+          <t>2026-09-06 09:23:51</t>
         </is>
       </c>
       <c r="Q68" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:49 (کد پیگیری: 49685355351842)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:51 (کد پیگیری: 49685355356744)</t>
         </is>
       </c>
     </row>
@@ -6319,12 +6323,12 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>7644030010355259</t>
+          <t>9793030010355261</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>810240</t>
+          <t>810242</t>
         </is>
       </c>
       <c r="G69" s="12" t="n">
@@ -6332,12 +6336,12 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>1406/03/02</t>
+          <t>1406/05/02</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>259 روز مانده</t>
+          <t>321 روز مانده</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
@@ -6347,7 +6351,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -6366,12 +6370,12 @@
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:50</t>
+          <t>2026-09-06 19:14:03</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:50 (کد پیگیری: 49685355359143)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363374741)</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6400,12 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>7525030010355260</t>
+          <t>6392030010355262</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>810241</t>
+          <t>810243</t>
         </is>
       </c>
       <c r="G70" s="13" t="n">
@@ -6409,12 +6413,12 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>1406/04/02</t>
+          <t>1406/06/02</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>290 روز مانده</t>
+          <t>352 روز مانده</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
@@ -6424,7 +6428,7 @@
       </c>
       <c r="K70" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L70" s="11" t="inlineStr">
@@ -6443,12 +6447,12 @@
       </c>
       <c r="P70" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:51</t>
+          <t>2026-09-06 19:14:03</t>
         </is>
       </c>
       <c r="Q70" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:51 (کد پیگیری: 49685355356744)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363377638)</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6462,12 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>عطاری ید اله</t>
+          <t>عقيل نرمكي</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>2298907366</t>
+          <t>0920541526</t>
         </is>
       </c>
       <c r="D71" s="19" t="inlineStr">
@@ -6473,59 +6477,55 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>9793030010355261</t>
+          <t>5561040153416463</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>810242</t>
+          <t>030616</t>
         </is>
       </c>
       <c r="G71" s="12" t="n">
-        <v>2000000000</v>
+        <v>1160000000</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>1406/05/02</t>
+          <t>1405/06/06</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>321 روز مانده</t>
+          <t>منقضی (9 روز گذشته)</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>* صادرات صفاشم</t>
+          <t>* سپه سيدي مشهد</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M71" s="12" t="n">
-        <v>28000000000</v>
+        <v>0</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>240000000</v>
+        <v>0</v>
       </c>
       <c r="O71" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P71" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 19:14:03</t>
-        </is>
-      </c>
+      <c r="P71" s="6" t="inlineStr"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363374741)</t>
+          <t>سررسید چک در تاریخ 1405/06/06 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>عطاری ید اله</t>
+          <t>عقيل نرمكي</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>2298907366</t>
+          <t>0920541526</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
@@ -6550,35 +6550,35 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>6392030010355262</t>
+          <t>5320040153416464</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>810243</t>
+          <t>030617</t>
         </is>
       </c>
       <c r="G72" s="13" t="n">
-        <v>2000000000</v>
+        <v>1160000000</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>1406/06/02</t>
+          <t>1405/07/06</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>352 روز مانده</t>
+          <t>22 روز مانده</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>* صادرات صفاشم</t>
+          <t>* سپه سيدي مشهد</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
@@ -6587,22 +6587,22 @@
         </is>
       </c>
       <c r="M72" s="13" t="n">
-        <v>28000000000</v>
+        <v>61089499998</v>
       </c>
       <c r="N72" s="13" t="n">
-        <v>240000000</v>
+        <v>1018900000</v>
       </c>
       <c r="O72" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 19:14:03</t>
+          <t>2026-09-06 09:21:45</t>
         </is>
       </c>
       <c r="Q72" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363377638)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:45 (کد پیگیری: 49685355304716)</t>
         </is>
       </c>
     </row>
@@ -6627,12 +6627,12 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>5561040153416463</t>
+          <t>3478040153416465</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>030616</t>
+          <t>030618</t>
         </is>
       </c>
       <c r="G73" s="12" t="n">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>1405/06/06</t>
+          <t>1405/08/06</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>منقضی (9 روز گذشته)</t>
+          <t>52 روز مانده</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
@@ -6660,22 +6660,26 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0</v>
+        <v>61089499998</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
+        <v>1018900000</v>
       </c>
       <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P73" s="6" t="inlineStr"/>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:22:19</t>
+        </is>
+      </c>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/06 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:19 (کد پیگیری: 49685355310375)</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6704,12 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>5320040153416464</t>
+          <t>2610040153416467</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>030617</t>
+          <t>030620</t>
         </is>
       </c>
       <c r="G74" s="13" t="n">
@@ -6713,12 +6717,12 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>1405/07/06</t>
+          <t>1405/10/06</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>22 روز مانده</t>
+          <t>112 روز مانده</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
@@ -6747,12 +6751,12 @@
       </c>
       <c r="P74" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:45</t>
+          <t>2026-09-06 09:23:23</t>
         </is>
       </c>
       <c r="Q74" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:45 (کد پیگیری: 49685355304716)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:23 (کد پیگیری: 49685355339937)</t>
         </is>
       </c>
     </row>
@@ -6762,14 +6766,10 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>عقيل نرمكي</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>0920541526</t>
-        </is>
-      </c>
+          <t>عليرضا ضرغام مقدم</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr"/>
       <c r="D75" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -6777,30 +6777,30 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>3478040153416465</t>
+          <t>7283030156765780</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>030618</t>
+          <t>444417</t>
         </is>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1160000000</v>
+        <v>350000000</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>1405/08/06</t>
+          <t>1405/06/25</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>52 روز مانده</t>
+          <t>10 روز مانده</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>* سپه سيدي مشهد</t>
+          <t>* سپه فرهنگيان مشهد</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -6810,26 +6810,22 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M75" s="12" t="n">
-        <v>61089499998</v>
+        <v>0</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1018900000</v>
+        <v>0</v>
       </c>
       <c r="O75" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P75" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:19</t>
-        </is>
-      </c>
+      <c r="P75" s="6" t="inlineStr"/>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:19 (کد پیگیری: 49685355310375)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -6839,45 +6835,37 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>عقيل نرمكي</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>0920541526</t>
-        </is>
-      </c>
+          <t>عليرضا يعقوبي</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr"/>
       <c r="D76" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>2610040153416467</t>
-        </is>
-      </c>
+      <c r="E76" s="10" t="inlineStr"/>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>030620</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="G76" s="13" t="n">
-        <v>1160000000</v>
+        <v>870000000</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>1405/10/06</t>
+          <t>1405/06/01</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>112 روز مانده</t>
+          <t>منقضی (14 روز گذشته)</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>* سپه سيدي مشهد</t>
+          <t>* کشاورزي دکتر حسابي</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
@@ -6887,26 +6875,22 @@
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سند سفته / فاقد صیاد (معاف)</t>
         </is>
       </c>
       <c r="M76" s="13" t="n">
-        <v>61089499998</v>
+        <v>0</v>
       </c>
       <c r="N76" s="13" t="n">
-        <v>1018900000</v>
+        <v>0</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P76" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:23:23</t>
-        </is>
-      </c>
+      <c r="P76" s="10" t="inlineStr"/>
       <c r="Q76" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:23 (کد پیگیری: 49685355339937)</t>
+          <t>سند تضمینی یا سفته فاقد شناسه ۱۶ رقمی صیاد</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6900,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>عليرضا ضرغام مقدم</t>
+          <t>عليرضا يعقوبي</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr"/>
@@ -6927,55 +6911,59 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>7283030156765780</t>
+          <t>2033040067329144</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>444417</t>
+          <t>243520</t>
         </is>
       </c>
       <c r="G77" s="12" t="n">
-        <v>350000000</v>
+        <v>870000000</v>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>1405/06/25</t>
+          <t>1405/09/02</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>10 روز مانده</t>
+          <t>78 روز مانده</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>* سپه فرهنگيان مشهد</t>
+          <t>* کشاورزي دکتر حسابي</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0</v>
+        <v>26680000000</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>0</v>
+        <v>37000000</v>
       </c>
       <c r="O77" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P77" s="6" t="inlineStr"/>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:22:41</t>
+        </is>
+      </c>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:41 (کد پیگیری: 49685355328166)</t>
         </is>
       </c>
     </row>
@@ -6985,7 +6973,7 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>عليرضا يعقوبي</t>
+          <t>فر هنگ نیا مهزیار</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr"/>
@@ -6994,28 +6982,32 @@
           <t>سفید</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr"/>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>3778020108164326</t>
+        </is>
+      </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>756139</t>
         </is>
       </c>
       <c r="G78" s="13" t="n">
-        <v>870000000</v>
+        <v>895000000</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>1405/06/01</t>
+          <t>1405/06/05</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>منقضی (14 روز گذشته)</t>
+          <t>منقضی (10 روز گذشته)</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>* کشاورزي دکتر حسابي</t>
+          <t>* صادرات کوي اب و برق</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
@@ -7025,7 +7017,7 @@
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>سند سفته / فاقد صیاد (معاف)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M78" s="13" t="n">
@@ -7040,7 +7032,7 @@
       <c r="P78" s="10" t="inlineStr"/>
       <c r="Q78" s="11" t="inlineStr">
         <is>
-          <t>سند تضمینی یا سفته فاقد شناسه ۱۶ رقمی صیاد</t>
+          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -7050,10 +7042,14 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>عليرضا يعقوبي</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr"/>
+          <t>فريد والي</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>0010485295</t>
+        </is>
+      </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -7061,59 +7057,59 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>2033040067329144</t>
+          <t>8842040083741990</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>243520</t>
+          <t>682185</t>
         </is>
       </c>
       <c r="G79" s="12" t="n">
-        <v>870000000</v>
+        <v>4000000000</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>1405/09/02</t>
+          <t>1405/06/30</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>78 روز مانده</t>
+          <t>15 روز مانده</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>* کشاورزي دکتر حسابي</t>
+          <t>* سپه رودکي</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M79" s="12" t="n">
-        <v>26680000000</v>
+        <v>58720000000</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>37000000</v>
+        <v>750000000</v>
       </c>
       <c r="O79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:41</t>
+          <t>2026-09-05 08:46:41</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:41 (کد پیگیری: 49685355328166)</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:41) (کد پیگیری قبلی: 49682942080036)</t>
         </is>
       </c>
     </row>
@@ -7123,10 +7119,14 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>فر هنگ نیا مهزیار</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr"/>
+          <t>محمد ابراهيمي دشت بياض</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>0880141281</t>
+        </is>
+      </c>
       <c r="D80" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -7134,55 +7134,59 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>3778020108164326</t>
+          <t>5179050070509551</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>756139</t>
+          <t>266951</t>
         </is>
       </c>
       <c r="G80" s="13" t="n">
-        <v>895000000</v>
+        <v>487500000</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>1405/06/05</t>
+          <t>1405/07/16</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>منقضی (10 روز گذشته)</t>
+          <t>32 روز مانده</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>* صادرات کوي اب و برق</t>
+          <t>* کشاورزي خضري</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M80" s="13" t="n">
-        <v>0</v>
+        <v>101507099414</v>
       </c>
       <c r="N80" s="13" t="n">
-        <v>0</v>
+        <v>26820000000</v>
       </c>
       <c r="O80" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P80" s="10" t="inlineStr"/>
+      <c r="P80" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:21:55</t>
+        </is>
+      </c>
       <c r="Q80" s="11" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/05 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:55 (کد پیگیری: 49685355305280)</t>
         </is>
       </c>
     </row>
@@ -7192,12 +7196,12 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>فريد والي</t>
+          <t>محمد ابراهيمي دشت بياض</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>0010485295</t>
+          <t>0880141281</t>
         </is>
       </c>
       <c r="D81" s="19" t="inlineStr">
@@ -7207,59 +7211,59 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>8842040083741990</t>
+          <t>3750050070509552</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>682185</t>
+          <t>266952</t>
         </is>
       </c>
       <c r="G81" s="12" t="n">
-        <v>4000000000</v>
+        <v>487500000</v>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>1405/06/30</t>
+          <t>1405/08/16</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>15 روز مانده</t>
+          <t>62 روز مانده</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>* سپه رودکي</t>
+          <t>* کشاورزي خضري</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>عادل رمضانزاده</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M81" s="12" t="n">
-        <v>58720000000</v>
+        <v>101507099414</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>750000000</v>
+        <v>26820000000</v>
       </c>
       <c r="O81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 08:46:41</t>
+          <t>2026-09-06 09:22:27</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:46:41) (کد پیگیری قبلی: 49682942080036)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:27 (کد پیگیری: 49685355323218)</t>
         </is>
       </c>
     </row>
@@ -7284,12 +7288,12 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>5179050070509551</t>
+          <t>2462050070509553</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>266951</t>
+          <t>266953</t>
         </is>
       </c>
       <c r="G82" s="13" t="n">
@@ -7297,12 +7301,12 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>1405/07/16</t>
+          <t>1405/09/16</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>32 روز مانده</t>
+          <t>92 روز مانده</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -7331,12 +7335,12 @@
       </c>
       <c r="P82" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:55</t>
+          <t>2026-09-06 09:23:00</t>
         </is>
       </c>
       <c r="Q82" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:55 (کد پیگیری: 49685355305280)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:00 (کد پیگیری: 49685355327928)</t>
         </is>
       </c>
     </row>
@@ -7361,12 +7365,12 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>3750050070509552</t>
+          <t>3194050070509554</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>266952</t>
+          <t>266954</t>
         </is>
       </c>
       <c r="G83" s="12" t="n">
@@ -7374,12 +7378,12 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>1405/08/16</t>
+          <t>1405/10/16</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>62 روز مانده</t>
+          <t>122 روز مانده</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
@@ -7408,12 +7412,12 @@
       </c>
       <c r="P83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:27</t>
+          <t>2026-09-06 09:23:27</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:27 (کد پیگیری: 49685355323218)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:27 (کد پیگیری: 49685355351557)</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7427,12 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>محمد ابراهيمي دشت بياض</t>
+          <t>محمد حميدي شيرغان</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>0880141281</t>
+          <t>0924049650</t>
         </is>
       </c>
       <c r="D84" s="19" t="inlineStr">
@@ -7438,35 +7442,35 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>2462050070509553</t>
+          <t>7646040094693690</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>266953</t>
+          <t>093814</t>
         </is>
       </c>
       <c r="G84" s="13" t="n">
-        <v>487500000</v>
+        <v>3720000000</v>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>1405/09/16</t>
+          <t>1405/07/24</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>92 روز مانده</t>
+          <t>40 روز مانده</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>* کشاورزي خضري</t>
+          <t>* سپه بازار بزرگ اطلس</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L84" s="11" t="inlineStr">
@@ -7475,22 +7479,22 @@
         </is>
       </c>
       <c r="M84" s="13" t="n">
-        <v>101507099414</v>
+        <v>17880000000</v>
       </c>
       <c r="N84" s="13" t="n">
-        <v>26820000000</v>
+        <v>10283000000</v>
       </c>
       <c r="O84" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:00</t>
+          <t>2026-09-06 09:22:00</t>
         </is>
       </c>
       <c r="Q84" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:00 (کد پیگیری: 49685355327928)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:00 (کد پیگیری: 49685355305344)</t>
         </is>
       </c>
     </row>
@@ -7500,12 +7504,12 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>محمد ابراهيمي دشت بياض</t>
+          <t>محمد حميدي شيرغان</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>0880141281</t>
+          <t>0924049650</t>
         </is>
       </c>
       <c r="D85" s="19" t="inlineStr">
@@ -7515,59 +7519,55 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>3194050070509554</t>
+          <t>7704040137481904</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>266954</t>
+          <t>415570</t>
         </is>
       </c>
       <c r="G85" s="12" t="n">
-        <v>487500000</v>
+        <v>220000000</v>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>1405/10/16</t>
+          <t>1405/07/24</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>122 روز مانده</t>
+          <t>40 روز مانده</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>* کشاورزي خضري</t>
+          <t>* پاسارگاد احمداباد</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>عادل رمضانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M85" s="12" t="n">
-        <v>101507099414</v>
+        <v>0</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>26820000000</v>
+        <v>0</v>
       </c>
       <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P85" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:23:27</t>
-        </is>
-      </c>
+      <c r="P85" s="6" t="inlineStr"/>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:27 (کد پیگیری: 49685355351557)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -7577,45 +7577,45 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>محمد حميدي شيرغان</t>
+          <t>محمد رفیق طرقی</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>0924049650</t>
-        </is>
-      </c>
-      <c r="D86" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>0890543331</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>7646040094693690</t>
+          <t>7510050000558312</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>093814</t>
+          <t>750111</t>
         </is>
       </c>
       <c r="G86" s="13" t="n">
-        <v>3720000000</v>
+        <v>15000000000</v>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>1405/07/24</t>
+          <t>1405/07/22</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>40 روز مانده</t>
+          <t>38 روز مانده</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>* سپه بازار بزرگ اطلس</t>
+          <t>* تجارت خيابان تهران</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr">
@@ -7629,22 +7629,22 @@
         </is>
       </c>
       <c r="M86" s="13" t="n">
-        <v>17880000000</v>
+        <v>265665000000</v>
       </c>
       <c r="N86" s="13" t="n">
-        <v>10283000000</v>
+        <v>81847500000</v>
       </c>
       <c r="O86" s="13" t="n">
-        <v>0</v>
+        <v>40300000000</v>
       </c>
       <c r="P86" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:00</t>
+          <t>2026-09-06 09:21:59</t>
         </is>
       </c>
       <c r="Q86" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:00 (کد پیگیری: 49685355305344)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:59 (کد پیگیری: 49685355307268)</t>
         </is>
       </c>
     </row>
@@ -7654,45 +7654,45 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>محمد حميدي شيرغان</t>
+          <t>محمد زاهدي آغوي</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>0924049650</t>
-        </is>
-      </c>
-      <c r="D87" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>0690489838</t>
+        </is>
+      </c>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>7704040137481904</t>
+          <t>2745040155889930</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>415570</t>
+          <t>218783</t>
         </is>
       </c>
       <c r="G87" s="12" t="n">
-        <v>220000000</v>
+        <v>1890000000</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>1405/07/24</t>
+          <t>1405/06/17</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>40 روز مانده</t>
+          <t>سررسید نزدیک (2 روز مانده)</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>* پاسارگاد احمداباد</t>
+          <t>* کشاورزي ترمينال</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
@@ -7702,22 +7702,26 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0</v>
+        <v>59290930000</v>
       </c>
       <c r="N87" s="12" t="n">
-        <v>0</v>
+        <v>52840962000</v>
       </c>
       <c r="O87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="6" t="inlineStr"/>
+        <v>9398000000</v>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:21:18</t>
+        </is>
+      </c>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:18 (کد پیگیری: 49685355297097)</t>
         </is>
       </c>
     </row>
@@ -7727,12 +7731,12 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>محمد رفیق طرقی</t>
+          <t>محمد زاهدي آغوي</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>0890543331</t>
+          <t>0690489838</t>
         </is>
       </c>
       <c r="D88" s="18" t="inlineStr">
@@ -7742,35 +7746,35 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>7510050000558312</t>
+          <t>6170040155889947</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>750111</t>
+          <t>218800</t>
         </is>
       </c>
       <c r="G88" s="13" t="n">
-        <v>15000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>1405/07/22</t>
+          <t>1405/08/25</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>38 روز مانده</t>
+          <t>71 روز مانده</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>* تجارت خيابان تهران</t>
+          <t>* کشاورزي ترمينال مشهد</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>علیرضا ضیافتی</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr">
@@ -7779,22 +7783,22 @@
         </is>
       </c>
       <c r="M88" s="13" t="n">
-        <v>265665000000</v>
+        <v>59290930000</v>
       </c>
       <c r="N88" s="13" t="n">
-        <v>81847500000</v>
+        <v>52840962000</v>
       </c>
       <c r="O88" s="13" t="n">
-        <v>40300000000</v>
+        <v>9398000000</v>
       </c>
       <c r="P88" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:59</t>
+          <t>2026-09-06 09:22:30</t>
         </is>
       </c>
       <c r="Q88" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:59 (کد پیگیری: 49685355307268)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:30 (کد پیگیری: 49685355323269)</t>
         </is>
       </c>
     </row>
@@ -7804,12 +7808,12 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>محمد زاهدي آغوي</t>
+          <t>محمد ضيافتي مالدار</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>0690489838</t>
+          <t>0922236992</t>
         </is>
       </c>
       <c r="D89" s="18" t="inlineStr">
@@ -7819,30 +7823,30 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>2745040155889930</t>
+          <t>5138040187866685</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>218783</t>
+          <t>180057</t>
         </is>
       </c>
       <c r="G89" s="12" t="n">
-        <v>1890000000</v>
+        <v>16000000000</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>1405/06/17</t>
+          <t>1405/05/01</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>سررسید نزدیک (2 روز مانده)</t>
+          <t>منقضی (45 روز گذشته)</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>* کشاورزي ترمينال</t>
+          <t>* بانک ملي کوي المهدي</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
@@ -7856,22 +7860,22 @@
         </is>
       </c>
       <c r="M89" s="12" t="n">
-        <v>59290930000</v>
+        <v>1144807000000</v>
       </c>
       <c r="N89" s="12" t="n">
-        <v>52840962000</v>
+        <v>305078252000</v>
       </c>
       <c r="O89" s="12" t="n">
-        <v>9398000000</v>
+        <v>19160000000</v>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:18</t>
+          <t>2026-09-06 09:20:54</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:18 (کد پیگیری: 49685355297097)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:54 (کد پیگیری: 49685355273867)</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7885,12 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>محمد زاهدي آغوي</t>
+          <t>محمد ضيافتي مالدار</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>0690489838</t>
+          <t>0922236992</t>
         </is>
       </c>
       <c r="D90" s="18" t="inlineStr">
@@ -7896,35 +7900,35 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>6170040155889947</t>
+          <t>5080030099110169</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>218800</t>
+          <t>970083</t>
         </is>
       </c>
       <c r="G90" s="13" t="n">
-        <v>7000000000</v>
+        <v>5660000000</v>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>1405/08/25</t>
+          <t>1405/06/01</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>71 روز مانده</t>
+          <t>منقضی (14 روز گذشته)</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>* کشاورزي ترمينال مشهد</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>علیرضا ضیافتی</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L90" s="11" t="inlineStr">
@@ -7933,22 +7937,22 @@
         </is>
       </c>
       <c r="M90" s="13" t="n">
-        <v>59290930000</v>
+        <v>1144807000000</v>
       </c>
       <c r="N90" s="13" t="n">
-        <v>52840962000</v>
+        <v>305078252000</v>
       </c>
       <c r="O90" s="13" t="n">
-        <v>9398000000</v>
+        <v>19160000000</v>
       </c>
       <c r="P90" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:30</t>
+          <t>2026-09-06 09:20:58</t>
         </is>
       </c>
       <c r="Q90" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:30 (کد پیگیری: 49685355323269)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:58 (کد پیگیری: 49685355276364)</t>
         </is>
       </c>
     </row>
@@ -7973,30 +7977,30 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>5138040187866685</t>
+          <t>6200030099110171</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>180057</t>
+          <t>970085</t>
         </is>
       </c>
       <c r="G91" s="12" t="n">
-        <v>16000000000</v>
+        <v>5660000000</v>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>1405/05/01</t>
+          <t>1405/08/01</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>منقضی (45 روز گذشته)</t>
+          <t>47 روز مانده</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
@@ -8020,12 +8024,12 @@
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:20:54</t>
+          <t>2026-09-06 09:22:10</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:54 (کد پیگیری: 49685355273867)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:10 (کد پیگیری: 49685355321584)</t>
         </is>
       </c>
     </row>
@@ -8050,30 +8054,30 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>5080030099110169</t>
+          <t>0885050004531113</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>970083</t>
+          <t>855067</t>
         </is>
       </c>
       <c r="G92" s="13" t="n">
-        <v>5660000000</v>
+        <v>5500000000</v>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>1405/06/01</t>
+          <t>1405/08/25</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
         <is>
-          <t>منقضی (14 روز گذشته)</t>
+          <t>71 روز مانده</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* ملت شيرازي</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr">
@@ -8083,26 +8087,22 @@
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M92" s="13" t="n">
-        <v>1144807000000</v>
+        <v>0</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>305078252000</v>
+        <v>0</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>19160000000</v>
-      </c>
-      <c r="P92" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:20:58</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P92" s="10" t="inlineStr"/>
       <c r="Q92" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:20:58 (کد پیگیری: 49685355276364)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>6200030099110171</t>
+          <t>2718030099110172</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>970085</t>
+          <t>970086</t>
         </is>
       </c>
       <c r="G93" s="12" t="n">
@@ -8140,17 +8140,17 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/09/01</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>47 روز مانده</t>
+          <t>77 روز مانده</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* بانک ملي کوي المهدي</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="P93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:10</t>
+          <t>2026-09-06 09:22:38</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:10 (کد پیگیری: 49685355321584)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:38 (کد پیگیری: 49685355330069)</t>
         </is>
       </c>
     </row>
@@ -8204,30 +8204,30 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>0885050004531113</t>
+          <t>0411800094693691</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>855067</t>
+          <t>093815</t>
         </is>
       </c>
       <c r="G94" s="13" t="n">
-        <v>5500000000</v>
+        <v>3720000000</v>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>1405/08/25</t>
+          <t>1405/09/24</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
         <is>
-          <t>71 روز مانده</t>
+          <t>100 روز مانده</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>* ملت شيرازي</t>
+          <t>* سپه بازار بزرگ اطلس</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>2718030099110172</t>
+          <t>5222030099110173</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>970086</t>
+          <t>970087</t>
         </is>
       </c>
       <c r="G95" s="12" t="n">
@@ -8290,17 +8290,17 @@
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>1405/09/01</t>
+          <t>1405/10/01</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>77 روز مانده</t>
+          <t>107 روز مانده</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="P95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:38</t>
+          <t>2026-09-06 09:23:12</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:38 (کد پیگیری: 49685355330069)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:12 (کد پیگیری: 49685355338321)</t>
         </is>
       </c>
     </row>
@@ -8354,30 +8354,30 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>0411800094693691</t>
+          <t>9569030099110174</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>093815</t>
+          <t>970088</t>
         </is>
       </c>
       <c r="G96" s="13" t="n">
-        <v>3720000000</v>
+        <v>5660000000</v>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>1405/09/24</t>
+          <t>1405/11/01</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
         <is>
-          <t>100 روز مانده</t>
+          <t>137 روز مانده</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>* سپه بازار بزرگ اطلس</t>
+          <t>* بانک ملي کوي المهدي 8601</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr">
@@ -8387,22 +8387,26 @@
       </c>
       <c r="L96" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل ۹ دارنده</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M96" s="13" t="n">
-        <v>0</v>
+        <v>1144807000000</v>
       </c>
       <c r="N96" s="13" t="n">
-        <v>0</v>
+        <v>305078252000</v>
       </c>
       <c r="O96" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="10" t="inlineStr"/>
+        <v>19160000000</v>
+      </c>
+      <c r="P96" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-06 09:23:33</t>
+        </is>
+      </c>
       <c r="Q96" s="11" t="inlineStr">
         <is>
-          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:33 (کد پیگیری: 49685355355077)</t>
         </is>
       </c>
     </row>
@@ -8412,45 +8416,41 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>محمد ضيافتي مالدار</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>0922236992</t>
-        </is>
-      </c>
-      <c r="D97" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>محمد طاهري</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr"/>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>5222030099110173</t>
+          <t>7413040073308914</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>970087</t>
+          <t>793454</t>
         </is>
       </c>
       <c r="G97" s="12" t="n">
-        <v>5660000000</v>
+        <v>6000000000</v>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>1405/10/01</t>
+          <t>1405/06/01</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>107 روز مانده</t>
+          <t>منقضی (14 روز گذشته)</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* بانک ملي شهداي گمنام تربت حيدريه</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
@@ -8460,26 +8460,22 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>سررسید گذشته / تسویه</t>
         </is>
       </c>
       <c r="M97" s="12" t="n">
-        <v>1144807000000</v>
+        <v>0</v>
       </c>
       <c r="N97" s="12" t="n">
-        <v>305078252000</v>
+        <v>0</v>
       </c>
       <c r="O97" s="12" t="n">
-        <v>19160000000</v>
-      </c>
-      <c r="P97" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:23:12</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P97" s="6" t="inlineStr"/>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:12 (کد پیگیری: 49685355338321)</t>
+          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل جاری خارج است</t>
         </is>
       </c>
     </row>
@@ -8489,45 +8485,45 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>محمد ضيافتي مالدار</t>
+          <t>محمدباقر مشيري</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>0922236992</t>
-        </is>
-      </c>
-      <c r="D98" s="18" t="inlineStr">
-        <is>
-          <t>قرمز</t>
+          <t>0922010536</t>
+        </is>
+      </c>
+      <c r="D98" s="19" t="inlineStr">
+        <is>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>9569030099110174</t>
+          <t>7220040201829551</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>970088</t>
+          <t>849737</t>
         </is>
       </c>
       <c r="G98" s="13" t="n">
-        <v>5660000000</v>
+        <v>2190000000</v>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>1405/11/01</t>
+          <t>1405/06/25</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
         <is>
-          <t>137 روز مانده</t>
+          <t>10 روز مانده</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>* بانک ملي کوي المهدي 8601</t>
+          <t>* مسکن وکيل اباد</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr">
@@ -8541,22 +8537,22 @@
         </is>
       </c>
       <c r="M98" s="13" t="n">
-        <v>1144807000000</v>
+        <v>48136400000</v>
       </c>
       <c r="N98" s="13" t="n">
-        <v>305078252000</v>
+        <v>35000000</v>
       </c>
       <c r="O98" s="13" t="n">
-        <v>19160000000</v>
+        <v>0</v>
       </c>
       <c r="P98" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:33</t>
+          <t>2026-09-06 09:21:24</t>
         </is>
       </c>
       <c r="Q98" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:33 (کد پیگیری: 49685355355077)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:24 (کد پیگیری: 49685355289857)</t>
         </is>
       </c>
     </row>
@@ -8566,10 +8562,14 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>محمد طاهري</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr"/>
+          <t>محمدباقر مشيري</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>0922010536</t>
+        </is>
+      </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
           <t>سفید</t>
@@ -8577,30 +8577,30 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>7413040073308914</t>
+          <t>2359050004531111</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>793454</t>
+          <t>855065</t>
         </is>
       </c>
       <c r="G99" s="12" t="n">
-        <v>6000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>1405/06/01</t>
+          <t>1405/06/25</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>منقضی (14 روز گذشته)</t>
+          <t>10 روز مانده</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>* بانک ملي شهداي گمنام تربت حيدريه</t>
+          <t>* ملت شيرازي</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
@@ -8610,22 +8610,26 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>سررسید گذشته / تسویه</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0</v>
+        <v>93388000000</v>
       </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
+        <v>9840000000</v>
       </c>
       <c r="O99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="6" t="inlineStr"/>
+        <v>1326000000</v>
+      </c>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-05 08:45:48</t>
+        </is>
+      </c>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>سررسید چک در تاریخ 1405/06/01 منقضی شده و از کارتابل جاری خارج است</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:45:48) (کد پیگیری قبلی: 49682942065011)</t>
         </is>
       </c>
     </row>
@@ -8650,12 +8654,12 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>7220040201829551</t>
+          <t>9910040201829536</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>849737</t>
+          <t>849738</t>
         </is>
       </c>
       <c r="G100" s="13" t="n">
@@ -8663,12 +8667,12 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>1405/06/25</t>
+          <t>1405/07/25</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
         <is>
-          <t>10 روز مانده</t>
+          <t>41 روز مانده</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr">
@@ -8697,12 +8701,12 @@
       </c>
       <c r="P100" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:21:24</t>
+          <t>2026-09-06 09:22:04</t>
         </is>
       </c>
       <c r="Q100" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:21:24 (کد پیگیری: 49685355289857)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:04 (کد پیگیری: 49685355310220)</t>
         </is>
       </c>
     </row>
@@ -8727,30 +8731,30 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>2359050004531111</t>
+          <t>2757040201829543</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>855065</t>
+          <t>849739</t>
         </is>
       </c>
       <c r="G101" s="12" t="n">
-        <v>5500000000</v>
+        <v>2190000000</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>1405/06/25</t>
+          <t>1405/08/25</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>10 روز مانده</t>
+          <t>71 روز مانده</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>* ملت شيرازي</t>
+          <t>* مسکن وکيل اباد</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
@@ -8760,26 +8764,26 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M101" s="12" t="n">
-        <v>93388000000</v>
+        <v>48136400000</v>
       </c>
       <c r="N101" s="12" t="n">
-        <v>9840000000</v>
+        <v>35000000</v>
       </c>
       <c r="O101" s="12" t="n">
-        <v>1326000000</v>
+        <v>0</v>
       </c>
       <c r="P101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 08:45:48</t>
+          <t>2026-09-06 09:22:33</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:45:48) (کد پیگیری قبلی: 49682942065011)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:33 (کد پیگیری: 49685355326605)</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8808,12 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>9910040201829536</t>
+          <t>1161040201829557</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>849738</t>
+          <t>849748</t>
         </is>
       </c>
       <c r="G102" s="13" t="n">
@@ -8817,12 +8821,12 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>1405/07/25</t>
+          <t>1406/05/25</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
         <is>
-          <t>41 روز مانده</t>
+          <t>344 روز مانده</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
@@ -8832,7 +8836,7 @@
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
@@ -8851,12 +8855,12 @@
       </c>
       <c r="P102" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:04</t>
+          <t>2026-09-06 09:23:55</t>
         </is>
       </c>
       <c r="Q102" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:04 (کد پیگیری: 49685355310220)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:55 (کد پیگیری: 49685355356775)</t>
         </is>
       </c>
     </row>
@@ -8881,12 +8885,12 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>2757040201829543</t>
+          <t>5621040201829539</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>849739</t>
+          <t>849749</t>
         </is>
       </c>
       <c r="G103" s="12" t="n">
@@ -8894,12 +8898,12 @@
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>1405/08/25</t>
+          <t>1406/06/25</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>71 روز مانده</t>
+          <t>375 روز مانده</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -8909,7 +8913,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>علی رمضانزاده</t>
+          <t>مهدی زمانزاده</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -8928,12 +8932,12 @@
       </c>
       <c r="P103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 09:22:33</t>
+          <t>2026-09-06 19:14:03</t>
         </is>
       </c>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:33 (کد پیگیری: 49685355326605)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363379579)</t>
         </is>
       </c>
     </row>
@@ -8943,74 +8947,74 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>محمدباقر مشيري</t>
+          <t>محمدجواد وفادارعيدگاهي</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>0922010536</t>
-        </is>
-      </c>
-      <c r="D104" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>0924020865</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>1161040201829557</t>
+          <t>1907030071639288</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>849748</t>
+          <t>804984</t>
         </is>
       </c>
       <c r="G104" s="13" t="n">
-        <v>2190000000</v>
+        <v>1380000000</v>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>1406/05/25</t>
+          <t>1405/06/10</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
-          <t>344 روز مانده</t>
+          <t>منقضی (5 روز گذشته)</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>* مسکن وکيل اباد</t>
+          <t>* سپه امام رضا فريمان</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M104" s="13" t="n">
-        <v>48136400000</v>
+        <v>91680000000</v>
       </c>
       <c r="N104" s="13" t="n">
-        <v>35000000</v>
+        <v>43715000000</v>
       </c>
       <c r="O104" s="13" t="n">
-        <v>0</v>
+        <v>21630000000</v>
       </c>
       <c r="P104" s="10" t="inlineStr">
         <is>
-          <t>2026-09-06 09:23:55</t>
+          <t>2026-09-05 08:42:05</t>
         </is>
       </c>
       <c r="Q104" s="11" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:23:55 (کد پیگیری: 49685355356775)</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:42:05) (کد پیگیری قبلی: 49682941988821)</t>
         </is>
       </c>
     </row>
@@ -9020,74 +9024,74 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>محمدباقر مشيري</t>
+          <t>محمدجواد وفادارعيدگاهي</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>0922010536</t>
-        </is>
-      </c>
-      <c r="D105" s="19" t="inlineStr">
-        <is>
-          <t>سفید</t>
+          <t>0924020865</t>
+        </is>
+      </c>
+      <c r="D105" s="18" t="inlineStr">
+        <is>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>5621040201829539</t>
+          <t>5963030071639289</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>849749</t>
+          <t>804985</t>
         </is>
       </c>
       <c r="G105" s="12" t="n">
-        <v>2190000000</v>
+        <v>1380000000</v>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>1406/06/25</t>
+          <t>1405/07/10</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>375 روز مانده</t>
+          <t>26 روز مانده</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>* مسکن وکيل اباد</t>
+          <t>* سپه امام رضا فريمان</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>مهدی زمانزاده</t>
+          <t>علی رمضانزاده</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>حفظ تاریخچه معتبر قبلی</t>
         </is>
       </c>
       <c r="M105" s="12" t="n">
-        <v>48136400000</v>
+        <v>91680000000</v>
       </c>
       <c r="N105" s="12" t="n">
-        <v>35000000</v>
+        <v>43715000000</v>
       </c>
       <c r="O105" s="12" t="n">
-        <v>0</v>
+        <v>21630000000</v>
       </c>
       <c r="P105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06 19:14:03</t>
+          <t>2026-09-05 08:47:08</t>
         </is>
       </c>
       <c r="Q105" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 19:14:03 (کد پیگیری: 49686363379579)</t>
+          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:47:08) (کد پیگیری قبلی: 49682942084694)</t>
         </is>
       </c>
     </row>
@@ -9112,12 +9116,12 @@
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>5963030071639289</t>
+          <t>5755030071639290</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>804985</t>
+          <t>804986</t>
         </is>
       </c>
       <c r="G106" s="13" t="n">
@@ -9125,12 +9129,12 @@
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>1405/07/10</t>
+          <t>1405/08/10</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
         <is>
-          <t>26 روز مانده</t>
+          <t>56 روز مانده</t>
         </is>
       </c>
       <c r="J106" s="11" t="inlineStr">
@@ -9145,7 +9149,7 @@
       </c>
       <c r="L106" s="11" t="inlineStr">
         <is>
-          <t>حفظ تاریخچه معتبر قبلی</t>
+          <t>استعلام زنده امروز (بروز)</t>
         </is>
       </c>
       <c r="M106" s="13" t="n">
@@ -9159,12 +9163,12 @@
       </c>
       <c r="P106" s="10" t="inlineStr">
         <is>
-          <t>2026-09-05 08:47:08</t>
+          <t>2026-09-06 09:22:24</t>
         </is>
       </c>
       <c r="Q106" s="11" t="inlineStr">
         <is>
-          <t>عدم حضور در کارتابل امروز؛ حفظ آخرین استعلام معتبر (2026-09-05 08:47:08) (کد پیگیری قبلی: 49682942084694)</t>
+          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:24 (کد پیگیری: 49685355318270)</t>
         </is>
       </c>
     </row>
@@ -9189,12 +9193,12 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>5755030071639290</t>
+          <t>9910030071163929</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>804986</t>
+          <t>804987</t>
         </is>
       </c>
       <c r="G107" s="12" t="n">
@@ -9202,12 +9206,12 @@
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>1405/08/10</t>
+          <t>1405/09/10</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>56 روز مانده</t>
+          <t>86 روز مانده</t>
         </is>
       </c>
       <c r="J107" s="7" t="inlineStr">
@@ -9222,26 +9226,22 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز (بروز)</t>
+          <t>عدم حضور در کارتابل ۹ دارنده</t>
         </is>
       </c>
       <c r="M107" s="12" t="n">
-        <v>91680000000</v>
+        <v>0</v>
       </c>
       <c r="N107" s="12" t="n">
-        <v>43715000000</v>
+        <v>0</v>
       </c>
       <c r="O107" s="12" t="n">
-        <v>21630000000</v>
-      </c>
-      <c r="P107" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-06 09:22:24</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P107" s="6" t="inlineStr"/>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>استعلام زنده امروز درگاه پاسارگاد در ساعت 09:22:24 (کد پیگیری: 49685355318270)</t>
+          <t>در استعلام گروهی امروز بررسی شد ولی در کارتابل هیچ‌یک از ۹ دارنده یافت نشد</t>
         </is>
       </c>
     </row>
@@ -12421,11 +12421,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
@@ -12579,7 +12579,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
+          <t>پرریسک با مبالغ خرد (تحت نظر)</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
@@ -13590,47 +13590,47 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>صاحب چک فريمان (۰۹۲۴۰۲۰۸۶۵)</t>
+          <t>طاهره حسني</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>0924020865</t>
+          <t>5228890297</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>قرمز</t>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>پرخطر</t>
+        <v>95.5</v>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>عالی</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>پرریسک با مبالغ خرد (تحت نظر)</t>
+          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>2760000000</v>
+        <v>15500000000</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>91680000000</v>
+        <v>582454940000</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>21630000000</v>
+        <v>0</v>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
+          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
         </is>
       </c>
     </row>
@@ -13640,12 +13640,12 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>طاهره حسني</t>
+          <t>عباس مقنی</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>5228890297</t>
+          <t>0922030936</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -13654,7 +13654,7 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>95.5</v>
+        <v>96.7</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
@@ -13667,13 +13667,13 @@
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>15500000000</v>
+        <v>42320000000</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>582454940000</v>
+        <v>909792000000</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>0</v>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>عباس مقنی</t>
+          <t>عطاری ید اله</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>0922030936</t>
+          <t>2298907366</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -13704,7 +13704,7 @@
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>96.7</v>
+        <v>96</v>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
@@ -13717,13 +13717,13 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>42320000000</v>
+        <v>24000000000</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>909792000000</v>
+        <v>308000000000</v>
       </c>
       <c r="K26" s="13" t="n">
         <v>0</v>
@@ -13740,12 +13740,12 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>عطاری ید اله</t>
+          <t>عقيل نرمكي</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2298907366</t>
+          <t>0920541526</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -13754,7 +13754,7 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>96</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
@@ -13767,13 +13767,13 @@
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>24000000000</v>
+        <v>4640000000</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>308000000000</v>
+        <v>183268499994</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
@@ -13790,21 +13790,17 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>عقيل نرمكي</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>0920541526</t>
-        </is>
-      </c>
+          <t>عليرضا ضرغام مقدم</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr"/>
       <c r="D28" s="11" t="inlineStr">
         <is>
           <t>سفید</t>
         </is>
       </c>
       <c r="E28" s="10" t="n">
-        <v>88.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
@@ -13813,17 +13809,17 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>4640000000</v>
+        <v>350000000</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>183268499994</v>
+        <v>0</v>
       </c>
       <c r="K28" s="13" t="n">
         <v>0</v>
@@ -13840,7 +13836,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>عليرضا ضرغام مقدم</t>
+          <t>عليرضا يعقوبي</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr"/>
@@ -13850,11 +13846,11 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>90</v>
+        <v>76.2</v>
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>عالی</t>
+          <t>خوب</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -13863,20 +13859,20 @@
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>350000000</v>
+        <v>1740000000</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>0</v>
+        <v>26680000000</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
+          <t>سلامت مالی مطلوب و کم‌ریسک. تداوم همکاری با رعایت دوره‌های معمول تسویه حساب توصیه می‌شود.</t>
         </is>
       </c>
     </row>
@@ -13886,7 +13882,7 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>عليرضا يعقوبي</t>
+          <t>فر هنگ نیا مهزیار</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr"/>
@@ -13896,7 +13892,7 @@
         </is>
       </c>
       <c r="E30" s="10" t="n">
-        <v>76.2</v>
+        <v>75</v>
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
@@ -13909,13 +13905,13 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>1740000000</v>
+        <v>895000000</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>26680000000</v>
+        <v>0</v>
       </c>
       <c r="K30" s="13" t="n">
         <v>0</v>
@@ -13932,21 +13928,25 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>فر هنگ نیا مهزیار</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr"/>
+          <t>فريد والي</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>0010485295</t>
+        </is>
+      </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
           <t>سفید</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>خوب</t>
+          <t>عالی</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -13958,17 +13958,17 @@
         <v>1</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>895000000</v>
+        <v>4000000000</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>0</v>
+        <v>58720000000</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>سلامت مالی مطلوب و کم‌ریسک. تداوم همکاری با رعایت دوره‌های معمول تسویه حساب توصیه می‌شود.</t>
+          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
         </is>
       </c>
     </row>
@@ -13978,12 +13978,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>فريد والي</t>
+          <t>محمد ابراهيمي دشت بياض</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>0010485295</t>
+          <t>0880141281</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -14001,17 +14001,17 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>4000000000</v>
+        <v>1950000000</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>58720000000</v>
+        <v>406028397656</v>
       </c>
       <c r="K32" s="13" t="n">
         <v>0</v>
@@ -14028,12 +14028,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>محمد ابراهيمي دشت بياض</t>
+          <t>محمد حميدي شيرغان</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>0880141281</t>
+          <t>0924049650</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -14055,13 +14055,13 @@
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>1950000000</v>
+        <v>3940000000</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>406028397656</v>
+        <v>17880000000</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>0</v>
@@ -14078,47 +14078,47 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>محمد حميدي شيرغان</t>
+          <t>محمد رفیق طرقی</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>0924049650</t>
+          <t>0890543331</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>سفید</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E34" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="F34" s="24" t="inlineStr">
-        <is>
-          <t>عالی</t>
+        <v>0</v>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>پرخطر</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
+          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>3940000000</v>
+        <v>15000000000</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>17880000000</v>
+        <v>265665000000</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>0</v>
+        <v>40300000000</v>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
+          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
         </is>
       </c>
     </row>
@@ -14128,12 +14128,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>محمد رفیق طرقی</t>
+          <t>محمد زاهدي آغوي</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>0890543331</t>
+          <t>0690489838</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -14155,16 +14155,16 @@
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>15000000000</v>
+        <v>8890000000</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>265665000000</v>
+        <v>118581860000</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>40300000000</v>
+        <v>18796000000</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -14178,12 +14178,12 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>محمد زاهدي آغوي</t>
+          <t>محمد ضيافتي مالدار</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>0690489838</t>
+          <t>0922236992</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -14205,16 +14205,16 @@
         </is>
       </c>
       <c r="H36" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>8890000000</v>
+        <v>53520000000</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>118581860000</v>
+        <v>6868842000000</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>18796000000</v>
+        <v>114960000000</v>
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
@@ -14228,47 +14228,43 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>محمد ضيافتي مالدار</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>0922236992</t>
-        </is>
-      </c>
+          <t>محمد طاهري</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>قرمز</t>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>پرخطر</t>
+        <v>75</v>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>خوب</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
+          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>53520000000</v>
+        <v>6000000000</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>6868842000000</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>114960000000</v>
+        <v>0</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
+          <t>سلامت مالی مطلوب و کم‌ریسک. تداوم همکاری با رعایت دوره‌های معمول تسویه حساب توصیه می‌شود.</t>
         </is>
       </c>
     </row>
@@ -14278,17 +14274,21 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>محمد طاهري</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr"/>
+          <t>محمدباقر مشيري</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>0922010536</t>
+        </is>
+      </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
           <t>سفید</t>
         </is>
       </c>
       <c r="E38" s="10" t="n">
-        <v>75</v>
+        <v>83.2</v>
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
@@ -14301,16 +14301,16 @@
         </is>
       </c>
       <c r="H38" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>6000000000</v>
+        <v>16450000000</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>0</v>
+        <v>334070000000</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>0</v>
+        <v>1326000000</v>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
@@ -14324,47 +14324,47 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>محمدباقر مشيري</t>
+          <t>محمدجواد وفادارعيدگاهي</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>0922010536</t>
+          <t>0924020865</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>سفید</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>خوب</t>
+        <v>0</v>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>پرخطر</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>16450000000</v>
+        <v>5520000000</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>334070000000</v>
+        <v>275040000000</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>1326000000</v>
+        <v>64890000000</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>سلامت مالی مطلوب و کم‌ریسک. تداوم همکاری با رعایت دوره‌های معمول تسویه حساب توصیه می‌شود.</t>
+          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
         </is>
       </c>
     </row>
@@ -14374,47 +14374,47 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>محمدجواد وفادارعيدگاهي</t>
+          <t>مرتضي مؤذن</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>0924020865</t>
+          <t>0920630138</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>قرمز</t>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>پرخطر</t>
+        <v>97.3</v>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>عالی</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>پرریسک با مبالغ خرد (تحت نظر)</t>
+          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
         </is>
       </c>
       <c r="H40" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>2760000000</v>
+        <v>3340000000</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>183360000000</v>
+        <v>237172500000</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>43260000000</v>
+        <v>0</v>
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
+          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
         </is>
       </c>
     </row>
@@ -14424,12 +14424,12 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>مرتضي مؤذن</t>
+          <t>مرتضي پيروزيان</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>0920630138</t>
+          <t>0942904257</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -14438,7 +14438,7 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>97.3</v>
+        <v>96.2</v>
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
@@ -14447,17 +14447,17 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
+          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>3340000000</v>
+        <v>6000000000</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>237172500000</v>
+        <v>81160000000</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>0</v>
@@ -14474,12 +14474,12 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>مرتضي پيروزيان</t>
+          <t>مريم حسني</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>0942904257</t>
+          <t>0934578771</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -14488,7 +14488,7 @@
         </is>
       </c>
       <c r="E42" s="10" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
@@ -14501,13 +14501,13 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>6000000000</v>
+        <v>9300000000</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>81160000000</v>
+        <v>230324220000</v>
       </c>
       <c r="K42" s="13" t="n">
         <v>0</v>
@@ -14524,12 +14524,12 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>مريم حسني</t>
+          <t>مسعود زرين نام</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>0934578771</t>
+          <t>0945428022</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
@@ -14547,17 +14547,17 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>9300000000</v>
+        <v>2000000000</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>230324220000</v>
+        <v>7899823000</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>0</v>
@@ -14574,12 +14574,12 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>مسعود زرين نام</t>
+          <t>معصومه دوامي</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>0945428022</t>
+          <t>6439564609</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -14588,7 +14588,7 @@
         </is>
       </c>
       <c r="E44" s="10" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
@@ -14597,17 +14597,17 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
+          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>2000000000</v>
+        <v>82500000000</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>7899823000</v>
+        <v>973800000000</v>
       </c>
       <c r="K44" s="13" t="n">
         <v>0</v>
@@ -14624,12 +14624,12 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>معصومه دوامي</t>
+          <t>مقنی عباس</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>6439564609</t>
+          <t>0922030936</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -14638,7 +14638,7 @@
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
@@ -14647,17 +14647,17 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>82500000000</v>
+        <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>973800000000</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>0</v>
@@ -14674,12 +14674,12 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>مقنی عباس</t>
+          <t>ملکه محمدي</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>0922030936</t>
+          <t>0932151930</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>0</v>
+        <v>935000000</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>0</v>
+        <v>8350000000</v>
       </c>
       <c r="K46" s="13" t="n">
         <v>0</v>
@@ -14724,12 +14724,12 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>ملکه محمدي</t>
+          <t>موذن مرتضی</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>0932151930</t>
+          <t>0920630138</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
@@ -14751,13 +14751,13 @@
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>935000000</v>
+        <v>1880000000</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>8350000000</v>
+        <v>143073500000</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>0</v>
@@ -14774,47 +14774,47 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>موذن مرتضی</t>
+          <t>ميلاد دلجو</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>0920630138</t>
+          <t>2710183331</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>سفید</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E48" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>عالی</t>
+        <v>0.6</v>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>پرخطر</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
+          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>1880000000</v>
+        <v>22000000000</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>143073500000</v>
+        <v>373552000000</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>0</v>
+        <v>5304000000</v>
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
+          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
         </is>
       </c>
     </row>
@@ -14824,47 +14824,47 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>ميلاد دلجو</t>
+          <t>نصرت شيدا</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>2710183331</t>
+          <t>6439490842</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>قرمز</t>
+          <t>سفید</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t>پرخطر</t>
+        <v>100</v>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>عالی</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
+          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>22000000000</v>
+        <v>340000000</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>373552000000</v>
+        <v>2430800000</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>5304000000</v>
+        <v>0</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
+          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
         </is>
       </c>
     </row>
@@ -14874,12 +14874,12 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>نصرت شيدا</t>
+          <t>و ارسته شهریار ان سعید</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>6439490842</t>
+          <t>0923318895</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -14888,7 +14888,7 @@
         </is>
       </c>
       <c r="E50" s="10" t="n">
-        <v>100</v>
+        <v>88.7</v>
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
@@ -14897,17 +14897,17 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>کم‌ریسک و کم‌تراکنش (عادی و فرصت‌ها)</t>
+          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>340000000</v>
+        <v>37350000000</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>2430800000</v>
+        <v>111320000000</v>
       </c>
       <c r="K50" s="13" t="n">
         <v>0</v>
@@ -14924,47 +14924,47 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>و ارسته شهریار ان سعید</t>
+          <t>وحيد اشرافيان</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>0923318895</t>
+          <t>0921320711</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>سفید</t>
+          <t>قرمز</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>عالی</t>
+        <v>0</v>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>پرخطر</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>کم‌ریسک و پرتراکنش (ستاره‌ها و مشتریان طلایی)</t>
+          <t>پرریسک با مبالغ خرد (تحت نظر)</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>37350000000</v>
+        <v>1465000000</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>111320000000</v>
+        <v>527354558624</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>0</v>
+        <v>12494000000</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>مشتری ممتاز با سلامت مالی درخشان. واجد شرایط دریافت بالاترین سقف اعتبار و تسهیلات تجاری.</t>
+          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
         </is>
       </c>
     </row>
@@ -14974,12 +14974,12 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>وحيد اشرافيان</t>
+          <t>وحيد محمدي انور</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>0921320711</t>
+          <t>1920394974</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -14997,20 +14997,20 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>پرریسک با مبالغ خرد (تحت نظر)</t>
+          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
         </is>
       </c>
       <c r="H52" s="10" t="n">
         <v>2</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>1465000000</v>
+        <v>7400000000</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>527354558624</v>
+        <v>25978000000</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>12494000000</v>
+        <v>8400000000</v>
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
@@ -15019,84 +15019,34 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>وحيد محمدي انور</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>1920394974</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>قرمز</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="23" t="inlineStr">
-        <is>
-          <t>پرخطر</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>پرریسک با تعهدات سنگین (هشدار قرمز و بحرانی)</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" s="12" t="n">
-        <v>7400000000</v>
-      </c>
-      <c r="J53" s="12" t="n">
-        <v>25978000000</v>
-      </c>
-      <c r="K53" s="12" t="n">
-        <v>8400000000</v>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>هشدار بحرانی: سلامت مالی بسیار ضعیف و احتمال بالای نکول. از پذیرش هرگونه چک جدید اکیداً خودداری شود.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>مجموع</t>
         </is>
       </c>
-      <c r="B54" s="21" t="n"/>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="21" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="25">
-        <f>SUM(H2:H53)</f>
+      <c r="B53" s="21" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="25">
+        <f>SUM(H2:H52)</f>
         <v/>
       </c>
-      <c r="I54" s="22">
-        <f>SUM(I2:I53)</f>
+      <c r="I53" s="22">
+        <f>SUM(I2:I52)</f>
         <v/>
       </c>
-      <c r="J54" s="22">
-        <f>SUM(J2:J53)</f>
+      <c r="J53" s="22">
+        <f>SUM(J2:J52)</f>
         <v/>
       </c>
-      <c r="K54" s="22">
-        <f>SUM(K2:K53)</f>
+      <c r="K53" s="22">
+        <f>SUM(K2:K52)</f>
         <v/>
       </c>
-      <c r="L54" s="21" t="n"/>
+      <c r="L53" s="21" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
